--- a/docs/oc-regiones/articulos-de-escritorio-y-papeleria/coquimbo.xlsx
+++ b/docs/oc-regiones/articulos-de-escritorio-y-papeleria/coquimbo.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M319"/>
+  <dimension ref="A1:M323"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>4266.94</v>
+        <v>4230.81</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>4131.16</v>
+        <v>4096.17</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>1526.26</v>
+        <v>1513.34</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>3160.12</v>
+        <v>3143.88</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>1822.46</v>
+        <v>1813.09</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>3479.56</v>
+        <v>3444.84</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>8711.469999999999</v>
+        <v>8620.24</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>2482.26</v>
+        <v>2456.26</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>17892.41</v>
+        <v>17794.62</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>2433.71</v>
+        <v>2420.41</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>8182.62</v>
+        <v>8091.46</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>2117.52</v>
+        <v>2105.93</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>2555.45</v>
+        <v>2552.2</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>748.11</v>
+        <v>747.16</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>2018.06</v>
+        <v>2015.49</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>772.66</v>
+        <v>775.42</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>826.08</v>
+        <v>829.03</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>1663.64</v>
+        <v>1669.57</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>749.71</v>
+        <v>757.87</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>3714.45</v>
+        <v>3726.66</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>2404.41</v>
+        <v>2445.91</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>3058.79</v>
+        <v>3111.59</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>942.35</v>
+        <v>958.62</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>2141.68</v>
+        <v>2178.64</v>
       </c>
     </row>
     <row r="26">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>2868.37</v>
+        <v>2888.24</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>8227.690000000001</v>
+        <v>8284.690000000001</v>
       </c>
     </row>
     <row r="28">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>7505.15</v>
+        <v>7540.1</v>
       </c>
     </row>
     <row r="29">
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>1123.43</v>
+        <v>1128.66</v>
       </c>
     </row>
     <row r="30">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>977.15</v>
+        <v>981.7</v>
       </c>
     </row>
     <row r="31">
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>829.45</v>
+        <v>833.3200000000001</v>
       </c>
     </row>
     <row r="32">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>6369.5</v>
+        <v>6415.42</v>
       </c>
     </row>
     <row r="33">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>1129.88</v>
+        <v>1138.03</v>
       </c>
     </row>
     <row r="34">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>4068.29</v>
+        <v>4097.62</v>
       </c>
     </row>
     <row r="35">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>4133.2</v>
+        <v>4163</v>
       </c>
     </row>
     <row r="36">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>3796.77</v>
+        <v>3824.14</v>
       </c>
     </row>
     <row r="37">
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>6818.91</v>
+        <v>6790.8</v>
       </c>
     </row>
     <row r="38">
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>2583.49</v>
+        <v>2572.84</v>
       </c>
     </row>
     <row r="39">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>7478.06</v>
+        <v>7447.24</v>
       </c>
     </row>
     <row r="40">
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>14909</v>
+        <v>14847.55</v>
       </c>
     </row>
     <row r="41">
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>8861.120000000001</v>
+        <v>8847.379999999999</v>
       </c>
     </row>
     <row r="42">
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>12276.73</v>
+        <v>12257.7</v>
       </c>
     </row>
     <row r="43">
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>941.7</v>
+        <v>940.24</v>
       </c>
     </row>
     <row r="44">
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>5255.4</v>
+        <v>5282.54</v>
       </c>
     </row>
     <row r="45">
@@ -3192,7 +3192,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>18688.09</v>
+        <v>18784.6</v>
       </c>
     </row>
     <row r="46">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>4010.17</v>
+        <v>4030.88</v>
       </c>
     </row>
     <row r="47">
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>2994.98</v>
+        <v>3010.45</v>
       </c>
     </row>
     <row r="48">
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>756.96</v>
+        <v>760.87</v>
       </c>
     </row>
     <row r="49">
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>6072.43</v>
+        <v>6115.29</v>
       </c>
     </row>
     <row r="50">
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>2480.53</v>
+        <v>2498.04</v>
       </c>
     </row>
     <row r="51">
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>2556.77</v>
+        <v>2574.82</v>
       </c>
     </row>
     <row r="52">
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>753.5700000000001</v>
+        <v>758.89</v>
       </c>
     </row>
     <row r="53">
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>741.11</v>
+        <v>746.34</v>
       </c>
     </row>
     <row r="54">
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>2776.63</v>
+        <v>2796.23</v>
       </c>
     </row>
     <row r="55">
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>1394.04</v>
+        <v>1376.33</v>
       </c>
     </row>
     <row r="56">
@@ -3863,7 +3863,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>2822.18</v>
+        <v>2786.33</v>
       </c>
     </row>
     <row r="57">
@@ -3924,7 +3924,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>5297.35</v>
+        <v>5230.06</v>
       </c>
     </row>
     <row r="58">
@@ -3985,7 +3985,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>970.92</v>
+        <v>958.59</v>
       </c>
     </row>
     <row r="59">
@@ -4046,7 +4046,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>1075.78</v>
+        <v>1065.08</v>
       </c>
     </row>
     <row r="60">
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>1123.51</v>
+        <v>1119.48</v>
       </c>
     </row>
     <row r="61">
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>3165.45</v>
+        <v>3154.1</v>
       </c>
     </row>
     <row r="62">
@@ -4229,7 +4229,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>1795.4</v>
+        <v>1788.96</v>
       </c>
     </row>
     <row r="63">
@@ -4290,7 +4290,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>803.3200000000001</v>
+        <v>801.58</v>
       </c>
     </row>
     <row r="64">
@@ -4351,7 +4351,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>783.4</v>
+        <v>780.12</v>
       </c>
     </row>
     <row r="65">
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>4684.08</v>
+        <v>4664.44</v>
       </c>
     </row>
     <row r="66">
@@ -4473,7 +4473,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>17652.61</v>
+        <v>17448.32</v>
       </c>
     </row>
     <row r="67">
@@ -4534,7 +4534,7 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>1184.27</v>
+        <v>1170.56</v>
       </c>
     </row>
     <row r="68">
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>8323.32</v>
+        <v>8252.82</v>
       </c>
     </row>
     <row r="69">
@@ -4656,7 +4656,7 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>2182.79</v>
+        <v>2181.04</v>
       </c>
     </row>
     <row r="70">
@@ -4717,7 +4717,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>3221.3</v>
+        <v>3218.71</v>
       </c>
     </row>
     <row r="71">
@@ -4778,7 +4778,7 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>68851.05</v>
+        <v>68795.71000000001</v>
       </c>
     </row>
     <row r="72">
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>919.5599999999999</v>
+        <v>918.8200000000001</v>
       </c>
     </row>
     <row r="73">
@@ -4900,7 +4900,7 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>7642.96</v>
+        <v>7636.82</v>
       </c>
     </row>
     <row r="74">
@@ -4961,7 +4961,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>2012.28</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="75">
@@ -5022,7 +5022,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>2968.77</v>
+        <v>2980.16</v>
       </c>
     </row>
     <row r="76">
@@ -5083,7 +5083,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>1709.66</v>
+        <v>1716.22</v>
       </c>
     </row>
     <row r="77">
@@ -5144,7 +5144,7 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>3949.53</v>
+        <v>3967.42</v>
       </c>
     </row>
     <row r="78">
@@ -5205,7 +5205,7 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>7724.84</v>
+        <v>7759.85</v>
       </c>
     </row>
     <row r="79">
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>1119.16</v>
+        <v>1124.23</v>
       </c>
     </row>
     <row r="80">
@@ -5327,7 +5327,7 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>3372.78</v>
+        <v>3381.73</v>
       </c>
     </row>
     <row r="81">
@@ -5388,7 +5388,7 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>872.37</v>
+        <v>874.6799999999999</v>
       </c>
     </row>
     <row r="82">
@@ -5449,7 +5449,7 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>11836.19</v>
+        <v>11851.36</v>
       </c>
     </row>
     <row r="83">
@@ -5510,7 +5510,7 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>7614.13</v>
+        <v>7623.89</v>
       </c>
     </row>
     <row r="84">
@@ -5571,7 +5571,7 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>2468.25</v>
+        <v>2471.41</v>
       </c>
     </row>
     <row r="85">
@@ -5632,7 +5632,7 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>1565.51</v>
+        <v>1567.52</v>
       </c>
     </row>
     <row r="86">
@@ -5693,7 +5693,7 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>1719.65</v>
+        <v>1721.86</v>
       </c>
     </row>
     <row r="87">
@@ -5754,7 +5754,7 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>1738.49</v>
+        <v>1750.45</v>
       </c>
     </row>
     <row r="88">
@@ -5815,7 +5815,7 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>7826.07</v>
+        <v>7879.94</v>
       </c>
     </row>
     <row r="89">
@@ -5876,7 +5876,7 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>809.54</v>
+        <v>815.11</v>
       </c>
     </row>
     <row r="90">
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>6245.87</v>
+        <v>6288.86</v>
       </c>
     </row>
     <row r="91">
@@ -5998,7 +5998,7 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>1267.53</v>
+        <v>1278.36</v>
       </c>
     </row>
     <row r="92">
@@ -6059,7 +6059,7 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>5283.52</v>
+        <v>5328.67</v>
       </c>
     </row>
     <row r="93">
@@ -6120,7 +6120,7 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>13211.04</v>
+        <v>13352.75</v>
       </c>
     </row>
     <row r="94">
@@ -6181,7 +6181,7 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>3017.33</v>
+        <v>3049.7</v>
       </c>
     </row>
     <row r="95">
@@ -6242,7 +6242,7 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>3375.09</v>
+        <v>3416.57</v>
       </c>
     </row>
     <row r="96">
@@ -6303,7 +6303,7 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>20475.37</v>
+        <v>20727.02</v>
       </c>
     </row>
     <row r="97">
@@ -6364,7 +6364,7 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>842.97</v>
+        <v>847.58</v>
       </c>
     </row>
     <row r="98">
@@ -6425,7 +6425,7 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>927.89</v>
+        <v>932.96</v>
       </c>
     </row>
     <row r="99">
@@ -6486,7 +6486,7 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>1405.49</v>
+        <v>1387.65</v>
       </c>
     </row>
     <row r="100">
@@ -6547,7 +6547,7 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>2677.83</v>
+        <v>2643.84</v>
       </c>
     </row>
     <row r="101">
@@ -6608,7 +6608,7 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>17626.34</v>
+        <v>17591.62</v>
       </c>
     </row>
     <row r="102">
@@ -6669,7 +6669,7 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>2092.07</v>
+        <v>2092.09</v>
       </c>
     </row>
     <row r="103">
@@ -6730,7 +6730,7 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>10564.35</v>
+        <v>10579.02</v>
       </c>
     </row>
     <row r="104">
@@ -6791,7 +6791,7 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>799.33</v>
+        <v>800.4400000000001</v>
       </c>
     </row>
     <row r="105">
@@ -6852,7 +6852,7 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>2394.93</v>
+        <v>2393.29</v>
       </c>
     </row>
     <row r="106">
@@ -6913,7 +6913,7 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>2663.23</v>
+        <v>2654.09</v>
       </c>
     </row>
     <row r="107">
@@ -6974,7 +6974,7 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>5305.65</v>
+        <v>5340.43</v>
       </c>
     </row>
     <row r="108">
@@ -7035,7 +7035,7 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>5390.59</v>
+        <v>5463.18</v>
       </c>
     </row>
     <row r="109">
@@ -7096,7 +7096,7 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>2828.1</v>
+        <v>2866.18</v>
       </c>
     </row>
     <row r="110">
@@ -7157,7 +7157,7 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>66503.98</v>
+        <v>67399.55</v>
       </c>
     </row>
     <row r="111">
@@ -7218,7 +7218,7 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>1980.32</v>
+        <v>2010.47</v>
       </c>
     </row>
     <row r="112">
@@ -7279,7 +7279,7 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>803.01</v>
+        <v>815.24</v>
       </c>
     </row>
     <row r="113">
@@ -7340,7 +7340,7 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>2889.39</v>
+        <v>2959.65</v>
       </c>
     </row>
     <row r="114">
@@ -7401,7 +7401,7 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>24985.42</v>
+        <v>25593.01</v>
       </c>
     </row>
     <row r="115">
@@ -7462,7 +7462,7 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>8385.120000000001</v>
+        <v>8589.030000000001</v>
       </c>
     </row>
     <row r="116">
@@ -7523,7 +7523,7 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>2923.08</v>
+        <v>3011.72</v>
       </c>
     </row>
     <row r="117">
@@ -7584,7 +7584,7 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>17888.52</v>
+        <v>18430.95</v>
       </c>
     </row>
     <row r="118">
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>8003.67</v>
+        <v>8246.370000000001</v>
       </c>
     </row>
     <row r="119">
@@ -7706,13 +7706,13 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>4081.44</v>
+        <v>4202.75</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2992-12-CM26</t>
+          <t>1430710-87-CM26</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>69.040.800-7</t>
+          <t>61.606.403-7</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MONTEPATRIA</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE COQUIMBO</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -7752,12 +7752,12 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K120" t="inlineStr"/>
@@ -7767,13 +7767,13 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>9302.459999999999</v>
+        <v>5144.81</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>3712-35-CM26</t>
+          <t>2992-12-CM26</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -7798,12 +7798,12 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>69.040.800-7</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>I MUNICIPALIDAD DE MONTEPATRIA</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -7813,12 +7813,12 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>OPEN SANTIAGO SPA</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>78.069.505-6</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K121" t="inlineStr"/>
@@ -7828,13 +7828,13 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>984.59</v>
+        <v>9578.959999999999</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>1430710-87-CM26</t>
+          <t>3712-35-CM26</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -7859,12 +7859,12 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>61.606.403-7</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE COQUIMBO</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -7874,12 +7874,12 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>OPEN SANTIAGO SPA</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>78.069.505-6</t>
         </is>
       </c>
       <c r="K122" t="inlineStr"/>
@@ -7889,7 +7889,7 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>4996.31</v>
+        <v>1013.86</v>
       </c>
     </row>
     <row r="123">
@@ -7950,7 +7950,7 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>4467.49</v>
+        <v>4434.06</v>
       </c>
     </row>
     <row r="124">
@@ -8011,7 +8011,7 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>1127.68</v>
+        <v>1130.94</v>
       </c>
     </row>
     <row r="125">
@@ -8072,7 +8072,7 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>2802.1</v>
+        <v>2810.21</v>
       </c>
     </row>
     <row r="126">
@@ -8133,7 +8133,7 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>5488.25</v>
+        <v>5504.15</v>
       </c>
     </row>
     <row r="127">
@@ -8194,7 +8194,7 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>1252.95</v>
+        <v>1259.42</v>
       </c>
     </row>
     <row r="128">
@@ -8255,7 +8255,7 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>2371.39</v>
+        <v>2383.64</v>
       </c>
     </row>
     <row r="129">
@@ -8316,13 +8316,13 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>2204.91</v>
+        <v>2216.3</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2711-27-CM26</t>
+          <t>707418-12-CM26</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -8347,12 +8347,12 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>69.040.700-0</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE OVALLE</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -8362,12 +8362,12 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K130" t="inlineStr"/>
@@ -8377,13 +8377,13 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>2222.71</v>
+        <v>2203.81</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>707418-12-CM26</t>
+          <t>2711-27-CM26</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -8408,12 +8408,12 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>69.040.700-0</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>MUNICIPALIDAD DE OVALLE</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K131" t="inlineStr"/>
@@ -8438,7 +8438,7 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>2213.14</v>
+        <v>2213.34</v>
       </c>
     </row>
     <row r="132">
@@ -8499,7 +8499,7 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>4179.82</v>
+        <v>4191.29</v>
       </c>
     </row>
     <row r="133">
@@ -8560,7 +8560,7 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>3636.34</v>
+        <v>3646.32</v>
       </c>
     </row>
     <row r="134">
@@ -8621,7 +8621,7 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>11039.68</v>
+        <v>11069.98</v>
       </c>
     </row>
     <row r="135">
@@ -8682,7 +8682,7 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>3348.5</v>
+        <v>3357.69</v>
       </c>
     </row>
     <row r="136">
@@ -8743,7 +8743,7 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>1294.23</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="137">
@@ -8804,7 +8804,7 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>1481.35</v>
+        <v>1494.83</v>
       </c>
     </row>
     <row r="138">
@@ -8865,7 +8865,7 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>10009.96</v>
+        <v>10079.65</v>
       </c>
     </row>
     <row r="139">
@@ -8926,7 +8926,7 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>811.67</v>
+        <v>817.02</v>
       </c>
     </row>
     <row r="140">
@@ -8987,7 +8987,7 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>5234.65</v>
+        <v>5281.27</v>
       </c>
     </row>
     <row r="141">
@@ -9048,7 +9048,7 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>846.11</v>
+        <v>844.66</v>
       </c>
     </row>
     <row r="142">
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>24584.03</v>
+        <v>24541.9</v>
       </c>
     </row>
     <row r="143">
@@ -9170,7 +9170,7 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>1196.02</v>
+        <v>1194.79</v>
       </c>
     </row>
     <row r="144">
@@ -9231,7 +9231,7 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>933.27</v>
+        <v>926.58</v>
       </c>
     </row>
     <row r="145">
@@ -9292,7 +9292,7 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>1053.27</v>
+        <v>1045.73</v>
       </c>
     </row>
     <row r="146">
@@ -9353,7 +9353,7 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>10833.3</v>
+        <v>10755.7</v>
       </c>
     </row>
     <row r="147">
@@ -9414,13 +9414,13 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>1949.94</v>
+        <v>1935.97</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>3712-67-CM26</t>
+          <t>1057439-1206-CM26</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -9445,12 +9445,12 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>61.606.402-9</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -9460,12 +9460,12 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>ROLAND VORWERK Y COMPANIA LIMITADA</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>78.178.530-k</t>
         </is>
       </c>
       <c r="K148" t="inlineStr"/>
@@ -9475,13 +9475,13 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>1037.84</v>
+        <v>3396.27</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>1057439-1206-CM26</t>
+          <t>1962-77-CM26</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -9506,12 +9506,12 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>61.606.402-9</t>
+          <t>61.004.012-8</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
+          <t>Gendarmería de Chile - Dirección Regional de Coquimbo</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -9521,12 +9521,12 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>ROLAND VORWERK Y COMPANIA LIMITADA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>78.178.530-k</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K149" t="inlineStr"/>
@@ -9536,13 +9536,13 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>3401.27</v>
+        <v>1977.71</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>1962-77-CM26</t>
+          <t>3712-67-CM26</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -9567,12 +9567,12 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>61.004.012-8</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Gendarmería de Chile - Dirección Regional de Coquimbo</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -9582,12 +9582,12 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K150" t="inlineStr"/>
@@ -9597,7 +9597,7 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>1980.63</v>
+        <v>1036.31</v>
       </c>
     </row>
     <row r="151">
@@ -9658,7 +9658,7 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>7147.98</v>
+        <v>7109.05</v>
       </c>
     </row>
     <row r="152">
@@ -9719,7 +9719,7 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>815.35</v>
+        <v>810.91</v>
       </c>
     </row>
     <row r="153">
@@ -9780,7 +9780,7 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>912.74</v>
+        <v>907.1900000000001</v>
       </c>
     </row>
     <row r="154">
@@ -9841,7 +9841,7 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>8029.1</v>
+        <v>7998.11</v>
       </c>
     </row>
     <row r="155">
@@ -9902,13 +9902,13 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>2124.32</v>
+        <v>2116.12</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>1079505-57-CM26</t>
+          <t>5553-9-CM26</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -9933,12 +9933,12 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>60.505.206-1</t>
+          <t>61.533.000-0</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IV ZONA</t>
+          <t>INSTITUTO DE SEGURIDAD LABORAL</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -9948,12 +9948,12 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>MALMO S.A.</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>76.195.558-6</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K156" t="inlineStr"/>
@@ -9963,7 +9963,7 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>1353.15</v>
+        <v>839.83</v>
       </c>
     </row>
     <row r="157">
@@ -10024,13 +10024,13 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>1265.49</v>
+        <v>1321.38</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>5553-9-CM26</t>
+          <t>1079505-57-CM26</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -10055,12 +10055,12 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>61.533.000-0</t>
+          <t>60.505.206-1</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>INSTITUTO DE SEGURIDAD LABORAL</t>
+          <t>SECCIÓN COMPRAS IV ZONA</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -10070,12 +10070,12 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>MALMO S.A.</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.195.558-6</t>
         </is>
       </c>
       <c r="K158" t="inlineStr"/>
@@ -10085,7 +10085,7 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>804.3099999999999</v>
+        <v>1412.91</v>
       </c>
     </row>
     <row r="159">
@@ -10146,13 +10146,13 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>1613.24</v>
+        <v>1660.1</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>1079505-61-CM26</t>
+          <t>3712-92-CM26</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -10177,12 +10177,12 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>60.505.206-1</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IV ZONA</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -10192,12 +10192,12 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>MALMO S.A.</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>76.195.558-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K160" t="inlineStr"/>
@@ -10207,13 +10207,13 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>53471.01</v>
+        <v>1059.54</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>3712-92-CM26</t>
+          <t>1079505-61-CM26</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -10238,12 +10238,12 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>60.505.206-1</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>SECCIÓN COMPRAS IV ZONA</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -10253,12 +10253,12 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>MALMO S.A.</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>76.195.558-6</t>
         </is>
       </c>
       <c r="K161" t="inlineStr"/>
@@ -10268,7 +10268,7 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>1055.38</v>
+        <v>53681.83</v>
       </c>
     </row>
     <row r="162">
@@ -10329,7 +10329,7 @@
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>3045.32</v>
+        <v>3052.81</v>
       </c>
     </row>
     <row r="163">
@@ -10390,7 +10390,7 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>8733.91</v>
+        <v>8621.469999999999</v>
       </c>
     </row>
     <row r="164">
@@ -10451,7 +10451,7 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>2386.82</v>
+        <v>2356.09</v>
       </c>
     </row>
     <row r="165">
@@ -10512,7 +10512,7 @@
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>4945.58</v>
+        <v>4910.68</v>
       </c>
     </row>
     <row r="166">
@@ -10573,7 +10573,7 @@
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>1179.13</v>
+        <v>1200.51</v>
       </c>
     </row>
     <row r="167">
@@ -10634,7 +10634,7 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>1002.62</v>
+        <v>1020.8</v>
       </c>
     </row>
     <row r="168">
@@ -10695,7 +10695,7 @@
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>881.9</v>
+        <v>881.86</v>
       </c>
     </row>
     <row r="169">
@@ -10756,7 +10756,7 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>10417.6</v>
+        <v>10371.01</v>
       </c>
     </row>
     <row r="170">
@@ -10817,7 +10817,7 @@
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>1756.8</v>
+        <v>1758.32</v>
       </c>
     </row>
     <row r="171">
@@ -10878,7 +10878,7 @@
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>11618.53</v>
+        <v>11628.54</v>
       </c>
     </row>
     <row r="172">
@@ -10939,7 +10939,7 @@
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>2399.62</v>
+        <v>2401.69</v>
       </c>
     </row>
     <row r="173">
@@ -11000,7 +11000,7 @@
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>929.11</v>
+        <v>932.95</v>
       </c>
     </row>
     <row r="174">
@@ -11061,7 +11061,7 @@
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>1063.97</v>
+        <v>1061.03</v>
       </c>
     </row>
     <row r="175">
@@ -11122,7 +11122,7 @@
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>3314.19</v>
+        <v>3275.93</v>
       </c>
     </row>
     <row r="176">
@@ -11183,7 +11183,7 @@
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>3909.94</v>
+        <v>3864.8</v>
       </c>
     </row>
     <row r="177">
@@ -11244,7 +11244,7 @@
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>9583.24</v>
+        <v>9472.610000000001</v>
       </c>
     </row>
     <row r="178">
@@ -11305,7 +11305,7 @@
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>2481.56</v>
+        <v>2452.91</v>
       </c>
     </row>
     <row r="179">
@@ -11366,13 +11366,13 @@
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>896.21</v>
+        <v>882.85</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>5416-184-CM26</t>
+          <t>1232565-48-CM26</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -11412,12 +11412,12 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>BAILEY GROUP SPA</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>77.638.992-7</t>
         </is>
       </c>
       <c r="K180" t="inlineStr"/>
@@ -11427,13 +11427,13 @@
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>1875.45</v>
+        <v>967.4</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>3712-159-CM26</t>
+          <t>5416-184-CM26</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K181" t="inlineStr"/>
@@ -11488,13 +11488,13 @@
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>1204.81</v>
+        <v>1864.68</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>1232565-48-CM26</t>
+          <t>3712-159-CM26</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -11519,12 +11519,12 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -11534,12 +11534,12 @@
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>BAILEY GROUP SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>77.638.992-7</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K182" t="inlineStr"/>
@@ -11549,7 +11549,7 @@
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>972.99</v>
+        <v>1197.89</v>
       </c>
     </row>
     <row r="183">
@@ -11610,7 +11610,7 @@
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>1140.52</v>
+        <v>1133.21</v>
       </c>
     </row>
     <row r="184">
@@ -11671,7 +11671,7 @@
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>1409.2</v>
+        <v>1400.18</v>
       </c>
     </row>
     <row r="185">
@@ -11732,7 +11732,7 @@
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>5518.57</v>
+        <v>5483.22</v>
       </c>
     </row>
     <row r="186">
@@ -11793,7 +11793,7 @@
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>3390.13</v>
+        <v>3368.41</v>
       </c>
     </row>
     <row r="187">
@@ -11854,7 +11854,7 @@
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>13639.12</v>
+        <v>13580.37</v>
       </c>
     </row>
     <row r="188">
@@ -11915,7 +11915,7 @@
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>1216.66</v>
+        <v>1199.06</v>
       </c>
     </row>
     <row r="189">
@@ -11976,13 +11976,13 @@
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>1462.79</v>
+        <v>1441.63</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>1057439-1991-CM26</t>
+          <t>1159-58-CM26</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -12002,17 +12002,17 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>61.606.402-9</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -12022,12 +12022,12 @@
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>ROLAND VORWERK Y COMPANIA LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>78.178.530-k</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K190" t="inlineStr"/>
@@ -12037,13 +12037,13 @@
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>1413.51</v>
+        <v>5892.84</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>1159-58-CM26</t>
+          <t>1057439-1991-CM26</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -12063,17 +12063,17 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>61.606.402-9</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -12083,12 +12083,12 @@
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>ROLAND VORWERK Y COMPANIA LIMITADA</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>78.178.530-k</t>
         </is>
       </c>
       <c r="K191" t="inlineStr"/>
@@ -12098,7 +12098,7 @@
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>6022.41</v>
+        <v>1383.1</v>
       </c>
     </row>
     <row r="192">
@@ -12159,7 +12159,7 @@
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>1090.59</v>
+        <v>1055.81</v>
       </c>
     </row>
     <row r="193">
@@ -12220,7 +12220,7 @@
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>778.64</v>
+        <v>753.8099999999999</v>
       </c>
     </row>
     <row r="194">
@@ -12281,7 +12281,7 @@
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>1457.17</v>
+        <v>1410.7</v>
       </c>
     </row>
     <row r="195">
@@ -12342,7 +12342,7 @@
         </is>
       </c>
       <c r="M195" s="2" t="n">
-        <v>795.1900000000001</v>
+        <v>769.84</v>
       </c>
     </row>
     <row r="196">
@@ -12403,7 +12403,7 @@
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>904.21</v>
+        <v>886.38</v>
       </c>
     </row>
     <row r="197">
@@ -12464,7 +12464,7 @@
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>779.1</v>
+        <v>763.74</v>
       </c>
     </row>
     <row r="198">
@@ -12525,7 +12525,7 @@
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>780.4400000000001</v>
+        <v>766.29</v>
       </c>
     </row>
     <row r="199">
@@ -12586,13 +12586,13 @@
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>904.9299999999999</v>
+        <v>880.6900000000001</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>2708-193-CM26</t>
+          <t>548854-16-CM26</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -12612,17 +12612,17 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>69.040.700-0</t>
+          <t>61.979.440-0</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE OVALLE</t>
+          <t>Instituto de Prevision Social</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -12647,13 +12647,13 @@
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>954.9</v>
+        <v>6860.64</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>548854-16-CM26</t>
+          <t>2708-193-CM26</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -12673,17 +12673,17 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>61.979.440-0</t>
+          <t>69.040.700-0</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Instituto de Prevision Social</t>
+          <t>MUNICIPALIDAD DE OVALLE</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -12708,7 +12708,7 @@
         </is>
       </c>
       <c r="M201" s="2" t="n">
-        <v>7049.39</v>
+        <v>929.33</v>
       </c>
     </row>
     <row r="202">
@@ -12769,7 +12769,7 @@
         </is>
       </c>
       <c r="M202" s="2" t="n">
-        <v>1243.16</v>
+        <v>1246.78</v>
       </c>
     </row>
     <row r="203">
@@ -12830,7 +12830,7 @@
         </is>
       </c>
       <c r="M203" s="2" t="n">
-        <v>781.0599999999999</v>
+        <v>784.3099999999999</v>
       </c>
     </row>
     <row r="204">
@@ -12891,7 +12891,7 @@
         </is>
       </c>
       <c r="M204" s="2" t="n">
-        <v>911.7</v>
+        <v>915.49</v>
       </c>
     </row>
     <row r="205">
@@ -12952,13 +12952,13 @@
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>4604.21</v>
+        <v>4623.35</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>3511-108-CM26</t>
+          <t>1461054-116-CM26</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -12978,17 +12978,17 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>61.981.040-6</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DEL ELQUI</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -13013,13 +13013,13 @@
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>1543.55</v>
+        <v>44593.84</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>1159-67-CM26</t>
+          <t>1057439-2381-CM26</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -13039,17 +13039,17 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>61.606.402-9</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -13059,12 +13059,12 @@
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>CARLOS ALBERTO VARGAS CASTILLO</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>13.940.082-8</t>
         </is>
       </c>
       <c r="K207" t="inlineStr"/>
@@ -13074,13 +13074,13 @@
         </is>
       </c>
       <c r="M207" s="2" t="n">
-        <v>2252.41</v>
+        <v>9554.030000000001</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>1289649-11-CM26</t>
+          <t>1159-67-CM26</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -13100,17 +13100,17 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>60.905.000-4</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>DIRECCIÓN REGIONAL DE COQUIMBO SERPAT</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -13120,12 +13120,12 @@
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>COMERCIAL IBL SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t>76.452.485-3</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K208" t="inlineStr"/>
@@ -13135,13 +13135,13 @@
         </is>
       </c>
       <c r="M208" s="2" t="n">
-        <v>1683.69</v>
+        <v>2271.52</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>1461054-116-CM26</t>
+          <t>3511-108-CM26</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -13161,17 +13161,17 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>61.981.040-6</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DEL ELQUI</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -13196,13 +13196,13 @@
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>44218.56</v>
+        <v>1556.65</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>1057439-2381-CM26</t>
+          <t>1289649-11-CM26</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -13227,12 +13227,12 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>61.606.402-9</t>
+          <t>60.905.000-4</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
+          <t>DIRECCIÓN REGIONAL DE COQUIMBO SERPAT</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -13242,12 +13242,12 @@
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO VARGAS CASTILLO</t>
+          <t>COMERCIAL IBL SPA</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t>13.940.082-8</t>
+          <t>76.452.485-3</t>
         </is>
       </c>
       <c r="K210" t="inlineStr"/>
@@ -13257,7 +13257,7 @@
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>9473.629999999999</v>
+        <v>1697.98</v>
       </c>
     </row>
     <row r="211">
@@ -13318,13 +13318,13 @@
         </is>
       </c>
       <c r="M211" s="2" t="n">
-        <v>3034.22</v>
+        <v>3071.56</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>3614-44-CM26</t>
+          <t>2708-229-CM26</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -13344,17 +13344,17 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>69.040.500-8</t>
+          <t>69.040.700-0</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VICUNA</t>
+          <t>MUNICIPALIDAD DE OVALLE</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -13379,13 +13379,13 @@
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>799.38</v>
+        <v>1023.35</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>2708-229-CM26</t>
+          <t>3614-44-CM26</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -13405,17 +13405,17 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>69.040.700-0</t>
+          <t>69.040.500-8</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE OVALLE</t>
+          <t>I MUNICIPALIDAD DE VICUNA</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -13440,7 +13440,7 @@
         </is>
       </c>
       <c r="M213" s="2" t="n">
-        <v>1009.91</v>
+        <v>810.02</v>
       </c>
     </row>
     <row r="214">
@@ -13501,7 +13501,7 @@
         </is>
       </c>
       <c r="M214" s="2" t="n">
-        <v>839.9</v>
+        <v>850.86</v>
       </c>
     </row>
     <row r="215">
@@ -13562,7 +13562,7 @@
         </is>
       </c>
       <c r="M215" s="2" t="n">
-        <v>2628.69</v>
+        <v>2693.38</v>
       </c>
     </row>
     <row r="216">
@@ -13623,13 +13623,13 @@
         </is>
       </c>
       <c r="M216" s="2" t="n">
-        <v>2738.86</v>
+        <v>2790.66</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>1057439-2721-CM26</t>
+          <t>3712-287-CM26</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -13649,17 +13649,17 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>61.606.402-9</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -13669,12 +13669,12 @@
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>ROLAND VORWERK Y COMPANIA LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t>78.178.530-k</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K217" t="inlineStr"/>
@@ -13684,13 +13684,13 @@
         </is>
       </c>
       <c r="M217" s="2" t="n">
-        <v>2114.28</v>
+        <v>1179.43</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>3712-287-CM26</t>
+          <t>1057439-2721-CM26</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -13710,17 +13710,17 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>61.606.402-9</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -13730,12 +13730,12 @@
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>ROLAND VORWERK Y COMPANIA LIMITADA</t>
         </is>
       </c>
       <c r="J218" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>78.178.530-k</t>
         </is>
       </c>
       <c r="K218" t="inlineStr"/>
@@ -13745,7 +13745,7 @@
         </is>
       </c>
       <c r="M218" s="2" t="n">
-        <v>1166.16</v>
+        <v>2138.33</v>
       </c>
     </row>
     <row r="219">
@@ -13806,7 +13806,7 @@
         </is>
       </c>
       <c r="M219" s="2" t="n">
-        <v>1716.97</v>
+        <v>1736.5</v>
       </c>
     </row>
     <row r="220">
@@ -13867,7 +13867,7 @@
         </is>
       </c>
       <c r="M220" s="2" t="n">
-        <v>927.26</v>
+        <v>935.61</v>
       </c>
     </row>
     <row r="221">
@@ -13932,13 +13932,13 @@
         </is>
       </c>
       <c r="M221" s="2" t="n">
-        <v>192487.36</v>
+        <v>193718.47</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>3712-301-CM26</t>
+          <t>5416-345-CM26</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -13963,12 +13963,12 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -13978,12 +13978,12 @@
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K222" t="inlineStr"/>
@@ -13993,13 +13993,13 @@
         </is>
       </c>
       <c r="M222" s="2" t="n">
-        <v>1451.38</v>
+        <v>951.66</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>1232820-55-CM26</t>
+          <t>3712-301-CM26</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -14019,17 +14019,17 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>65.080.284-5</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE TURISMO VICUNA</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
@@ -14054,13 +14054,13 @@
         </is>
       </c>
       <c r="M223" s="2" t="n">
-        <v>792.67</v>
+        <v>1455.94</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>5416-345-CM26</t>
+          <t>1232820-55-CM26</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -14080,17 +14080,17 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>65.080.284-5</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>CORPORACION MUNICIPAL DE TURISMO VICUNA</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
@@ -14100,12 +14100,12 @@
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J224" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K224" t="inlineStr"/>
@@ -14115,7 +14115,7 @@
         </is>
       </c>
       <c r="M224" s="2" t="n">
-        <v>948.67</v>
+        <v>795.16</v>
       </c>
     </row>
     <row r="225">
@@ -14176,7 +14176,7 @@
         </is>
       </c>
       <c r="M225" s="2" t="n">
-        <v>7394.97</v>
+        <v>7410.29</v>
       </c>
     </row>
     <row r="226">
@@ -14237,7 +14237,7 @@
         </is>
       </c>
       <c r="M226" s="2" t="n">
-        <v>963.78</v>
+        <v>965.78</v>
       </c>
     </row>
     <row r="227">
@@ -14298,7 +14298,7 @@
         </is>
       </c>
       <c r="M227" s="2" t="n">
-        <v>3220.14</v>
+        <v>3206.31</v>
       </c>
     </row>
     <row r="228">
@@ -14359,13 +14359,13 @@
         </is>
       </c>
       <c r="M228" s="2" t="n">
-        <v>1100.92</v>
+        <v>1094.32</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>3872-149-CM26</t>
+          <t>3511-117-CM26</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -14390,12 +14390,12 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>69.040.900-3</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUNITAQUI</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
@@ -14405,12 +14405,12 @@
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J229" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K229" t="inlineStr"/>
@@ -14420,13 +14420,13 @@
         </is>
       </c>
       <c r="M229" s="2" t="n">
-        <v>8323.780000000001</v>
+        <v>1041.94</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>3511-117-CM26</t>
+          <t>3872-149-CM26</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -14451,12 +14451,12 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>69.040.900-3</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>I MUNICIPALIDAD DE PUNITAQUI</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -14466,12 +14466,12 @@
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J230" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K230" t="inlineStr"/>
@@ -14481,13 +14481,13 @@
         </is>
       </c>
       <c r="M230" s="2" t="n">
-        <v>1050.9</v>
+        <v>8252.780000000001</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>2288-400-CM26</t>
+          <t>1057439-2988-CM26</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -14512,12 +14512,12 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>69.041.300-0</t>
+          <t>61.606.402-9</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CANELA</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
@@ -14527,12 +14527,12 @@
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>SURTI VENTAS S.A.</t>
+          <t>CARLOS ALBERTO VARGAS CASTILLO</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
         <is>
-          <t>76.462.500-5</t>
+          <t>13.940.082-8</t>
         </is>
       </c>
       <c r="K231" t="inlineStr"/>
@@ -14542,13 +14542,13 @@
         </is>
       </c>
       <c r="M231" s="2" t="n">
-        <v>998.16</v>
+        <v>9589.450000000001</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>1057439-2988-CM26</t>
+          <t>2288-400-CM26</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -14573,12 +14573,12 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>61.606.402-9</t>
+          <t>69.041.300-0</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
+          <t>I MUNICIPALIDAD DE CANELA</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
@@ -14588,12 +14588,12 @@
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO VARGAS CASTILLO</t>
+          <t>SURTI VENTAS S.A.</t>
         </is>
       </c>
       <c r="J232" t="inlineStr">
         <is>
-          <t>13.940.082-8</t>
+          <t>76.462.500-5</t>
         </is>
       </c>
       <c r="K232" t="inlineStr"/>
@@ -14603,7 +14603,7 @@
         </is>
       </c>
       <c r="M232" s="2" t="n">
-        <v>9538.09</v>
+        <v>1003.54</v>
       </c>
     </row>
     <row r="233">
@@ -14664,7 +14664,7 @@
         </is>
       </c>
       <c r="M233" s="2" t="n">
-        <v>2542.56</v>
+        <v>2556.25</v>
       </c>
     </row>
     <row r="234">
@@ -14725,7 +14725,7 @@
         </is>
       </c>
       <c r="M234" s="2" t="n">
-        <v>27264.1</v>
+        <v>27569.02</v>
       </c>
     </row>
     <row r="235">
@@ -14786,7 +14786,7 @@
         </is>
       </c>
       <c r="M235" s="2" t="n">
-        <v>12910.21</v>
+        <v>13054.6</v>
       </c>
     </row>
     <row r="236">
@@ -14847,7 +14847,7 @@
         </is>
       </c>
       <c r="M236" s="2" t="n">
-        <v>24062.35</v>
+        <v>24331.46</v>
       </c>
     </row>
     <row r="237">
@@ -14908,7 +14908,7 @@
         </is>
       </c>
       <c r="M237" s="2" t="n">
-        <v>811.22</v>
+        <v>817.37</v>
       </c>
     </row>
     <row r="238">
@@ -14969,7 +14969,7 @@
         </is>
       </c>
       <c r="M238" s="2" t="n">
-        <v>1523.61</v>
+        <v>1535.15</v>
       </c>
     </row>
     <row r="239">
@@ -15030,13 +15030,13 @@
         </is>
       </c>
       <c r="M239" s="2" t="n">
-        <v>1067.1</v>
+        <v>1071.14</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>1004823-47-CM26</t>
+          <t>2125-1018-CM26</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -15056,17 +15056,17 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>61.999.280-6</t>
+          <t>61.606.407-k</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACION TECNICA DE LA REGION DE COQUIMBO</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DR. HUMBERTO ELORZA CORTES</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
@@ -15076,12 +15076,12 @@
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J240" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K240" t="inlineStr"/>
@@ -15091,13 +15091,13 @@
         </is>
       </c>
       <c r="M240" s="2" t="n">
-        <v>3875.98</v>
+        <v>872.66</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>2125-1018-CM26</t>
+          <t>1004823-47-CM26</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -15117,17 +15117,17 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>61.606.407-k</t>
+          <t>61.999.280-6</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DR. HUMBERTO ELORZA CORTES</t>
+          <t>CENTRO DE FORMACION TECNICA DE LA REGION DE COQUIMBO</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
@@ -15137,12 +15137,12 @@
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J241" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K241" t="inlineStr"/>
@@ -15152,13 +15152,13 @@
         </is>
       </c>
       <c r="M241" s="2" t="n">
-        <v>874.87</v>
+        <v>3866.2</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>4295-53-CM26</t>
+          <t>4295-54-CM26</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -15198,12 +15198,12 @@
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>BARDANE SPA</t>
         </is>
       </c>
       <c r="J242" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.205.722-9</t>
         </is>
       </c>
       <c r="K242" t="inlineStr"/>
@@ -15213,13 +15213,13 @@
         </is>
       </c>
       <c r="M242" s="2" t="n">
-        <v>35422.32</v>
+        <v>9664.629999999999</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>4295-54-CM26</t>
+          <t>4295-53-CM26</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -15259,12 +15259,12 @@
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>BARDANE SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J243" t="inlineStr">
         <is>
-          <t>77.205.722-9</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K243" t="inlineStr"/>
@@ -15274,7 +15274,7 @@
         </is>
       </c>
       <c r="M243" s="2" t="n">
-        <v>9573.67</v>
+        <v>35758.86</v>
       </c>
     </row>
     <row r="244">
@@ -15335,7 +15335,7 @@
         </is>
       </c>
       <c r="M244" s="2" t="n">
-        <v>1194.35</v>
+        <v>1203.25</v>
       </c>
     </row>
     <row r="245">
@@ -15396,7 +15396,7 @@
         </is>
       </c>
       <c r="M245" s="2" t="n">
-        <v>2055.35</v>
+        <v>2070.66</v>
       </c>
     </row>
     <row r="246">
@@ -15457,7 +15457,7 @@
         </is>
       </c>
       <c r="M246" s="2" t="n">
-        <v>2503.74</v>
+        <v>2522.4</v>
       </c>
     </row>
     <row r="247">
@@ -15518,7 +15518,7 @@
         </is>
       </c>
       <c r="M247" s="2" t="n">
-        <v>1689.47</v>
+        <v>1702.06</v>
       </c>
     </row>
     <row r="248">
@@ -15579,7 +15579,7 @@
         </is>
       </c>
       <c r="M248" s="2" t="n">
-        <v>4594.32</v>
+        <v>4548.5</v>
       </c>
     </row>
     <row r="249">
@@ -15640,7 +15640,7 @@
         </is>
       </c>
       <c r="M249" s="2" t="n">
-        <v>2229.96</v>
+        <v>2205.7</v>
       </c>
     </row>
     <row r="250">
@@ -15701,13 +15701,13 @@
         </is>
       </c>
       <c r="M250" s="2" t="n">
-        <v>5802.6</v>
+        <v>5739.47</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>3509-197-CM26</t>
+          <t>3714-110-CM26</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -15727,17 +15727,17 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
@@ -15747,12 +15747,12 @@
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>SURTI VENTAS S.A.</t>
         </is>
       </c>
       <c r="J251" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>76.462.500-5</t>
         </is>
       </c>
       <c r="K251" t="inlineStr"/>
@@ -15762,13 +15762,13 @@
         </is>
       </c>
       <c r="M251" s="2" t="n">
-        <v>788.4</v>
+        <v>3748.11</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>3714-109-CM26</t>
+          <t>3509-197-CM26</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -15788,17 +15788,17 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
@@ -15808,12 +15808,12 @@
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t>SURTI VENTAS S.A.</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J252" t="inlineStr">
         <is>
-          <t>76.462.500-5</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K252" t="inlineStr"/>
@@ -15823,13 +15823,13 @@
         </is>
       </c>
       <c r="M252" s="2" t="n">
-        <v>873.64</v>
+        <v>786.61</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>3714-110-CM26</t>
+          <t>3714-109-CM26</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -15884,7 +15884,7 @@
         </is>
       </c>
       <c r="M253" s="2" t="n">
-        <v>3756.64</v>
+        <v>871.65</v>
       </c>
     </row>
     <row r="254">
@@ -15945,7 +15945,7 @@
         </is>
       </c>
       <c r="M254" s="2" t="n">
-        <v>1699.88</v>
+        <v>1708.23</v>
       </c>
     </row>
     <row r="255">
@@ -16006,7 +16006,7 @@
         </is>
       </c>
       <c r="M255" s="2" t="n">
-        <v>973.0599999999999</v>
+        <v>976.29</v>
       </c>
     </row>
     <row r="256">
@@ -16067,7 +16067,7 @@
         </is>
       </c>
       <c r="M256" s="2" t="n">
-        <v>1406.62</v>
+        <v>1411.29</v>
       </c>
     </row>
     <row r="257">
@@ -16128,7 +16128,7 @@
         </is>
       </c>
       <c r="M257" s="2" t="n">
-        <v>2173.99</v>
+        <v>2180.91</v>
       </c>
     </row>
     <row r="258">
@@ -16189,7 +16189,7 @@
         </is>
       </c>
       <c r="M258" s="2" t="n">
-        <v>2785.02</v>
+        <v>2793.88</v>
       </c>
     </row>
     <row r="259">
@@ -16250,7 +16250,7 @@
         </is>
       </c>
       <c r="M259" s="2" t="n">
-        <v>4275.33</v>
+        <v>4336.5</v>
       </c>
     </row>
     <row r="260">
@@ -16311,7 +16311,7 @@
         </is>
       </c>
       <c r="M260" s="2" t="n">
-        <v>1264.94</v>
+        <v>1279.78</v>
       </c>
     </row>
     <row r="261">
@@ -16372,7 +16372,7 @@
         </is>
       </c>
       <c r="M261" s="2" t="n">
-        <v>793.33</v>
+        <v>802.64</v>
       </c>
     </row>
     <row r="262">
@@ -16433,13 +16433,13 @@
         </is>
       </c>
       <c r="M262" s="2" t="n">
-        <v>1668.85</v>
+        <v>1688.42</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>3509-220-CM26</t>
+          <t>1574-78-CM26</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -16464,12 +16464,12 @@
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
@@ -16479,12 +16479,12 @@
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J263" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K263" t="inlineStr"/>
@@ -16494,13 +16494,13 @@
         </is>
       </c>
       <c r="M263" s="2" t="n">
-        <v>1775.65</v>
+        <v>2148.75</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>1574-77-CM26</t>
+          <t>3509-220-CM26</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -16525,12 +16525,12 @@
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
@@ -16540,12 +16540,12 @@
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J264" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K264" t="inlineStr"/>
@@ -16555,13 +16555,13 @@
         </is>
       </c>
       <c r="M264" s="2" t="n">
-        <v>4770.35</v>
+        <v>1805.68</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>1574-78-CM26</t>
+          <t>1574-77-CM26</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -16616,7 +16616,7 @@
         </is>
       </c>
       <c r="M265" s="2" t="n">
-        <v>2113.02</v>
+        <v>4851.02</v>
       </c>
     </row>
     <row r="266">
@@ -16677,7 +16677,7 @@
         </is>
       </c>
       <c r="M266" s="2" t="n">
-        <v>982.8099999999999</v>
+        <v>975.35</v>
       </c>
     </row>
     <row r="267">
@@ -16738,7 +16738,7 @@
         </is>
       </c>
       <c r="M267" s="2" t="n">
-        <v>22369.99</v>
+        <v>22200.28</v>
       </c>
     </row>
     <row r="268">
@@ -16799,7 +16799,7 @@
         </is>
       </c>
       <c r="M268" s="2" t="n">
-        <v>9585.629999999999</v>
+        <v>9423.68</v>
       </c>
     </row>
     <row r="269">
@@ -16860,7 +16860,7 @@
         </is>
       </c>
       <c r="M269" s="2" t="n">
-        <v>958.71</v>
+        <v>945.1</v>
       </c>
     </row>
     <row r="270">
@@ -16921,7 +16921,7 @@
         </is>
       </c>
       <c r="M270" s="2" t="n">
-        <v>4120.42</v>
+        <v>4063.8</v>
       </c>
     </row>
     <row r="271">
@@ -16982,13 +16982,13 @@
         </is>
       </c>
       <c r="M271" s="2" t="n">
-        <v>6369.32</v>
+        <v>6281.81</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>3884-263-CM26</t>
+          <t>697055-32-CM26</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -17008,17 +17008,17 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>69.040.600-4</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD PAIHUANO</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
@@ -17028,12 +17028,12 @@
       </c>
       <c r="I272" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J272" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K272" t="inlineStr"/>
@@ -17043,13 +17043,13 @@
         </is>
       </c>
       <c r="M272" s="2" t="n">
-        <v>2518.09</v>
+        <v>4898.03</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>1057439-3953-CM26</t>
+          <t>3884-263-CM26</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -17069,17 +17069,17 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>61.606.402-9</t>
+          <t>69.040.600-4</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
+          <t>I MUNICIPALIDAD PAIHUANO</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
@@ -17089,12 +17089,12 @@
       </c>
       <c r="I273" t="inlineStr">
         <is>
-          <t>ROLAND VORWERK Y COMPANIA LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J273" t="inlineStr">
         <is>
-          <t>78.178.530-k</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K273" t="inlineStr"/>
@@ -17104,13 +17104,13 @@
         </is>
       </c>
       <c r="M273" s="2" t="n">
-        <v>1596.67</v>
+        <v>2502.48</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>697055-32-CM26</t>
+          <t>1057439-3953-CM26</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -17135,12 +17135,12 @@
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>61.606.402-9</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
@@ -17150,12 +17150,12 @@
       </c>
       <c r="I274" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>ROLAND VORWERK Y COMPANIA LIMITADA</t>
         </is>
       </c>
       <c r="J274" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>78.178.530-k</t>
         </is>
       </c>
       <c r="K274" t="inlineStr"/>
@@ -17165,7 +17165,7 @@
         </is>
       </c>
       <c r="M274" s="2" t="n">
-        <v>4928.59</v>
+        <v>1586.78</v>
       </c>
     </row>
     <row r="275">
@@ -17226,7 +17226,7 @@
         </is>
       </c>
       <c r="M275" s="2" t="n">
-        <v>6388.26</v>
+        <v>6348.66</v>
       </c>
     </row>
     <row r="276">
@@ -17287,7 +17287,7 @@
         </is>
       </c>
       <c r="M276" s="2" t="n">
-        <v>792.8099999999999</v>
+        <v>796.41</v>
       </c>
     </row>
     <row r="277">
@@ -17348,13 +17348,13 @@
         </is>
       </c>
       <c r="M277" s="2" t="n">
-        <v>1888.49</v>
+        <v>1924.39</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>3712-413-CM26</t>
+          <t>3712-412-CM26</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -17409,13 +17409,13 @@
         </is>
       </c>
       <c r="M278" s="2" t="n">
-        <v>1279.43</v>
+        <v>1131.91</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>2992-193-CM26</t>
+          <t>3712-413-CM26</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -17435,17 +17435,17 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>69.040.800-7</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MONTEPATRIA</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
@@ -17455,12 +17455,12 @@
       </c>
       <c r="I279" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J279" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>77.346.435-9</t>
         </is>
       </c>
       <c r="K279" t="inlineStr"/>
@@ -17470,13 +17470,13 @@
         </is>
       </c>
       <c r="M279" s="2" t="n">
-        <v>1928.66</v>
+        <v>1308.28</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>3712-412-CM26</t>
+          <t>2992-193-CM26</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -17496,17 +17496,17 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>69.040.800-7</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>I MUNICIPALIDAD DE MONTEPATRIA</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
@@ -17516,12 +17516,12 @@
       </c>
       <c r="I280" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J280" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K280" t="inlineStr"/>
@@ -17531,13 +17531,13 @@
         </is>
       </c>
       <c r="M280" s="2" t="n">
-        <v>1106.94</v>
+        <v>1972.16</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>2125-1292-CM26</t>
+          <t>2992-211-CM26</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -17557,17 +17557,17 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>61.606.407-k</t>
+          <t>69.040.800-7</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DR. HUMBERTO ELORZA CORTES</t>
+          <t>I MUNICIPALIDAD DE MONTEPATRIA</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
@@ -17577,12 +17577,12 @@
       </c>
       <c r="I281" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J281" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K281" t="inlineStr"/>
@@ -17592,13 +17592,13 @@
         </is>
       </c>
       <c r="M281" s="2" t="n">
-        <v>1343.69</v>
+        <v>5014.22</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>2992-211-CM26</t>
+          <t>2125-1292-CM26</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -17618,17 +17618,17 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>69.040.800-7</t>
+          <t>61.606.407-k</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MONTEPATRIA</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DR. HUMBERTO ELORZA CORTES</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
@@ -17638,12 +17638,12 @@
       </c>
       <c r="I282" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J282" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K282" t="inlineStr"/>
@@ -17653,13 +17653,13 @@
         </is>
       </c>
       <c r="M282" s="2" t="n">
-        <v>4979.84</v>
+        <v>1352.97</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>1079505-335-CM26</t>
+          <t>2711-156-CM26</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -17684,12 +17684,12 @@
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>60.505.206-1</t>
+          <t>69.040.700-0</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IV ZONA</t>
+          <t>MUNICIPALIDAD DE OVALLE</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
@@ -17699,12 +17699,12 @@
       </c>
       <c r="I283" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J283" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K283" t="inlineStr"/>
@@ -17714,13 +17714,13 @@
         </is>
       </c>
       <c r="M283" s="2" t="n">
-        <v>1116.83</v>
+        <v>865.65</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>2711-156-CM26</t>
+          <t>1079505-335-CM26</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -17745,12 +17745,12 @@
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>69.040.700-0</t>
+          <t>60.505.206-1</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE OVALLE</t>
+          <t>SECCIÓN COMPRAS IV ZONA</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
@@ -17760,12 +17760,12 @@
       </c>
       <c r="I284" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J284" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K284" t="inlineStr"/>
@@ -17775,7 +17775,7 @@
         </is>
       </c>
       <c r="M284" s="2" t="n">
-        <v>867.95</v>
+        <v>1113.87</v>
       </c>
     </row>
     <row r="285">
@@ -17836,7 +17836,7 @@
         </is>
       </c>
       <c r="M285" s="2" t="n">
-        <v>2075.83</v>
+        <v>2048.18</v>
       </c>
     </row>
     <row r="286">
@@ -17897,7 +17897,7 @@
         </is>
       </c>
       <c r="M286" s="2" t="n">
-        <v>2342.13</v>
+        <v>2310.93</v>
       </c>
     </row>
     <row r="287">
@@ -17958,13 +17958,13 @@
         </is>
       </c>
       <c r="M287" s="2" t="n">
-        <v>4116.71</v>
+        <v>4061.88</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>1346282-289-CM26</t>
+          <t>1962-370-CM26</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -17989,12 +17989,12 @@
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>61.004.012-8</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>Gendarmería de Chile - Dirección Regional de Coquimbo</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
@@ -18004,12 +18004,12 @@
       </c>
       <c r="I288" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J288" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K288" t="inlineStr"/>
@@ -18019,13 +18019,13 @@
         </is>
       </c>
       <c r="M288" s="2" t="n">
-        <v>1028.36</v>
+        <v>1801.34</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>1574-99-CM26</t>
+          <t>1574-103-CM26</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -18045,7 +18045,7 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
@@ -18065,12 +18065,12 @@
       </c>
       <c r="I289" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>IMPORTADORA Y COMERCIALIZADORA JMMB SPA</t>
         </is>
       </c>
       <c r="J289" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.461.733-7</t>
         </is>
       </c>
       <c r="K289" t="inlineStr"/>
@@ -18080,13 +18080,13 @@
         </is>
       </c>
       <c r="M289" s="2" t="n">
-        <v>38878.96</v>
+        <v>1584.15</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>1574-100-CM26</t>
+          <t>1574-102-CM26</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -18106,7 +18106,7 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
@@ -18126,12 +18126,12 @@
       </c>
       <c r="I290" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>IMPORTADORA Y COMERCIALIZADORA JMMB SPA</t>
         </is>
       </c>
       <c r="J290" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.461.733-7</t>
         </is>
       </c>
       <c r="K290" t="inlineStr"/>
@@ -18141,13 +18141,13 @@
         </is>
       </c>
       <c r="M290" s="2" t="n">
-        <v>28508.24</v>
+        <v>3120.97</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>1574-102-CM26</t>
+          <t>1352-56-CM26</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -18167,17 +18167,17 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>61.002.010-0</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>Servicio de Registro Civil e Identificación</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
@@ -18187,12 +18187,12 @@
       </c>
       <c r="I291" t="inlineStr">
         <is>
-          <t>IMPORTADORA Y COMERCIALIZADORA JMMB SPA</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J291" t="inlineStr">
         <is>
-          <t>77.461.733-7</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K291" t="inlineStr"/>
@@ -18202,13 +18202,13 @@
         </is>
       </c>
       <c r="M291" s="2" t="n">
-        <v>3183.28</v>
+        <v>1115.85</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>1574-103-CM26</t>
+          <t>1574-99-CM26</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -18228,7 +18228,7 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
@@ -18248,12 +18248,12 @@
       </c>
       <c r="I292" t="inlineStr">
         <is>
-          <t>IMPORTADORA Y COMERCIALIZADORA JMMB SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J292" t="inlineStr">
         <is>
-          <t>77.461.733-7</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K292" t="inlineStr"/>
@@ -18263,13 +18263,13 @@
         </is>
       </c>
       <c r="M292" s="2" t="n">
-        <v>1615.78</v>
+        <v>38117.95</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>1352-56-CM26</t>
+          <t>1346282-289-CM26</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -18289,17 +18289,17 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>61.002.010-0</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>Servicio de Registro Civil e Identificación</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
@@ -18309,12 +18309,12 @@
       </c>
       <c r="I293" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J293" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K293" t="inlineStr"/>
@@ -18324,13 +18324,13 @@
         </is>
       </c>
       <c r="M293" s="2" t="n">
-        <v>1138.13</v>
+        <v>1008.24</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>1962-370-CM26</t>
+          <t>1574-100-CM26</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -18350,17 +18350,17 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>61.004.012-8</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>Gendarmería de Chile - Dirección Regional de Coquimbo</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
@@ -18370,12 +18370,12 @@
       </c>
       <c r="I294" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J294" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K294" t="inlineStr"/>
@@ -18385,13 +18385,13 @@
         </is>
       </c>
       <c r="M294" s="2" t="n">
-        <v>1837.31</v>
+        <v>27950.22</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>1159-175-CM26</t>
+          <t>2992-230-CM26</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -18416,12 +18416,12 @@
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>69.040.800-7</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>I MUNICIPALIDAD DE MONTEPATRIA</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
@@ -18431,12 +18431,12 @@
       </c>
       <c r="I295" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J295" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K295" t="inlineStr"/>
@@ -18446,13 +18446,13 @@
         </is>
       </c>
       <c r="M295" s="2" t="n">
-        <v>1746.54</v>
+        <v>4947.34</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>1159-174-CM26</t>
+          <t>2992-233-CM26</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -18477,12 +18477,12 @@
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>69.040.800-7</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>I MUNICIPALIDAD DE MONTEPATRIA</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
@@ -18492,12 +18492,12 @@
       </c>
       <c r="I296" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J296" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K296" t="inlineStr"/>
@@ -18507,13 +18507,13 @@
         </is>
       </c>
       <c r="M296" s="2" t="n">
-        <v>2807.29</v>
+        <v>2950.02</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>2288-580-CM26</t>
+          <t>1159-174-CM26</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -18533,17 +18533,17 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>69.041.300-0</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CANELA</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
@@ -18553,12 +18553,12 @@
       </c>
       <c r="I297" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J297" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.346.435-9</t>
         </is>
       </c>
       <c r="K297" t="inlineStr"/>
@@ -18568,13 +18568,13 @@
         </is>
       </c>
       <c r="M297" s="2" t="n">
-        <v>2197.69</v>
+        <v>2765.7</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>2992-230-CM26</t>
+          <t>2288-580-CM26</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -18594,17 +18594,17 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>69.040.800-7</t>
+          <t>69.041.300-0</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MONTEPATRIA</t>
+          <t>I MUNICIPALIDAD DE CANELA</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
@@ -18614,12 +18614,12 @@
       </c>
       <c r="I298" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J298" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K298" t="inlineStr"/>
@@ -18629,13 +18629,13 @@
         </is>
       </c>
       <c r="M298" s="2" t="n">
-        <v>5021.75</v>
+        <v>2165.13</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>2992-233-CM26</t>
+          <t>1159-175-CM26</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -18660,12 +18660,12 @@
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>69.040.800-7</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MONTEPATRIA</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
@@ -18675,12 +18675,12 @@
       </c>
       <c r="I299" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J299" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K299" t="inlineStr"/>
@@ -18690,13 +18690,13 @@
         </is>
       </c>
       <c r="M299" s="2" t="n">
-        <v>2994.38</v>
+        <v>1720.66</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>2992-203-CM26</t>
+          <t>1124-28-CM26</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -18721,12 +18721,12 @@
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>69.040.800-7</t>
+          <t>61.307.000-1</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MONTEPATRIA</t>
+          <t>INSTITUTO DE DESARROLLO AGROPECUARIO</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
@@ -18736,12 +18736,12 @@
       </c>
       <c r="I300" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>ANTALIS CHILE LIMITADA</t>
         </is>
       </c>
       <c r="J300" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>77.305.910-1</t>
         </is>
       </c>
       <c r="K300" t="inlineStr"/>
@@ -18751,13 +18751,13 @@
         </is>
       </c>
       <c r="M300" s="2" t="n">
-        <v>7284.58</v>
+        <v>1395.01</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>1124-28-CM26</t>
+          <t>2992-203-CM26</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -18782,12 +18782,12 @@
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>61.307.000-1</t>
+          <t>69.040.800-7</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>INSTITUTO DE DESARROLLO AGROPECUARIO</t>
+          <t>I MUNICIPALIDAD DE MONTEPATRIA</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
@@ -18797,12 +18797,12 @@
       </c>
       <c r="I301" t="inlineStr">
         <is>
-          <t>ANTALIS CHILE LIMITADA</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J301" t="inlineStr">
         <is>
-          <t>77.305.910-1</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K301" t="inlineStr"/>
@@ -18812,13 +18812,13 @@
         </is>
       </c>
       <c r="M301" s="2" t="n">
-        <v>1424.28</v>
+        <v>7134.87</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>2992-225-CM26</t>
+          <t>5416-661-CM26</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -18838,17 +18838,17 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>69.040.800-7</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MONTEPATRIA</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
@@ -18873,7 +18873,7 @@
         </is>
       </c>
       <c r="M302" s="2" t="n">
-        <v>3859.33</v>
+        <v>1406.77</v>
       </c>
     </row>
     <row r="303">
@@ -18934,13 +18934,13 @@
         </is>
       </c>
       <c r="M303" s="2" t="n">
-        <v>5046.91</v>
+        <v>5094.85</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>5416-661-CM26</t>
+          <t>2992-225-CM26</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -18960,17 +18960,17 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>69.040.800-7</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>I MUNICIPALIDAD DE MONTEPATRIA</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
@@ -18995,7 +18995,7 @@
         </is>
       </c>
       <c r="M304" s="2" t="n">
-        <v>1393.53</v>
+        <v>3895.99</v>
       </c>
     </row>
     <row r="305">
@@ -19060,7 +19060,7 @@
         </is>
       </c>
       <c r="M305" s="2" t="n">
-        <v>45020.31</v>
+        <v>45196.05</v>
       </c>
     </row>
     <row r="306">
@@ -19121,7 +19121,7 @@
         </is>
       </c>
       <c r="M306" s="2" t="n">
-        <v>967.0700000000001</v>
+        <v>976.8</v>
       </c>
     </row>
     <row r="307">
@@ -19182,7 +19182,7 @@
         </is>
       </c>
       <c r="M307" s="2" t="n">
-        <v>4878.17</v>
+        <v>4927.02</v>
       </c>
     </row>
     <row r="308">
@@ -19243,7 +19243,7 @@
         </is>
       </c>
       <c r="M308" s="2" t="n">
-        <v>917.1</v>
+        <v>921.77</v>
       </c>
     </row>
     <row r="309">
@@ -19304,7 +19304,7 @@
         </is>
       </c>
       <c r="M309" s="2" t="n">
-        <v>2863.06</v>
+        <v>2877.65</v>
       </c>
     </row>
     <row r="310">
@@ -19365,7 +19365,7 @@
         </is>
       </c>
       <c r="M310" s="2" t="n">
-        <v>5765.48</v>
+        <v>5787.93</v>
       </c>
     </row>
     <row r="311">
@@ -19426,7 +19426,7 @@
         </is>
       </c>
       <c r="M311" s="2" t="n">
-        <v>1509.48</v>
+        <v>1501.84</v>
       </c>
     </row>
     <row r="312">
@@ -19487,7 +19487,7 @@
         </is>
       </c>
       <c r="M312" s="2" t="n">
-        <v>3392.44</v>
+        <v>3414.56</v>
       </c>
     </row>
     <row r="313">
@@ -19548,13 +19548,13 @@
         </is>
       </c>
       <c r="M313" s="2" t="n">
-        <v>2182.59</v>
+        <v>2187.59</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>1057439-4523-CM26</t>
+          <t>1461054-241-CM26</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -19579,12 +19579,12 @@
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>61.606.402-9</t>
+          <t>61.981.040-6</t>
         </is>
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DEL ELQUI</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
@@ -19594,12 +19594,12 @@
       </c>
       <c r="I314" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO VARGAS CASTILLO</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J314" t="inlineStr">
         <is>
-          <t>13.940.082-8</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K314" t="inlineStr"/>
@@ -19609,13 +19609,13 @@
         </is>
       </c>
       <c r="M314" s="2" t="n">
-        <v>8081.52</v>
+        <v>4174.98</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>1057439-4554-CM26</t>
+          <t>1057439-4523-CM26</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -19655,12 +19655,12 @@
       </c>
       <c r="I315" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>CARLOS ALBERTO VARGAS CASTILLO</t>
         </is>
       </c>
       <c r="J315" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>13.940.082-8</t>
         </is>
       </c>
       <c r="K315" t="inlineStr"/>
@@ -19670,13 +19670,13 @@
         </is>
       </c>
       <c r="M315" s="2" t="n">
-        <v>2761.61</v>
+        <v>8135.62</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>1461054-241-CM26</t>
+          <t>1057439-4554-CM26</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -19701,12 +19701,12 @@
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>61.981.040-6</t>
+          <t>61.606.402-9</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DEL ELQUI</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
         </is>
       </c>
       <c r="H316" t="inlineStr">
@@ -19716,12 +19716,12 @@
       </c>
       <c r="I316" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J316" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K316" t="inlineStr"/>
@@ -19731,7 +19731,7 @@
         </is>
       </c>
       <c r="M316" s="2" t="n">
-        <v>4147.22</v>
+        <v>2780.09</v>
       </c>
     </row>
     <row r="317">
@@ -19792,7 +19792,7 @@
         </is>
       </c>
       <c r="M317" s="2" t="n">
-        <v>962.13</v>
+        <v>956.5599999999999</v>
       </c>
     </row>
     <row r="318">
@@ -19853,7 +19853,7 @@
         </is>
       </c>
       <c r="M318" s="2" t="n">
-        <v>786.5</v>
+        <v>773.8099999999999</v>
       </c>
     </row>
     <row r="319">
@@ -19914,7 +19914,251 @@
         </is>
       </c>
       <c r="M319" s="2" t="n">
-        <v>6505.3</v>
+        <v>6469.24</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>2711-203-CM26</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>69.040.700-0</t>
+        </is>
+      </c>
+      <c r="G320" t="inlineStr">
+        <is>
+          <t>MUNICIPALIDAD DE OVALLE</t>
+        </is>
+      </c>
+      <c r="H320" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I320" t="inlineStr">
+        <is>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+        </is>
+      </c>
+      <c r="J320" t="inlineStr">
+        <is>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K320" t="inlineStr"/>
+      <c r="L320" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M320" s="2" t="n">
+        <v>4386.07</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>2711-204-CM26</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>69.040.700-0</t>
+        </is>
+      </c>
+      <c r="G321" t="inlineStr">
+        <is>
+          <t>MUNICIPALIDAD DE OVALLE</t>
+        </is>
+      </c>
+      <c r="H321" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I321" t="inlineStr">
+        <is>
+          <t>CASTILLA Y ARAGON SPA</t>
+        </is>
+      </c>
+      <c r="J321" t="inlineStr">
+        <is>
+          <t>96.989.530-7</t>
+        </is>
+      </c>
+      <c r="K321" t="inlineStr"/>
+      <c r="L321" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M321" s="2" t="n">
+        <v>2345.64</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>1962-532-CM26</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>61.004.012-8</t>
+        </is>
+      </c>
+      <c r="G322" t="inlineStr">
+        <is>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+        </is>
+      </c>
+      <c r="H322" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I322" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA CUARENTA Y UNO SPA</t>
+        </is>
+      </c>
+      <c r="J322" t="inlineStr">
+        <is>
+          <t>78.085.401-4</t>
+        </is>
+      </c>
+      <c r="K322" t="inlineStr"/>
+      <c r="L322" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M322" s="2" t="n">
+        <v>876.1</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>1057439-5257-CM26</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>61.606.402-9</t>
+        </is>
+      </c>
+      <c r="G323" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
+        </is>
+      </c>
+      <c r="H323" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I323" t="inlineStr">
+        <is>
+          <t>ROLAND VORWERK Y COMPANIA LIMITADA</t>
+        </is>
+      </c>
+      <c r="J323" t="inlineStr">
+        <is>
+          <t>78.178.530-k</t>
+        </is>
+      </c>
+      <c r="K323" t="inlineStr"/>
+      <c r="L323" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M323" s="2" t="n">
+        <v>2843.29</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/articulos-de-escritorio-y-papeleria/coquimbo.xlsx
+++ b/docs/oc-regiones/articulos-de-escritorio-y-papeleria/coquimbo.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M663"/>
+  <dimension ref="A1:M667"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -13833,7 +13833,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>1574-314-CM25</t>
+          <t>1574-313-CM25</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -13888,13 +13888,13 @@
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>795.89</v>
+        <v>1224.69</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>3511-389-CM25</t>
+          <t>1574-314-CM25</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -13914,17 +13914,17 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -13934,26 +13934,22 @@
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>INVERSIONES Y RENTAS AMINORTE LIMITADA</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
-        </is>
-      </c>
-      <c r="K210" t="inlineStr">
-        <is>
-          <t>Coquimbo</t>
-        </is>
-      </c>
+          <t>76.432.149-9</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr"/>
       <c r="L210" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>756.78</v>
+        <v>795.89</v>
       </c>
     </row>
     <row r="211">
@@ -14085,7 +14081,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>1574-313-CM25</t>
+          <t>3511-389-CM25</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -14105,17 +14101,17 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -14125,22 +14121,26 @@
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>INVERSIONES Y RENTAS AMINORTE LIMITADA</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J213" t="inlineStr">
         <is>
-          <t>76.432.149-9</t>
-        </is>
-      </c>
-      <c r="K213" t="inlineStr"/>
+          <t>77.012.870-6</t>
+        </is>
+      </c>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L213" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M213" s="2" t="n">
-        <v>1224.69</v>
+        <v>756.78</v>
       </c>
     </row>
     <row r="214">
@@ -15942,7 +15942,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>1159-210-CM25</t>
+          <t>1159-209-CM25</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -16001,13 +16001,13 @@
         </is>
       </c>
       <c r="M242" s="2" t="n">
-        <v>4076.94</v>
+        <v>3455.74</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>1159-209-CM25</t>
+          <t>1159-210-CM25</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -16066,13 +16066,13 @@
         </is>
       </c>
       <c r="M243" s="2" t="n">
-        <v>3455.74</v>
+        <v>4076.94</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>3884-557-CM25</t>
+          <t>3884-556-CM25</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -16112,32 +16112,28 @@
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>IMPORTADORA  Y DISTRIBUIDORA BLANMAR SPA</t>
         </is>
       </c>
       <c r="J244" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
-        </is>
-      </c>
-      <c r="K244" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.993.355-7</t>
+        </is>
+      </c>
+      <c r="K244" t="inlineStr"/>
       <c r="L244" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M244" s="2" t="n">
-        <v>1183.64</v>
+        <v>2253.67</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>5416-1086-CM25</t>
+          <t>3884-557-CM25</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -16162,12 +16158,12 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>69.040.600-4</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>I MUNICIPALIDAD PAIHUANO</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
@@ -16177,17 +16173,17 @@
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J245" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K245" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L245" t="inlineStr">
@@ -16196,13 +16192,13 @@
         </is>
       </c>
       <c r="M245" s="2" t="n">
-        <v>1214.58</v>
+        <v>1183.64</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>3884-556-CM25</t>
+          <t>5416-1086-CM25</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -16227,12 +16223,12 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>69.040.600-4</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD PAIHUANO</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
@@ -16242,22 +16238,26 @@
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t>IMPORTADORA  Y DISTRIBUIDORA BLANMAR SPA</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J246" t="inlineStr">
         <is>
-          <t>76.993.355-7</t>
-        </is>
-      </c>
-      <c r="K246" t="inlineStr"/>
+          <t>77.012.870-6</t>
+        </is>
+      </c>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L246" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M246" s="2" t="n">
-        <v>2253.67</v>
+        <v>1214.58</v>
       </c>
     </row>
     <row r="247">
@@ -16836,7 +16836,7 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>1057438-295-CM25</t>
+          <t>707418-176-CM25</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -16861,12 +16861,12 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>61.606.401-0</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL VICUNA</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
@@ -16876,17 +16876,17 @@
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J256" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K256" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L256" t="inlineStr">
@@ -16895,13 +16895,13 @@
         </is>
       </c>
       <c r="M256" s="2" t="n">
-        <v>1402.13</v>
+        <v>6454.19</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>707418-174-CM25</t>
+          <t>1057438-295-CM25</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -16926,12 +16926,12 @@
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.606.401-0</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL VICUNA</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
@@ -16941,17 +16941,17 @@
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SAN JERONIMO SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J257" t="inlineStr">
         <is>
-          <t>77.610.393-4</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K257" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L257" t="inlineStr">
@@ -16960,13 +16960,13 @@
         </is>
       </c>
       <c r="M257" s="2" t="n">
-        <v>2262.26</v>
+        <v>1402.13</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>707418-176-CM25</t>
+          <t>707418-174-CM25</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -17006,12 +17006,12 @@
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIALIZADORA SAN JERONIMO SPA</t>
         </is>
       </c>
       <c r="J258" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.610.393-4</t>
         </is>
       </c>
       <c r="K258" t="inlineStr">
@@ -17025,7 +17025,7 @@
         </is>
       </c>
       <c r="M258" s="2" t="n">
-        <v>6454.19</v>
+        <v>2262.26</v>
       </c>
     </row>
     <row r="259">
@@ -24243,7 +24243,7 @@
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F371" t="inlineStr">
@@ -25064,7 +25064,7 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>2992-12-CM26</t>
+          <t>3712-35-CM26</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
@@ -25089,12 +25089,12 @@
       </c>
       <c r="F384" t="inlineStr">
         <is>
-          <t>69.040.800-7</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G384" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MONTEPATRIA</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H384" t="inlineStr">
@@ -25104,17 +25104,17 @@
       </c>
       <c r="I384" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>OPEN SANTIAGO SPA</t>
         </is>
       </c>
       <c r="J384" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>78.069.505-6</t>
         </is>
       </c>
       <c r="K384" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L384" t="inlineStr">
@@ -25123,7 +25123,7 @@
         </is>
       </c>
       <c r="M384" s="2" t="n">
-        <v>9578.959999999999</v>
+        <v>1013.86</v>
       </c>
     </row>
     <row r="385">
@@ -25259,7 +25259,7 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>3712-35-CM26</t>
+          <t>2992-12-CM26</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
@@ -25284,12 +25284,12 @@
       </c>
       <c r="F387" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>69.040.800-7</t>
         </is>
       </c>
       <c r="G387" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>I MUNICIPALIDAD DE MONTEPATRIA</t>
         </is>
       </c>
       <c r="H387" t="inlineStr">
@@ -25299,17 +25299,17 @@
       </c>
       <c r="I387" t="inlineStr">
         <is>
-          <t>OPEN SANTIAGO SPA</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J387" t="inlineStr">
         <is>
-          <t>78.069.505-6</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K387" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="L387" t="inlineStr">
@@ -25318,7 +25318,7 @@
         </is>
       </c>
       <c r="M387" s="2" t="n">
-        <v>1013.86</v>
+        <v>9578.959999999999</v>
       </c>
     </row>
     <row r="388">
@@ -25389,7 +25389,7 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>3712-56-CM26</t>
+          <t>3615-5-CM26</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
@@ -25414,12 +25414,12 @@
       </c>
       <c r="F389" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>69.041.100-8</t>
         </is>
       </c>
       <c r="G389" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>ILUSTRE MINICIPALIDAD DE COMBARBALA</t>
         </is>
       </c>
       <c r="H389" t="inlineStr">
@@ -25448,13 +25448,13 @@
         </is>
       </c>
       <c r="M389" s="2" t="n">
-        <v>1130.94</v>
+        <v>5504.15</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>3615-5-CM26</t>
+          <t>2146-34-CM26</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
@@ -25479,12 +25479,12 @@
       </c>
       <c r="F390" t="inlineStr">
         <is>
-          <t>69.041.100-8</t>
+          <t>61.606.405-3</t>
         </is>
       </c>
       <c r="G390" t="inlineStr">
         <is>
-          <t>ILUSTRE MINICIPALIDAD DE COMBARBALA</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE ANDACOLLO</t>
         </is>
       </c>
       <c r="H390" t="inlineStr">
@@ -25513,13 +25513,13 @@
         </is>
       </c>
       <c r="M390" s="2" t="n">
-        <v>5504.15</v>
+        <v>2810.21</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>2146-34-CM26</t>
+          <t>3712-56-CM26</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
@@ -25544,12 +25544,12 @@
       </c>
       <c r="F391" t="inlineStr">
         <is>
-          <t>61.606.405-3</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G391" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE ANDACOLLO</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H391" t="inlineStr">
@@ -25578,7 +25578,7 @@
         </is>
       </c>
       <c r="M391" s="2" t="n">
-        <v>2810.21</v>
+        <v>1130.94</v>
       </c>
     </row>
     <row r="392">
@@ -25799,7 +25799,7 @@
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F395" t="inlineStr">
@@ -26750,7 +26750,7 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>1346282-67-CM26</t>
+          <t>1057439-1118-CM26</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
@@ -26775,12 +26775,12 @@
       </c>
       <c r="F410" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>61.606.402-9</t>
         </is>
       </c>
       <c r="G410" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
         </is>
       </c>
       <c r="H410" t="inlineStr">
@@ -26790,32 +26790,28 @@
       </c>
       <c r="I410" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>CARLOS ALBERTO VARGAS CASTILLO</t>
         </is>
       </c>
       <c r="J410" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
-        </is>
-      </c>
-      <c r="K410" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>13.940.082-8</t>
+        </is>
+      </c>
+      <c r="K410" t="inlineStr"/>
       <c r="L410" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M410" s="2" t="n">
-        <v>1045.73</v>
+        <v>10755.7</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>1057439-1118-CM26</t>
+          <t>1346282-68-CM26</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
@@ -26840,12 +26836,12 @@
       </c>
       <c r="F411" t="inlineStr">
         <is>
-          <t>61.606.402-9</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G411" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H411" t="inlineStr">
@@ -26855,28 +26851,32 @@
       </c>
       <c r="I411" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO VARGAS CASTILLO</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J411" t="inlineStr">
         <is>
-          <t>13.940.082-8</t>
-        </is>
-      </c>
-      <c r="K411" t="inlineStr"/>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K411" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L411" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M411" s="2" t="n">
-        <v>10755.7</v>
+        <v>1935.97</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>1346282-68-CM26</t>
+          <t>1346282-67-CM26</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
@@ -26935,7 +26935,7 @@
         </is>
       </c>
       <c r="M412" s="2" t="n">
-        <v>1935.97</v>
+        <v>1045.73</v>
       </c>
     </row>
     <row r="413">
@@ -27327,7 +27327,7 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>2992-64-CM26</t>
+          <t>2992-66-CM26</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
@@ -27386,13 +27386,13 @@
         </is>
       </c>
       <c r="M419" s="2" t="n">
-        <v>7998.11</v>
+        <v>2116.12</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>2992-66-CM26</t>
+          <t>2992-64-CM26</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
@@ -27451,7 +27451,7 @@
         </is>
       </c>
       <c r="M420" s="2" t="n">
-        <v>2116.12</v>
+        <v>7998.11</v>
       </c>
     </row>
     <row r="421">
@@ -27644,7 +27644,7 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>1079505-61-CM26</t>
+          <t>3712-92-CM26</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
@@ -27669,12 +27669,12 @@
       </c>
       <c r="F424" t="inlineStr">
         <is>
-          <t>60.505.206-1</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G424" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H424" t="inlineStr">
@@ -27684,28 +27684,32 @@
       </c>
       <c r="I424" t="inlineStr">
         <is>
-          <t>MALMO S.A.</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J424" t="inlineStr">
         <is>
-          <t>76.195.558-6</t>
-        </is>
-      </c>
-      <c r="K424" t="inlineStr"/>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K424" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L424" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M424" s="2" t="n">
-        <v>53681.83</v>
+        <v>1059.54</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>3712-92-CM26</t>
+          <t>1079505-61-CM26</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
@@ -27730,12 +27734,12 @@
       </c>
       <c r="F425" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>60.505.206-1</t>
         </is>
       </c>
       <c r="G425" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H425" t="inlineStr">
@@ -27745,26 +27749,22 @@
       </c>
       <c r="I425" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>MALMO S.A.</t>
         </is>
       </c>
       <c r="J425" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
-        </is>
-      </c>
-      <c r="K425" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.195.558-6</t>
+        </is>
+      </c>
+      <c r="K425" t="inlineStr"/>
       <c r="L425" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M425" s="2" t="n">
-        <v>1059.54</v>
+        <v>53681.83</v>
       </c>
     </row>
     <row r="426">
@@ -27835,7 +27835,7 @@
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>1395-111-CM26</t>
+          <t>2145-204-CM26</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
@@ -27860,12 +27860,12 @@
       </c>
       <c r="F427" t="inlineStr">
         <is>
-          <t>61.606.400-2</t>
+          <t>61.606.409-6</t>
         </is>
       </c>
       <c r="G427" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE LOS VILOS</t>
         </is>
       </c>
       <c r="H427" t="inlineStr">
@@ -27875,17 +27875,17 @@
       </c>
       <c r="I427" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>BAILEY GROUP SPA</t>
         </is>
       </c>
       <c r="J427" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>77.638.992-7</t>
         </is>
       </c>
       <c r="K427" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L427" t="inlineStr">
@@ -27894,13 +27894,13 @@
         </is>
       </c>
       <c r="M427" s="2" t="n">
-        <v>8621.469999999999</v>
+        <v>2356.09</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>2145-204-CM26</t>
+          <t>1395-111-CM26</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
@@ -27925,12 +27925,12 @@
       </c>
       <c r="F428" t="inlineStr">
         <is>
-          <t>61.606.409-6</t>
+          <t>61.606.400-2</t>
         </is>
       </c>
       <c r="G428" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE LOS VILOS</t>
+          <t>SERVICIO DE SALUD COQUIMBO</t>
         </is>
       </c>
       <c r="H428" t="inlineStr">
@@ -27940,17 +27940,17 @@
       </c>
       <c r="I428" t="inlineStr">
         <is>
-          <t>BAILEY GROUP SPA</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J428" t="inlineStr">
         <is>
-          <t>77.638.992-7</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K428" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="L428" t="inlineStr">
@@ -27959,7 +27959,7 @@
         </is>
       </c>
       <c r="M428" s="2" t="n">
-        <v>2356.09</v>
+        <v>8621.469999999999</v>
       </c>
     </row>
     <row r="429">
@@ -28030,7 +28030,7 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>3712-208-CM26</t>
+          <t>3712-165-CM26</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
@@ -28089,13 +28089,13 @@
         </is>
       </c>
       <c r="M430" s="2" t="n">
-        <v>1020.8</v>
+        <v>1200.51</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>3712-165-CM26</t>
+          <t>3712-208-CM26</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
@@ -28154,7 +28154,7 @@
         </is>
       </c>
       <c r="M431" s="2" t="n">
-        <v>1200.51</v>
+        <v>1020.8</v>
       </c>
     </row>
     <row r="432">
@@ -28355,7 +28355,7 @@
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>1079505-88-CM26</t>
+          <t>1079505-89-CM26</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
@@ -28410,13 +28410,13 @@
         </is>
       </c>
       <c r="M435" s="2" t="n">
-        <v>2401.69</v>
+        <v>11628.54</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>1079505-89-CM26</t>
+          <t>1079505-88-CM26</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
@@ -28471,7 +28471,7 @@
         </is>
       </c>
       <c r="M436" s="2" t="n">
-        <v>11628.54</v>
+        <v>2401.69</v>
       </c>
     </row>
     <row r="437">
@@ -28607,7 +28607,7 @@
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>1430710-195-CM26</t>
+          <t>1057439-1890-CM26</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
@@ -28632,12 +28632,12 @@
       </c>
       <c r="F439" t="inlineStr">
         <is>
-          <t>61.606.403-7</t>
+          <t>61.606.402-9</t>
         </is>
       </c>
       <c r="G439" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE COQUIMBO</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
         </is>
       </c>
       <c r="H439" t="inlineStr">
@@ -28647,32 +28647,28 @@
       </c>
       <c r="I439" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>CARLOS ALBERTO VARGAS CASTILLO</t>
         </is>
       </c>
       <c r="J439" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
-        </is>
-      </c>
-      <c r="K439" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>13.940.082-8</t>
+        </is>
+      </c>
+      <c r="K439" t="inlineStr"/>
       <c r="L439" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M439" s="2" t="n">
-        <v>3275.93</v>
+        <v>9472.610000000001</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>1057439-1890-CM26</t>
+          <t>1242121-142-CM26</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
@@ -28697,12 +28693,12 @@
       </c>
       <c r="F440" t="inlineStr">
         <is>
-          <t>61.606.402-9</t>
+          <t>61.606.404-5</t>
         </is>
       </c>
       <c r="G440" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE O</t>
         </is>
       </c>
       <c r="H440" t="inlineStr">
@@ -28712,28 +28708,32 @@
       </c>
       <c r="I440" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO VARGAS CASTILLO</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J440" t="inlineStr">
         <is>
-          <t>13.940.082-8</t>
-        </is>
-      </c>
-      <c r="K440" t="inlineStr"/>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K440" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L440" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M440" s="2" t="n">
-        <v>9472.610000000001</v>
+        <v>3864.8</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>2711-64-CM26</t>
+          <t>1430710-195-CM26</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
@@ -28753,17 +28753,17 @@
       </c>
       <c r="E441" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F441" t="inlineStr">
         <is>
-          <t>69.040.700-0</t>
+          <t>61.606.403-7</t>
         </is>
       </c>
       <c r="G441" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE OVALLE</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE COQUIMBO</t>
         </is>
       </c>
       <c r="H441" t="inlineStr">
@@ -28773,17 +28773,17 @@
       </c>
       <c r="I441" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J441" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K441" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L441" t="inlineStr">
@@ -28792,13 +28792,13 @@
         </is>
       </c>
       <c r="M441" s="2" t="n">
-        <v>2452.91</v>
+        <v>3275.93</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>1242121-142-CM26</t>
+          <t>2711-64-CM26</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
@@ -28818,17 +28818,17 @@
       </c>
       <c r="E442" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F442" t="inlineStr">
         <is>
-          <t>61.606.404-5</t>
+          <t>69.040.700-0</t>
         </is>
       </c>
       <c r="G442" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE O</t>
+          <t>MUNICIPALIDAD DE OVALLE</t>
         </is>
       </c>
       <c r="H442" t="inlineStr">
@@ -28838,17 +28838,17 @@
       </c>
       <c r="I442" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J442" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K442" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L442" t="inlineStr">
@@ -28857,7 +28857,7 @@
         </is>
       </c>
       <c r="M442" s="2" t="n">
-        <v>3864.8</v>
+        <v>2452.91</v>
       </c>
     </row>
     <row r="443">
@@ -28928,7 +28928,7 @@
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>1232565-48-CM26</t>
+          <t>3712-159-CM26</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
@@ -28953,12 +28953,12 @@
       </c>
       <c r="F444" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G444" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H444" t="inlineStr">
@@ -28968,12 +28968,12 @@
       </c>
       <c r="I444" t="inlineStr">
         <is>
-          <t>BAILEY GROUP SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J444" t="inlineStr">
         <is>
-          <t>77.638.992-7</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K444" t="inlineStr">
@@ -28987,13 +28987,13 @@
         </is>
       </c>
       <c r="M444" s="2" t="n">
-        <v>967.4</v>
+        <v>1197.89</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>5416-184-CM26</t>
+          <t>1232565-48-CM26</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
@@ -29033,17 +29033,17 @@
       </c>
       <c r="I445" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>BAILEY GROUP SPA</t>
         </is>
       </c>
       <c r="J445" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>77.638.992-7</t>
         </is>
       </c>
       <c r="K445" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L445" t="inlineStr">
@@ -29052,13 +29052,13 @@
         </is>
       </c>
       <c r="M445" s="2" t="n">
-        <v>1864.68</v>
+        <v>967.4</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>3712-159-CM26</t>
+          <t>5416-184-CM26</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
@@ -29083,12 +29083,12 @@
       </c>
       <c r="F446" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G446" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H446" t="inlineStr">
@@ -29098,17 +29098,17 @@
       </c>
       <c r="I446" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J446" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K446" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="L446" t="inlineStr">
@@ -29117,7 +29117,7 @@
         </is>
       </c>
       <c r="M446" s="2" t="n">
-        <v>1197.89</v>
+        <v>1864.68</v>
       </c>
     </row>
     <row r="447">
@@ -29188,7 +29188,7 @@
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>2146-123-CM26</t>
+          <t>3616-30-CM26</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
@@ -29208,17 +29208,17 @@
       </c>
       <c r="E448" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F448" t="inlineStr">
         <is>
-          <t>61.606.405-3</t>
+          <t>69.041.100-8</t>
         </is>
       </c>
       <c r="G448" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE ANDACOLLO</t>
+          <t>ILUSTRE MINICIPALIDAD DE COMBARBALA</t>
         </is>
       </c>
       <c r="H448" t="inlineStr">
@@ -29247,13 +29247,13 @@
         </is>
       </c>
       <c r="M448" s="2" t="n">
-        <v>1400.18</v>
+        <v>5483.22</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>3616-30-CM26</t>
+          <t>5416-197-CM26</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
@@ -29273,17 +29273,17 @@
       </c>
       <c r="E449" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F449" t="inlineStr">
         <is>
-          <t>69.041.100-8</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G449" t="inlineStr">
         <is>
-          <t>ILUSTRE MINICIPALIDAD DE COMBARBALA</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H449" t="inlineStr">
@@ -29293,17 +29293,17 @@
       </c>
       <c r="I449" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J449" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K449" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="L449" t="inlineStr">
@@ -29312,13 +29312,13 @@
         </is>
       </c>
       <c r="M449" s="2" t="n">
-        <v>5483.22</v>
+        <v>3368.41</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>5416-197-CM26</t>
+          <t>2146-123-CM26</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
@@ -29343,12 +29343,12 @@
       </c>
       <c r="F450" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>61.606.405-3</t>
         </is>
       </c>
       <c r="G450" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE ANDACOLLO</t>
         </is>
       </c>
       <c r="H450" t="inlineStr">
@@ -29358,17 +29358,17 @@
       </c>
       <c r="I450" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J450" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K450" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L450" t="inlineStr">
@@ -29377,7 +29377,7 @@
         </is>
       </c>
       <c r="M450" s="2" t="n">
-        <v>3368.41</v>
+        <v>1400.18</v>
       </c>
     </row>
     <row r="451">
@@ -29659,7 +29659,7 @@
       </c>
       <c r="E455" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F455" t="inlineStr">
@@ -30155,7 +30155,7 @@
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>548854-16-CM26</t>
+          <t>2125-759-CM26</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
@@ -30180,12 +30180,12 @@
       </c>
       <c r="F463" t="inlineStr">
         <is>
-          <t>61.979.440-0</t>
+          <t>61.606.407-k</t>
         </is>
       </c>
       <c r="G463" t="inlineStr">
         <is>
-          <t>INSTITUTO DE PREVISION SOCIAL</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DR. HUMBERTO ELORZA CORTES</t>
         </is>
       </c>
       <c r="H463" t="inlineStr">
@@ -30214,7 +30214,7 @@
         </is>
       </c>
       <c r="M463" s="2" t="n">
-        <v>6860.64</v>
+        <v>880.6900000000001</v>
       </c>
     </row>
     <row r="464">
@@ -30285,7 +30285,7 @@
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>2125-759-CM26</t>
+          <t>548854-16-CM26</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
@@ -30310,12 +30310,12 @@
       </c>
       <c r="F465" t="inlineStr">
         <is>
-          <t>61.606.407-k</t>
+          <t>61.979.440-0</t>
         </is>
       </c>
       <c r="G465" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DR. HUMBERTO ELORZA CORTES</t>
+          <t>INSTITUTO DE PREVISION SOCIAL</t>
         </is>
       </c>
       <c r="H465" t="inlineStr">
@@ -30344,7 +30344,7 @@
         </is>
       </c>
       <c r="M465" s="2" t="n">
-        <v>880.6900000000001</v>
+        <v>6860.64</v>
       </c>
     </row>
     <row r="466">
@@ -30736,7 +30736,7 @@
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>1057439-2381-CM26</t>
+          <t>1159-67-CM26</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
@@ -30761,12 +30761,12 @@
       </c>
       <c r="F472" t="inlineStr">
         <is>
-          <t>61.606.402-9</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G472" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H472" t="inlineStr">
@@ -30776,28 +30776,32 @@
       </c>
       <c r="I472" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO VARGAS CASTILLO</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J472" t="inlineStr">
         <is>
-          <t>13.940.082-8</t>
-        </is>
-      </c>
-      <c r="K472" t="inlineStr"/>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K472" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L472" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M472" s="2" t="n">
-        <v>9554.030000000001</v>
+        <v>2271.52</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>1461054-116-CM26</t>
+          <t>1057439-2381-CM26</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
@@ -30822,12 +30826,12 @@
       </c>
       <c r="F473" t="inlineStr">
         <is>
-          <t>61.981.040-6</t>
+          <t>61.606.402-9</t>
         </is>
       </c>
       <c r="G473" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DEL ELQUI</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
         </is>
       </c>
       <c r="H473" t="inlineStr">
@@ -30837,32 +30841,28 @@
       </c>
       <c r="I473" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>CARLOS ALBERTO VARGAS CASTILLO</t>
         </is>
       </c>
       <c r="J473" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
-        </is>
-      </c>
-      <c r="K473" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>13.940.082-8</t>
+        </is>
+      </c>
+      <c r="K473" t="inlineStr"/>
       <c r="L473" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M473" s="2" t="n">
-        <v>44593.84</v>
+        <v>9554.030000000001</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>1159-67-CM26</t>
+          <t>1461054-116-CM26</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
@@ -30882,17 +30882,17 @@
       </c>
       <c r="E474" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F474" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>61.981.040-6</t>
         </is>
       </c>
       <c r="G474" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DEL ELQUI</t>
         </is>
       </c>
       <c r="H474" t="inlineStr">
@@ -30902,17 +30902,17 @@
       </c>
       <c r="I474" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J474" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K474" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L474" t="inlineStr">
@@ -30921,7 +30921,7 @@
         </is>
       </c>
       <c r="M474" s="2" t="n">
-        <v>2271.52</v>
+        <v>44593.84</v>
       </c>
     </row>
     <row r="475">
@@ -31317,7 +31317,7 @@
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>3712-287-CM26</t>
+          <t>1057439-2721-CM26</t>
         </is>
       </c>
       <c r="B481" t="inlineStr">
@@ -31342,12 +31342,12 @@
       </c>
       <c r="F481" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>61.606.402-9</t>
         </is>
       </c>
       <c r="G481" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
         </is>
       </c>
       <c r="H481" t="inlineStr">
@@ -31357,32 +31357,28 @@
       </c>
       <c r="I481" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>ROLAND VORWERK Y COMPANIA LIMITADA</t>
         </is>
       </c>
       <c r="J481" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
-        </is>
-      </c>
-      <c r="K481" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>78.178.530-k</t>
+        </is>
+      </c>
+      <c r="K481" t="inlineStr"/>
       <c r="L481" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M481" s="2" t="n">
-        <v>1179.43</v>
+        <v>2138.33</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>646-40-CM26</t>
+          <t>3712-287-CM26</t>
         </is>
       </c>
       <c r="B482" t="inlineStr">
@@ -31407,12 +31403,12 @@
       </c>
       <c r="F482" t="inlineStr">
         <is>
-          <t>61.816.000-9</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G482" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION IV REGION</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H482" t="inlineStr">
@@ -31422,12 +31418,12 @@
       </c>
       <c r="I482" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J482" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K482" t="inlineStr">
@@ -31441,13 +31437,13 @@
         </is>
       </c>
       <c r="M482" s="2" t="n">
-        <v>1736.5</v>
+        <v>1179.43</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>1057439-2721-CM26</t>
+          <t>646-40-CM26</t>
         </is>
       </c>
       <c r="B483" t="inlineStr">
@@ -31472,12 +31468,12 @@
       </c>
       <c r="F483" t="inlineStr">
         <is>
-          <t>61.606.402-9</t>
+          <t>61.816.000-9</t>
         </is>
       </c>
       <c r="G483" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION IV REGION</t>
         </is>
       </c>
       <c r="H483" t="inlineStr">
@@ -31487,22 +31483,26 @@
       </c>
       <c r="I483" t="inlineStr">
         <is>
-          <t>ROLAND VORWERK Y COMPANIA LIMITADA</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J483" t="inlineStr">
         <is>
-          <t>78.178.530-k</t>
-        </is>
-      </c>
-      <c r="K483" t="inlineStr"/>
+          <t>76.540.457-6</t>
+        </is>
+      </c>
+      <c r="K483" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L483" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M483" s="2" t="n">
-        <v>2138.33</v>
+        <v>1736.5</v>
       </c>
     </row>
     <row r="484">
@@ -31703,7 +31703,7 @@
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>1232820-55-CM26</t>
+          <t>3712-301-CM26</t>
         </is>
       </c>
       <c r="B487" t="inlineStr">
@@ -31723,17 +31723,17 @@
       </c>
       <c r="E487" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F487" t="inlineStr">
         <is>
-          <t>65.080.284-5</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G487" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE TURISMO VICUNA</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H487" t="inlineStr">
@@ -31762,13 +31762,13 @@
         </is>
       </c>
       <c r="M487" s="2" t="n">
-        <v>795.16</v>
+        <v>1455.94</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>3712-301-CM26</t>
+          <t>1232820-55-CM26</t>
         </is>
       </c>
       <c r="B488" t="inlineStr">
@@ -31788,17 +31788,17 @@
       </c>
       <c r="E488" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F488" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>65.080.284-5</t>
         </is>
       </c>
       <c r="G488" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>CORPORACION MUNICIPAL DE TURISMO VICUNA</t>
         </is>
       </c>
       <c r="H488" t="inlineStr">
@@ -31827,7 +31827,7 @@
         </is>
       </c>
       <c r="M488" s="2" t="n">
-        <v>1455.94</v>
+        <v>795.16</v>
       </c>
     </row>
     <row r="489">
@@ -32284,7 +32284,7 @@
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>3512-473-CM26</t>
+          <t>1057439-2988-CM26</t>
         </is>
       </c>
       <c r="B496" t="inlineStr">
@@ -32304,17 +32304,17 @@
       </c>
       <c r="E496" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F496" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>61.606.402-9</t>
         </is>
       </c>
       <c r="G496" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
         </is>
       </c>
       <c r="H496" t="inlineStr">
@@ -32324,32 +32324,28 @@
       </c>
       <c r="I496" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>CARLOS ALBERTO VARGAS CASTILLO</t>
         </is>
       </c>
       <c r="J496" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
-        </is>
-      </c>
-      <c r="K496" t="inlineStr">
-        <is>
-          <t>Antofagasta</t>
-        </is>
-      </c>
+          <t>13.940.082-8</t>
+        </is>
+      </c>
+      <c r="K496" t="inlineStr"/>
       <c r="L496" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M496" s="2" t="n">
-        <v>2556.25</v>
+        <v>9589.450000000001</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>1057439-2988-CM26</t>
+          <t>3512-473-CM26</t>
         </is>
       </c>
       <c r="B497" t="inlineStr">
@@ -32369,17 +32365,17 @@
       </c>
       <c r="E497" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F497" t="inlineStr">
         <is>
-          <t>61.606.402-9</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G497" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H497" t="inlineStr">
@@ -32389,28 +32385,32 @@
       </c>
       <c r="I497" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO VARGAS CASTILLO</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J497" t="inlineStr">
         <is>
-          <t>13.940.082-8</t>
-        </is>
-      </c>
-      <c r="K497" t="inlineStr"/>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K497" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L497" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M497" s="2" t="n">
-        <v>9589.450000000001</v>
+        <v>2556.25</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>2710-201-CM26</t>
+          <t>2710-204-CM26</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
@@ -32430,7 +32430,7 @@
       </c>
       <c r="E498" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F498" t="inlineStr">
@@ -32450,17 +32450,17 @@
       </c>
       <c r="I498" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J498" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>77.474.803-2</t>
         </is>
       </c>
       <c r="K498" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="L498" t="inlineStr">
@@ -32469,13 +32469,13 @@
         </is>
       </c>
       <c r="M498" s="2" t="n">
-        <v>27569.02</v>
+        <v>13054.6</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>2710-204-CM26</t>
+          <t>2710-210-CM26</t>
         </is>
       </c>
       <c r="B499" t="inlineStr">
@@ -32495,7 +32495,7 @@
       </c>
       <c r="E499" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F499" t="inlineStr">
@@ -32515,17 +32515,17 @@
       </c>
       <c r="I499" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J499" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K499" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L499" t="inlineStr">
@@ -32534,13 +32534,13 @@
         </is>
       </c>
       <c r="M499" s="2" t="n">
-        <v>13054.6</v>
+        <v>24331.46</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>2710-210-CM26</t>
+          <t>2710-201-CM26</t>
         </is>
       </c>
       <c r="B500" t="inlineStr">
@@ -32580,12 +32580,12 @@
       </c>
       <c r="I500" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J500" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K500" t="inlineStr">
@@ -32599,13 +32599,13 @@
         </is>
       </c>
       <c r="M500" s="2" t="n">
-        <v>24331.46</v>
+        <v>27569.02</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>707418-60-CM26</t>
+          <t>3511-141-CM26</t>
         </is>
       </c>
       <c r="B501" t="inlineStr">
@@ -32625,17 +32625,17 @@
       </c>
       <c r="E501" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F501" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G501" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H501" t="inlineStr">
@@ -32645,32 +32645,28 @@
       </c>
       <c r="I501" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>AMINORTE S A</t>
         </is>
       </c>
       <c r="J501" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
-        </is>
-      </c>
-      <c r="K501" t="inlineStr">
-        <is>
-          <t>Coquimbo</t>
-        </is>
-      </c>
+          <t>99.533.780-0</t>
+        </is>
+      </c>
+      <c r="K501" t="inlineStr"/>
       <c r="L501" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M501" s="2" t="n">
-        <v>1535.15</v>
+        <v>817.37</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>3511-141-CM26</t>
+          <t>707418-60-CM26</t>
         </is>
       </c>
       <c r="B502" t="inlineStr">
@@ -32690,17 +32686,17 @@
       </c>
       <c r="E502" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F502" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G502" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H502" t="inlineStr">
@@ -32710,22 +32706,26 @@
       </c>
       <c r="I502" t="inlineStr">
         <is>
-          <t>AMINORTE S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J502" t="inlineStr">
         <is>
-          <t>99.533.780-0</t>
-        </is>
-      </c>
-      <c r="K502" t="inlineStr"/>
+          <t>77.012.870-6</t>
+        </is>
+      </c>
+      <c r="K502" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L502" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M502" s="2" t="n">
-        <v>817.37</v>
+        <v>1535.15</v>
       </c>
     </row>
     <row r="503">
@@ -33263,7 +33263,7 @@
       </c>
       <c r="E511" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F511" t="inlineStr">
@@ -33503,7 +33503,7 @@
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>3714-109-CM26</t>
+          <t>3714-110-CM26</t>
         </is>
       </c>
       <c r="B515" t="inlineStr">
@@ -33558,13 +33558,13 @@
         </is>
       </c>
       <c r="M515" s="2" t="n">
-        <v>871.65</v>
+        <v>3748.11</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>3714-110-CM26</t>
+          <t>3509-197-CM26</t>
         </is>
       </c>
       <c r="B516" t="inlineStr">
@@ -33584,17 +33584,17 @@
       </c>
       <c r="E516" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F516" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G516" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H516" t="inlineStr">
@@ -33604,28 +33604,32 @@
       </c>
       <c r="I516" t="inlineStr">
         <is>
-          <t>SURTI VENTAS S.A.</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J516" t="inlineStr">
         <is>
-          <t>76.462.500-5</t>
-        </is>
-      </c>
-      <c r="K516" t="inlineStr"/>
+          <t>77.012.870-6</t>
+        </is>
+      </c>
+      <c r="K516" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L516" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M516" s="2" t="n">
-        <v>3748.11</v>
+        <v>786.61</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>3509-197-CM26</t>
+          <t>3714-109-CM26</t>
         </is>
       </c>
       <c r="B517" t="inlineStr">
@@ -33645,17 +33649,17 @@
       </c>
       <c r="E517" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F517" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G517" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H517" t="inlineStr">
@@ -33665,26 +33669,22 @@
       </c>
       <c r="I517" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>SURTI VENTAS S.A.</t>
         </is>
       </c>
       <c r="J517" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
-        </is>
-      </c>
-      <c r="K517" t="inlineStr">
-        <is>
-          <t>Coquimbo</t>
-        </is>
-      </c>
+          <t>76.462.500-5</t>
+        </is>
+      </c>
+      <c r="K517" t="inlineStr"/>
       <c r="L517" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M517" s="2" t="n">
-        <v>786.61</v>
+        <v>871.65</v>
       </c>
     </row>
     <row r="518">
@@ -34226,7 +34226,7 @@
       </c>
       <c r="E526" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F526" t="inlineStr">
@@ -34336,7 +34336,7 @@
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>1574-77-CM26</t>
+          <t>3509-220-CM26</t>
         </is>
       </c>
       <c r="B528" t="inlineStr">
@@ -34361,12 +34361,12 @@
       </c>
       <c r="F528" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G528" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H528" t="inlineStr">
@@ -34376,17 +34376,17 @@
       </c>
       <c r="I528" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J528" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K528" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="L528" t="inlineStr">
@@ -34395,13 +34395,13 @@
         </is>
       </c>
       <c r="M528" s="2" t="n">
-        <v>4851.02</v>
+        <v>1805.68</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>1574-78-CM26</t>
+          <t>1574-77-CM26</t>
         </is>
       </c>
       <c r="B529" t="inlineStr">
@@ -34421,7 +34421,7 @@
       </c>
       <c r="E529" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F529" t="inlineStr">
@@ -34460,13 +34460,13 @@
         </is>
       </c>
       <c r="M529" s="2" t="n">
-        <v>2148.75</v>
+        <v>4851.02</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>3509-220-CM26</t>
+          <t>1574-78-CM26</t>
         </is>
       </c>
       <c r="B530" t="inlineStr">
@@ -34491,12 +34491,12 @@
       </c>
       <c r="F530" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G530" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H530" t="inlineStr">
@@ -34506,17 +34506,17 @@
       </c>
       <c r="I530" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J530" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K530" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L530" t="inlineStr">
@@ -34525,7 +34525,7 @@
         </is>
       </c>
       <c r="M530" s="2" t="n">
-        <v>1805.68</v>
+        <v>2148.75</v>
       </c>
     </row>
     <row r="531">
@@ -34872,7 +34872,7 @@
       </c>
       <c r="E536" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F536" t="inlineStr">
@@ -34917,7 +34917,7 @@
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>3884-263-CM26</t>
+          <t>697055-32-CM26</t>
         </is>
       </c>
       <c r="B537" t="inlineStr">
@@ -34937,17 +34937,17 @@
       </c>
       <c r="E537" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F537" t="inlineStr">
         <is>
-          <t>69.040.600-4</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G537" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD PAIHUANO</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H537" t="inlineStr">
@@ -34957,17 +34957,17 @@
       </c>
       <c r="I537" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J537" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K537" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L537" t="inlineStr">
@@ -34976,13 +34976,13 @@
         </is>
       </c>
       <c r="M537" s="2" t="n">
-        <v>2502.48</v>
+        <v>4898.03</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>697055-32-CM26</t>
+          <t>2711-150-CM26</t>
         </is>
       </c>
       <c r="B538" t="inlineStr">
@@ -35002,17 +35002,17 @@
       </c>
       <c r="E538" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F538" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>69.040.700-0</t>
         </is>
       </c>
       <c r="G538" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>MUNICIPALIDAD DE OVALLE</t>
         </is>
       </c>
       <c r="H538" t="inlineStr">
@@ -35022,12 +35022,12 @@
       </c>
       <c r="I538" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J538" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K538" t="inlineStr">
@@ -35041,7 +35041,7 @@
         </is>
       </c>
       <c r="M538" s="2" t="n">
-        <v>4898.03</v>
+        <v>6348.66</v>
       </c>
     </row>
     <row r="539">
@@ -35108,7 +35108,7 @@
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>2711-150-CM26</t>
+          <t>3884-263-CM26</t>
         </is>
       </c>
       <c r="B540" t="inlineStr">
@@ -35128,17 +35128,17 @@
       </c>
       <c r="E540" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F540" t="inlineStr">
         <is>
-          <t>69.040.700-0</t>
+          <t>69.040.600-4</t>
         </is>
       </c>
       <c r="G540" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE OVALLE</t>
+          <t>I MUNICIPALIDAD PAIHUANO</t>
         </is>
       </c>
       <c r="H540" t="inlineStr">
@@ -35148,17 +35148,17 @@
       </c>
       <c r="I540" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J540" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K540" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L540" t="inlineStr">
@@ -35167,7 +35167,7 @@
         </is>
       </c>
       <c r="M540" s="2" t="n">
-        <v>6348.66</v>
+        <v>2502.48</v>
       </c>
     </row>
     <row r="541">
@@ -35303,7 +35303,7 @@
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>3712-413-CM26</t>
+          <t>2992-193-CM26</t>
         </is>
       </c>
       <c r="B543" t="inlineStr">
@@ -35328,12 +35328,12 @@
       </c>
       <c r="F543" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>69.040.800-7</t>
         </is>
       </c>
       <c r="G543" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>I MUNICIPALIDAD DE MONTEPATRIA</t>
         </is>
       </c>
       <c r="H543" t="inlineStr">
@@ -35343,17 +35343,17 @@
       </c>
       <c r="I543" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J543" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K543" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="L543" t="inlineStr">
@@ -35362,7 +35362,7 @@
         </is>
       </c>
       <c r="M543" s="2" t="n">
-        <v>1308.28</v>
+        <v>1972.16</v>
       </c>
     </row>
     <row r="544">
@@ -35433,7 +35433,7 @@
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>2992-193-CM26</t>
+          <t>3712-413-CM26</t>
         </is>
       </c>
       <c r="B545" t="inlineStr">
@@ -35453,17 +35453,17 @@
       </c>
       <c r="E545" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F545" t="inlineStr">
         <is>
-          <t>69.040.800-7</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G545" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MONTEPATRIA</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H545" t="inlineStr">
@@ -35473,17 +35473,17 @@
       </c>
       <c r="I545" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J545" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>77.346.435-9</t>
         </is>
       </c>
       <c r="K545" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L545" t="inlineStr">
@@ -35492,13 +35492,13 @@
         </is>
       </c>
       <c r="M545" s="2" t="n">
-        <v>1972.16</v>
+        <v>1308.28</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>2125-1292-CM26</t>
+          <t>2992-211-CM26</t>
         </is>
       </c>
       <c r="B546" t="inlineStr">
@@ -35523,12 +35523,12 @@
       </c>
       <c r="F546" t="inlineStr">
         <is>
-          <t>61.606.407-k</t>
+          <t>69.040.800-7</t>
         </is>
       </c>
       <c r="G546" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DR. HUMBERTO ELORZA CORTES</t>
+          <t>I MUNICIPALIDAD DE MONTEPATRIA</t>
         </is>
       </c>
       <c r="H546" t="inlineStr">
@@ -35538,17 +35538,17 @@
       </c>
       <c r="I546" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J546" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K546" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="L546" t="inlineStr">
@@ -35557,13 +35557,13 @@
         </is>
       </c>
       <c r="M546" s="2" t="n">
-        <v>1352.97</v>
+        <v>5014.22</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>2992-211-CM26</t>
+          <t>2125-1292-CM26</t>
         </is>
       </c>
       <c r="B547" t="inlineStr">
@@ -35583,17 +35583,17 @@
       </c>
       <c r="E547" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F547" t="inlineStr">
         <is>
-          <t>69.040.800-7</t>
+          <t>61.606.407-k</t>
         </is>
       </c>
       <c r="G547" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MONTEPATRIA</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DR. HUMBERTO ELORZA CORTES</t>
         </is>
       </c>
       <c r="H547" t="inlineStr">
@@ -35603,17 +35603,17 @@
       </c>
       <c r="I547" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J547" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K547" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L547" t="inlineStr">
@@ -35622,7 +35622,7 @@
         </is>
       </c>
       <c r="M547" s="2" t="n">
-        <v>5014.22</v>
+        <v>1352.97</v>
       </c>
     </row>
     <row r="548">
@@ -35648,7 +35648,7 @@
       </c>
       <c r="E548" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F548" t="inlineStr">
@@ -35778,7 +35778,7 @@
       </c>
       <c r="E550" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F550" t="inlineStr">
@@ -35908,7 +35908,7 @@
       </c>
       <c r="E552" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F552" t="inlineStr">
@@ -36103,7 +36103,7 @@
       </c>
       <c r="E555" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F555" t="inlineStr">
@@ -36148,7 +36148,7 @@
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>1574-102-CM26</t>
+          <t>1962-370-CM26</t>
         </is>
       </c>
       <c r="B556" t="inlineStr">
@@ -36173,12 +36173,12 @@
       </c>
       <c r="F556" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>61.004.012-8</t>
         </is>
       </c>
       <c r="G556" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H556" t="inlineStr">
@@ -36188,17 +36188,17 @@
       </c>
       <c r="I556" t="inlineStr">
         <is>
-          <t>IMPORTADORA Y COMERCIALIZADORA JMMB SPA</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J556" t="inlineStr">
         <is>
-          <t>77.461.733-7</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K556" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="L556" t="inlineStr">
@@ -36207,13 +36207,13 @@
         </is>
       </c>
       <c r="M556" s="2" t="n">
-        <v>3120.97</v>
+        <v>1801.34</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>1352-56-CM26</t>
+          <t>1574-102-CM26</t>
         </is>
       </c>
       <c r="B557" t="inlineStr">
@@ -36233,17 +36233,17 @@
       </c>
       <c r="E557" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F557" t="inlineStr">
         <is>
-          <t>61.002.010-0</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G557" t="inlineStr">
         <is>
-          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H557" t="inlineStr">
@@ -36253,17 +36253,17 @@
       </c>
       <c r="I557" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>IMPORTADORA Y COMERCIALIZADORA JMMB SPA</t>
         </is>
       </c>
       <c r="J557" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>77.461.733-7</t>
         </is>
       </c>
       <c r="K557" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L557" t="inlineStr">
@@ -36272,13 +36272,13 @@
         </is>
       </c>
       <c r="M557" s="2" t="n">
-        <v>1115.85</v>
+        <v>3120.97</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>1962-370-CM26</t>
+          <t>1574-103-CM26</t>
         </is>
       </c>
       <c r="B558" t="inlineStr">
@@ -36303,12 +36303,12 @@
       </c>
       <c r="F558" t="inlineStr">
         <is>
-          <t>61.004.012-8</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G558" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H558" t="inlineStr">
@@ -36318,17 +36318,17 @@
       </c>
       <c r="I558" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>IMPORTADORA Y COMERCIALIZADORA JMMB SPA</t>
         </is>
       </c>
       <c r="J558" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>77.461.733-7</t>
         </is>
       </c>
       <c r="K558" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L558" t="inlineStr">
@@ -36337,13 +36337,13 @@
         </is>
       </c>
       <c r="M558" s="2" t="n">
-        <v>1801.34</v>
+        <v>1584.15</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>1574-103-CM26</t>
+          <t>1352-56-CM26</t>
         </is>
       </c>
       <c r="B559" t="inlineStr">
@@ -36363,17 +36363,17 @@
       </c>
       <c r="E559" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F559" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>61.002.010-0</t>
         </is>
       </c>
       <c r="G559" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
         </is>
       </c>
       <c r="H559" t="inlineStr">
@@ -36383,17 +36383,17 @@
       </c>
       <c r="I559" t="inlineStr">
         <is>
-          <t>IMPORTADORA Y COMERCIALIZADORA JMMB SPA</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J559" t="inlineStr">
         <is>
-          <t>77.461.733-7</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K559" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="L559" t="inlineStr">
@@ -36402,7 +36402,7 @@
         </is>
       </c>
       <c r="M559" s="2" t="n">
-        <v>1584.15</v>
+        <v>1115.85</v>
       </c>
     </row>
     <row r="560">
@@ -36428,7 +36428,7 @@
       </c>
       <c r="E560" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F560" t="inlineStr">
@@ -36473,7 +36473,7 @@
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>2992-233-CM26</t>
+          <t>1159-174-CM26</t>
         </is>
       </c>
       <c r="B561" t="inlineStr">
@@ -36493,17 +36493,17 @@
       </c>
       <c r="E561" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F561" t="inlineStr">
         <is>
-          <t>69.040.800-7</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G561" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MONTEPATRIA</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H561" t="inlineStr">
@@ -36513,17 +36513,17 @@
       </c>
       <c r="I561" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J561" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>77.346.435-9</t>
         </is>
       </c>
       <c r="K561" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L561" t="inlineStr">
@@ -36532,13 +36532,13 @@
         </is>
       </c>
       <c r="M561" s="2" t="n">
-        <v>2950.02</v>
+        <v>2765.7</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>1159-174-CM26</t>
+          <t>2288-580-CM26</t>
         </is>
       </c>
       <c r="B562" t="inlineStr">
@@ -36558,17 +36558,17 @@
       </c>
       <c r="E562" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F562" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>69.041.300-0</t>
         </is>
       </c>
       <c r="G562" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>I MUNICIPALIDAD DE CANELA</t>
         </is>
       </c>
       <c r="H562" t="inlineStr">
@@ -36578,12 +36578,12 @@
       </c>
       <c r="I562" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J562" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K562" t="inlineStr">
@@ -36597,13 +36597,13 @@
         </is>
       </c>
       <c r="M562" s="2" t="n">
-        <v>2765.7</v>
+        <v>2165.13</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>2288-580-CM26</t>
+          <t>1159-175-CM26</t>
         </is>
       </c>
       <c r="B563" t="inlineStr">
@@ -36628,12 +36628,12 @@
       </c>
       <c r="F563" t="inlineStr">
         <is>
-          <t>69.041.300-0</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G563" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CANELA</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H563" t="inlineStr">
@@ -36662,13 +36662,13 @@
         </is>
       </c>
       <c r="M563" s="2" t="n">
-        <v>2165.13</v>
+        <v>1720.66</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>1159-175-CM26</t>
+          <t>2992-233-CM26</t>
         </is>
       </c>
       <c r="B564" t="inlineStr">
@@ -36688,17 +36688,17 @@
       </c>
       <c r="E564" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F564" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>69.040.800-7</t>
         </is>
       </c>
       <c r="G564" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>I MUNICIPALIDAD DE MONTEPATRIA</t>
         </is>
       </c>
       <c r="H564" t="inlineStr">
@@ -36708,17 +36708,17 @@
       </c>
       <c r="I564" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J564" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K564" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="L564" t="inlineStr">
@@ -36727,13 +36727,13 @@
         </is>
       </c>
       <c r="M564" s="2" t="n">
-        <v>1720.66</v>
+        <v>2950.02</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>1124-28-CM26</t>
+          <t>2992-203-CM26</t>
         </is>
       </c>
       <c r="B565" t="inlineStr">
@@ -36758,12 +36758,12 @@
       </c>
       <c r="F565" t="inlineStr">
         <is>
-          <t>61.307.000-1</t>
+          <t>69.040.800-7</t>
         </is>
       </c>
       <c r="G565" t="inlineStr">
         <is>
-          <t>INSTITUTO DE DESARROLLO AGROPECUARIO</t>
+          <t>I MUNICIPALIDAD DE MONTEPATRIA</t>
         </is>
       </c>
       <c r="H565" t="inlineStr">
@@ -36773,17 +36773,17 @@
       </c>
       <c r="I565" t="inlineStr">
         <is>
-          <t>ANTALIS CHILE LIMITADA</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J565" t="inlineStr">
         <is>
-          <t>77.305.910-1</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K565" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="L565" t="inlineStr">
@@ -36792,13 +36792,13 @@
         </is>
       </c>
       <c r="M565" s="2" t="n">
-        <v>1395.01</v>
+        <v>7134.87</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>2992-203-CM26</t>
+          <t>1124-28-CM26</t>
         </is>
       </c>
       <c r="B566" t="inlineStr">
@@ -36818,17 +36818,17 @@
       </c>
       <c r="E566" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F566" t="inlineStr">
         <is>
-          <t>69.040.800-7</t>
+          <t>61.307.000-1</t>
         </is>
       </c>
       <c r="G566" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MONTEPATRIA</t>
+          <t>INSTITUTO DE DESARROLLO AGROPECUARIO</t>
         </is>
       </c>
       <c r="H566" t="inlineStr">
@@ -36838,17 +36838,17 @@
       </c>
       <c r="I566" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>ANTALIS CHILE LIMITADA</t>
         </is>
       </c>
       <c r="J566" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>77.305.910-1</t>
         </is>
       </c>
       <c r="K566" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L566" t="inlineStr">
@@ -36857,7 +36857,7 @@
         </is>
       </c>
       <c r="M566" s="2" t="n">
-        <v>7134.87</v>
+        <v>1395.01</v>
       </c>
     </row>
     <row r="567">
@@ -36883,7 +36883,7 @@
       </c>
       <c r="E567" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F567" t="inlineStr">
@@ -36928,7 +36928,7 @@
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>2992-232-CM26</t>
+          <t>5416-661-CM26</t>
         </is>
       </c>
       <c r="B568" t="inlineStr">
@@ -36948,17 +36948,17 @@
       </c>
       <c r="E568" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F568" t="inlineStr">
         <is>
-          <t>69.040.800-7</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G568" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MONTEPATRIA</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H568" t="inlineStr">
@@ -36987,13 +36987,13 @@
         </is>
       </c>
       <c r="M568" s="2" t="n">
-        <v>5094.85</v>
+        <v>1406.77</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>5416-661-CM26</t>
+          <t>2992-232-CM26</t>
         </is>
       </c>
       <c r="B569" t="inlineStr">
@@ -37018,12 +37018,12 @@
       </c>
       <c r="F569" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>69.040.800-7</t>
         </is>
       </c>
       <c r="G569" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>I MUNICIPALIDAD DE MONTEPATRIA</t>
         </is>
       </c>
       <c r="H569" t="inlineStr">
@@ -37052,7 +37052,7 @@
         </is>
       </c>
       <c r="M569" s="2" t="n">
-        <v>1406.77</v>
+        <v>5094.85</v>
       </c>
     </row>
     <row r="570">
@@ -37253,7 +37253,7 @@
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>1660-591-CM26</t>
+          <t>3712-449-CM26</t>
         </is>
       </c>
       <c r="B573" t="inlineStr">
@@ -37278,12 +37278,12 @@
       </c>
       <c r="F573" t="inlineStr">
         <is>
-          <t>61.606.408-8</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G573" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD COQUIMBO HOSP DE SALAMANC</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H573" t="inlineStr">
@@ -37293,12 +37293,12 @@
       </c>
       <c r="I573" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J573" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.346.435-9</t>
         </is>
       </c>
       <c r="K573" t="inlineStr">
@@ -37312,13 +37312,13 @@
         </is>
       </c>
       <c r="M573" s="2" t="n">
-        <v>2877.65</v>
+        <v>921.77</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>3712-449-CM26</t>
+          <t>1660-591-CM26</t>
         </is>
       </c>
       <c r="B574" t="inlineStr">
@@ -37343,12 +37343,12 @@
       </c>
       <c r="F574" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>61.606.408-8</t>
         </is>
       </c>
       <c r="G574" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>SERVICIO SALUD COQUIMBO HOSP DE SALAMANC</t>
         </is>
       </c>
       <c r="H574" t="inlineStr">
@@ -37358,12 +37358,12 @@
       </c>
       <c r="I574" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J574" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K574" t="inlineStr">
@@ -37377,7 +37377,7 @@
         </is>
       </c>
       <c r="M574" s="2" t="n">
-        <v>921.77</v>
+        <v>2877.65</v>
       </c>
     </row>
     <row r="575">
@@ -37468,7 +37468,7 @@
       </c>
       <c r="E576" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F576" t="inlineStr">
@@ -37513,7 +37513,7 @@
     <row r="577">
       <c r="A577" t="inlineStr">
         <is>
-          <t>1430710-493-CM26</t>
+          <t>3512-644-CM26</t>
         </is>
       </c>
       <c r="B577" t="inlineStr">
@@ -37528,22 +37528,22 @@
       </c>
       <c r="D577" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="E577" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F577" t="inlineStr">
         <is>
-          <t>61.606.403-7</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G577" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE COQUIMBO</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H577" t="inlineStr">
@@ -37553,32 +37553,28 @@
       </c>
       <c r="I577" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>Comercial IBL SpA</t>
         </is>
       </c>
       <c r="J577" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
-        </is>
-      </c>
-      <c r="K577" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.452.485-3</t>
+        </is>
+      </c>
+      <c r="K577" t="inlineStr"/>
       <c r="L577" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M577" s="2" t="n">
-        <v>3414.56</v>
+        <v>2014.24</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="inlineStr">
         <is>
-          <t>1461054-271-CM26</t>
+          <t>1430710-493-CM26</t>
         </is>
       </c>
       <c r="B578" t="inlineStr">
@@ -37593,7 +37589,7 @@
       </c>
       <c r="D578" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="E578" t="inlineStr">
@@ -37603,12 +37599,12 @@
       </c>
       <c r="F578" t="inlineStr">
         <is>
-          <t>61.981.040-6</t>
+          <t>61.606.403-7</t>
         </is>
       </c>
       <c r="G578" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DEL ELQUI</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE COQUIMBO</t>
         </is>
       </c>
       <c r="H578" t="inlineStr">
@@ -37618,12 +37614,12 @@
       </c>
       <c r="I578" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J578" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K578" t="inlineStr">
@@ -37637,13 +37633,13 @@
         </is>
       </c>
       <c r="M578" s="2" t="n">
-        <v>2187.59</v>
+        <v>3414.56</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="inlineStr">
         <is>
-          <t>1461054-241-CM26</t>
+          <t>3712-436-CM26</t>
         </is>
       </c>
       <c r="B579" t="inlineStr">
@@ -37658,22 +37654,22 @@
       </c>
       <c r="D579" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="E579" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F579" t="inlineStr">
         <is>
-          <t>61.981.040-6</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G579" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DEL ELQUI</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H579" t="inlineStr">
@@ -37683,12 +37679,12 @@
       </c>
       <c r="I579" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>BAILEY GROUP SPA</t>
         </is>
       </c>
       <c r="J579" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.638.992-7</t>
         </is>
       </c>
       <c r="K579" t="inlineStr">
@@ -37702,13 +37698,13 @@
         </is>
       </c>
       <c r="M579" s="2" t="n">
-        <v>4174.98</v>
+        <v>908.05</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="inlineStr">
         <is>
-          <t>1057439-4554-CM26</t>
+          <t>1461054-271-CM26</t>
         </is>
       </c>
       <c r="B580" t="inlineStr">
@@ -37723,22 +37719,22 @@
       </c>
       <c r="D580" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="E580" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F580" t="inlineStr">
         <is>
-          <t>61.606.402-9</t>
+          <t>61.981.040-6</t>
         </is>
       </c>
       <c r="G580" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DEL ELQUI</t>
         </is>
       </c>
       <c r="H580" t="inlineStr">
@@ -37748,17 +37744,17 @@
       </c>
       <c r="I580" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J580" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K580" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L580" t="inlineStr">
@@ -37767,7 +37763,7 @@
         </is>
       </c>
       <c r="M580" s="2" t="n">
-        <v>2780.09</v>
+        <v>2187.59</v>
       </c>
     </row>
     <row r="581">
@@ -37793,7 +37789,7 @@
       </c>
       <c r="E581" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F581" t="inlineStr">
@@ -37834,7 +37830,7 @@
     <row r="582">
       <c r="A582" t="inlineStr">
         <is>
-          <t>3511-275-CM26</t>
+          <t>1057439-4554-CM26</t>
         </is>
       </c>
       <c r="B582" t="inlineStr">
@@ -37849,22 +37845,22 @@
       </c>
       <c r="D582" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="E582" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F582" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>61.606.402-9</t>
         </is>
       </c>
       <c r="G582" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
         </is>
       </c>
       <c r="H582" t="inlineStr">
@@ -37893,13 +37889,13 @@
         </is>
       </c>
       <c r="M582" s="2" t="n">
-        <v>956.5599999999999</v>
+        <v>2780.09</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="inlineStr">
         <is>
-          <t>3509-298-CM26</t>
+          <t>1461054-241-CM26</t>
         </is>
       </c>
       <c r="B583" t="inlineStr">
@@ -37914,22 +37910,22 @@
       </c>
       <c r="D583" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="E583" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F583" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>61.981.040-6</t>
         </is>
       </c>
       <c r="G583" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DEL ELQUI</t>
         </is>
       </c>
       <c r="H583" t="inlineStr">
@@ -37939,28 +37935,32 @@
       </c>
       <c r="I583" t="inlineStr">
         <is>
-          <t>ECOFFICE COMPUTACION LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J583" t="inlineStr">
         <is>
-          <t>76.293.503-1</t>
-        </is>
-      </c>
-      <c r="K583" t="inlineStr"/>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K583" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L583" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M583" s="2" t="n">
-        <v>773.8099999999999</v>
+        <v>4174.98</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="inlineStr">
         <is>
-          <t>2448-759-CM26</t>
+          <t>3511-275-CM26</t>
         </is>
       </c>
       <c r="B584" t="inlineStr">
@@ -37975,22 +37975,22 @@
       </c>
       <c r="D584" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="E584" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F584" t="inlineStr">
         <is>
-          <t>69.040.300-5</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G584" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COQUIMBO</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H584" t="inlineStr">
@@ -38000,17 +38000,17 @@
       </c>
       <c r="I584" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA CELGREN SPA</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J584" t="inlineStr">
         <is>
-          <t>77.529.681-K</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K584" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="L584" t="inlineStr">
@@ -38019,13 +38019,13 @@
         </is>
       </c>
       <c r="M584" s="2" t="n">
-        <v>6469.24</v>
+        <v>956.5599999999999</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="inlineStr">
         <is>
-          <t>3511-284-CM26</t>
+          <t>3509-298-CM26</t>
         </is>
       </c>
       <c r="B585" t="inlineStr">
@@ -38035,12 +38035,12 @@
       </c>
       <c r="C585" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D585" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="E585" t="inlineStr">
@@ -38065,32 +38065,28 @@
       </c>
       <c r="I585" t="inlineStr">
         <is>
-          <t>CASTILLA Y ARAGON SPA</t>
+          <t>ECOFFICE COMPUTACION LIMITADA</t>
         </is>
       </c>
       <c r="J585" t="inlineStr">
         <is>
-          <t>96.989.530-7</t>
-        </is>
-      </c>
-      <c r="K585" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.293.503-1</t>
+        </is>
+      </c>
+      <c r="K585" t="inlineStr"/>
       <c r="L585" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M585" s="2" t="n">
-        <v>3593.82</v>
+        <v>773.8099999999999</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="inlineStr">
         <is>
-          <t>3712-531-CM26</t>
+          <t>2448-759-CM26</t>
         </is>
       </c>
       <c r="B586" t="inlineStr">
@@ -38100,12 +38096,12 @@
       </c>
       <c r="C586" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D586" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E586" t="inlineStr">
@@ -38115,12 +38111,12 @@
       </c>
       <c r="F586" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>69.040.300-5</t>
         </is>
       </c>
       <c r="G586" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>I MUNICIPALIDAD DE COQUIMBO</t>
         </is>
       </c>
       <c r="H586" t="inlineStr">
@@ -38130,17 +38126,17 @@
       </c>
       <c r="I586" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIALIZADORA CELGREN SPA</t>
         </is>
       </c>
       <c r="J586" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.529.681-K</t>
         </is>
       </c>
       <c r="K586" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L586" t="inlineStr">
@@ -38149,13 +38145,13 @@
         </is>
       </c>
       <c r="M586" s="2" t="n">
-        <v>1124.42</v>
+        <v>6469.24</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="inlineStr">
         <is>
-          <t>1962-510-CM26</t>
+          <t>3615-116-CM26</t>
         </is>
       </c>
       <c r="B587" t="inlineStr">
@@ -38165,27 +38161,27 @@
       </c>
       <c r="C587" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D587" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E587" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F587" t="inlineStr">
         <is>
-          <t>61.004.012-8</t>
+          <t>69.041.100-8</t>
         </is>
       </c>
       <c r="G587" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>ILUSTRE MINICIPALIDAD DE COMBARBALA</t>
         </is>
       </c>
       <c r="H587" t="inlineStr">
@@ -38195,32 +38191,28 @@
       </c>
       <c r="I587" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>Comercial IBL SpA</t>
         </is>
       </c>
       <c r="J587" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
-        </is>
-      </c>
-      <c r="K587" t="inlineStr">
-        <is>
-          <t>Coquimbo</t>
-        </is>
-      </c>
+          <t>76.452.485-3</t>
+        </is>
+      </c>
+      <c r="K587" t="inlineStr"/>
       <c r="L587" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M587" s="2" t="n">
-        <v>979.21</v>
+        <v>5095.16</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="inlineStr">
         <is>
-          <t>2711-204-CM26</t>
+          <t>3511-284-CM26</t>
         </is>
       </c>
       <c r="B588" t="inlineStr">
@@ -38235,7 +38227,7 @@
       </c>
       <c r="D588" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E588" t="inlineStr">
@@ -38245,12 +38237,12 @@
       </c>
       <c r="F588" t="inlineStr">
         <is>
-          <t>69.040.700-0</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G588" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE OVALLE</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H588" t="inlineStr">
@@ -38279,13 +38271,13 @@
         </is>
       </c>
       <c r="M588" s="2" t="n">
-        <v>2345.64</v>
+        <v>3593.82</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="inlineStr">
         <is>
-          <t>2711-203-CM26</t>
+          <t>3712-531-CM26</t>
         </is>
       </c>
       <c r="B589" t="inlineStr">
@@ -38300,22 +38292,22 @@
       </c>
       <c r="D589" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="E589" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F589" t="inlineStr">
         <is>
-          <t>69.040.700-0</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G589" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE OVALLE</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H589" t="inlineStr">
@@ -38325,17 +38317,17 @@
       </c>
       <c r="I589" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J589" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K589" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L589" t="inlineStr">
@@ -38344,13 +38336,13 @@
         </is>
       </c>
       <c r="M589" s="2" t="n">
-        <v>4386.07</v>
+        <v>1124.42</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="inlineStr">
         <is>
-          <t>1057439-5145-CM26</t>
+          <t>1962-510-CM26</t>
         </is>
       </c>
       <c r="B590" t="inlineStr">
@@ -38365,7 +38357,7 @@
       </c>
       <c r="D590" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E590" t="inlineStr">
@@ -38375,12 +38367,12 @@
       </c>
       <c r="F590" t="inlineStr">
         <is>
-          <t>61.606.402-9</t>
+          <t>61.004.012-8</t>
         </is>
       </c>
       <c r="G590" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H590" t="inlineStr">
@@ -38390,28 +38382,32 @@
       </c>
       <c r="I590" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO VARGAS CASTILLO</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J590" t="inlineStr">
         <is>
-          <t>13.940.082-8</t>
-        </is>
-      </c>
-      <c r="K590" t="inlineStr"/>
+          <t>77.012.870-6</t>
+        </is>
+      </c>
+      <c r="K590" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L590" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M590" s="2" t="n">
-        <v>8251.700000000001</v>
+        <v>979.21</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="inlineStr">
         <is>
-          <t>2125-1600-CM26</t>
+          <t>2711-204-CM26</t>
         </is>
       </c>
       <c r="B591" t="inlineStr">
@@ -38426,22 +38422,22 @@
       </c>
       <c r="D591" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E591" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F591" t="inlineStr">
         <is>
-          <t>61.606.407-k</t>
+          <t>69.040.700-0</t>
         </is>
       </c>
       <c r="G591" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DR. HUMBERTO ELORZA CORTES</t>
+          <t>MUNICIPALIDAD DE OVALLE</t>
         </is>
       </c>
       <c r="H591" t="inlineStr">
@@ -38451,12 +38447,12 @@
       </c>
       <c r="I591" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>CASTILLA Y ARAGON SPA</t>
         </is>
       </c>
       <c r="J591" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.989.530-7</t>
         </is>
       </c>
       <c r="K591" t="inlineStr">
@@ -38470,13 +38466,13 @@
         </is>
       </c>
       <c r="M591" s="2" t="n">
-        <v>920.37</v>
+        <v>2345.64</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="inlineStr">
         <is>
-          <t>1346282-339-CM26</t>
+          <t>2711-203-CM26</t>
         </is>
       </c>
       <c r="B592" t="inlineStr">
@@ -38491,22 +38487,22 @@
       </c>
       <c r="D592" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E592" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F592" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>69.040.700-0</t>
         </is>
       </c>
       <c r="G592" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>MUNICIPALIDAD DE OVALLE</t>
         </is>
       </c>
       <c r="H592" t="inlineStr">
@@ -38535,13 +38531,13 @@
         </is>
       </c>
       <c r="M592" s="2" t="n">
-        <v>1058.58</v>
+        <v>4386.07</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="inlineStr">
         <is>
-          <t>3712-535-CM26</t>
+          <t>1057439-5145-CM26</t>
         </is>
       </c>
       <c r="B593" t="inlineStr">
@@ -38556,22 +38552,22 @@
       </c>
       <c r="D593" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="E593" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F593" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>61.606.402-9</t>
         </is>
       </c>
       <c r="G593" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
         </is>
       </c>
       <c r="H593" t="inlineStr">
@@ -38581,32 +38577,28 @@
       </c>
       <c r="I593" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>CARLOS ALBERTO VARGAS CASTILLO</t>
         </is>
       </c>
       <c r="J593" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
-        </is>
-      </c>
-      <c r="K593" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>13.940.082-8</t>
+        </is>
+      </c>
+      <c r="K593" t="inlineStr"/>
       <c r="L593" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M593" s="2" t="n">
-        <v>1190.13</v>
+        <v>8251.700000000001</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="inlineStr">
         <is>
-          <t>1574-159-CM26</t>
+          <t>2125-1600-CM26</t>
         </is>
       </c>
       <c r="B594" t="inlineStr">
@@ -38621,7 +38613,7 @@
       </c>
       <c r="D594" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="E594" t="inlineStr">
@@ -38631,12 +38623,12 @@
       </c>
       <c r="F594" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>61.606.407-k</t>
         </is>
       </c>
       <c r="G594" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DR. HUMBERTO ELORZA CORTES</t>
         </is>
       </c>
       <c r="H594" t="inlineStr">
@@ -38665,13 +38657,13 @@
         </is>
       </c>
       <c r="M594" s="2" t="n">
-        <v>1317.61</v>
+        <v>920.37</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="inlineStr">
         <is>
-          <t>1574-156-CM26</t>
+          <t>1346282-339-CM26</t>
         </is>
       </c>
       <c r="B595" t="inlineStr">
@@ -38686,7 +38678,7 @@
       </c>
       <c r="D595" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="E595" t="inlineStr">
@@ -38696,12 +38688,12 @@
       </c>
       <c r="F595" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G595" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H595" t="inlineStr">
@@ -38711,12 +38703,12 @@
       </c>
       <c r="I595" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J595" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K595" t="inlineStr">
@@ -38730,13 +38722,13 @@
         </is>
       </c>
       <c r="M595" s="2" t="n">
-        <v>1147.86</v>
+        <v>1058.58</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="inlineStr">
         <is>
-          <t>1574-155-CM26</t>
+          <t>3509-326-CM26</t>
         </is>
       </c>
       <c r="B596" t="inlineStr">
@@ -38751,22 +38743,22 @@
       </c>
       <c r="D596" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="E596" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F596" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G596" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H596" t="inlineStr">
@@ -38776,12 +38768,12 @@
       </c>
       <c r="I596" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>BAILEY GROUP SPA</t>
         </is>
       </c>
       <c r="J596" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>77.638.992-7</t>
         </is>
       </c>
       <c r="K596" t="inlineStr">
@@ -38795,13 +38787,13 @@
         </is>
       </c>
       <c r="M596" s="2" t="n">
-        <v>2142.43</v>
+        <v>2123.74</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="inlineStr">
         <is>
-          <t>1574-154-CM26</t>
+          <t>3712-535-CM26</t>
         </is>
       </c>
       <c r="B597" t="inlineStr">
@@ -38816,22 +38808,22 @@
       </c>
       <c r="D597" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="E597" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F597" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G597" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H597" t="inlineStr">
@@ -38841,12 +38833,12 @@
       </c>
       <c r="I597" t="inlineStr">
         <is>
-          <t>IMPORTADORA Y COMERCIALIZADORA JMMB SPA</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J597" t="inlineStr">
         <is>
-          <t>77.461.733-7</t>
+          <t>77.346.435-9</t>
         </is>
       </c>
       <c r="K597" t="inlineStr">
@@ -38860,13 +38852,13 @@
         </is>
       </c>
       <c r="M597" s="2" t="n">
-        <v>1701.69</v>
+        <v>1190.13</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="inlineStr">
         <is>
-          <t>1574-153-CM26</t>
+          <t>1574-159-CM26</t>
         </is>
       </c>
       <c r="B598" t="inlineStr">
@@ -38906,12 +38898,12 @@
       </c>
       <c r="I598" t="inlineStr">
         <is>
-          <t>IMPORTADORA Y COMERCIALIZADORA JMMB SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J598" t="inlineStr">
         <is>
-          <t>77.461.733-7</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K598" t="inlineStr">
@@ -38925,13 +38917,13 @@
         </is>
       </c>
       <c r="M598" s="2" t="n">
-        <v>3053.61</v>
+        <v>1317.61</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="inlineStr">
         <is>
-          <t>3265-417-CM26</t>
+          <t>1574-156-CM26</t>
         </is>
       </c>
       <c r="B599" t="inlineStr">
@@ -38951,17 +38943,17 @@
       </c>
       <c r="E599" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F599" t="inlineStr">
         <is>
-          <t>69.041.000-1</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G599" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RIO HURTADO</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H599" t="inlineStr">
@@ -38971,12 +38963,12 @@
       </c>
       <c r="I599" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA CUARENTA Y UNO SPA</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J599" t="inlineStr">
         <is>
-          <t>78.085.401-4</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K599" t="inlineStr">
@@ -38990,13 +38982,13 @@
         </is>
       </c>
       <c r="M599" s="2" t="n">
-        <v>1344.24</v>
+        <v>1147.86</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="inlineStr">
         <is>
-          <t>1574-158-CM26</t>
+          <t>1574-155-CM26</t>
         </is>
       </c>
       <c r="B600" t="inlineStr">
@@ -39036,12 +39028,12 @@
       </c>
       <c r="I600" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA CUARENTA Y UNO SPA</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J600" t="inlineStr">
         <is>
-          <t>78.085.401-4</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K600" t="inlineStr">
@@ -39055,13 +39047,13 @@
         </is>
       </c>
       <c r="M600" s="2" t="n">
-        <v>10317.27</v>
+        <v>2142.43</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="inlineStr">
         <is>
-          <t>1574-157-CM26</t>
+          <t>1574-154-CM26</t>
         </is>
       </c>
       <c r="B601" t="inlineStr">
@@ -39101,12 +39093,12 @@
       </c>
       <c r="I601" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA CUARENTA Y UNO SPA</t>
+          <t>IMPORTADORA Y COMERCIALIZADORA JMMB SPA</t>
         </is>
       </c>
       <c r="J601" t="inlineStr">
         <is>
-          <t>78.085.401-4</t>
+          <t>77.461.733-7</t>
         </is>
       </c>
       <c r="K601" t="inlineStr">
@@ -39120,13 +39112,13 @@
         </is>
       </c>
       <c r="M601" s="2" t="n">
-        <v>11365.81</v>
+        <v>1701.69</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="inlineStr">
         <is>
-          <t>1962-532-CM26</t>
+          <t>1574-153-CM26</t>
         </is>
       </c>
       <c r="B602" t="inlineStr">
@@ -39141,22 +39133,22 @@
       </c>
       <c r="D602" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="E602" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F602" t="inlineStr">
         <is>
-          <t>61.004.012-8</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G602" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H602" t="inlineStr">
@@ -39166,12 +39158,12 @@
       </c>
       <c r="I602" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA CUARENTA Y UNO SPA</t>
+          <t>IMPORTADORA Y COMERCIALIZADORA JMMB SPA</t>
         </is>
       </c>
       <c r="J602" t="inlineStr">
         <is>
-          <t>78.085.401-4</t>
+          <t>77.461.733-7</t>
         </is>
       </c>
       <c r="K602" t="inlineStr">
@@ -39185,13 +39177,13 @@
         </is>
       </c>
       <c r="M602" s="2" t="n">
-        <v>876.1</v>
+        <v>3053.61</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="inlineStr">
         <is>
-          <t>3712-550-CM26</t>
+          <t>3265-417-CM26</t>
         </is>
       </c>
       <c r="B603" t="inlineStr">
@@ -39206,7 +39198,7 @@
       </c>
       <c r="D603" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="E603" t="inlineStr">
@@ -39216,12 +39208,12 @@
       </c>
       <c r="F603" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>69.041.000-1</t>
         </is>
       </c>
       <c r="G603" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>I MUNICIPALIDAD DE RIO HURTADO</t>
         </is>
       </c>
       <c r="H603" t="inlineStr">
@@ -39231,12 +39223,12 @@
       </c>
       <c r="I603" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIALIZADORA CUARENTA Y UNO SPA</t>
         </is>
       </c>
       <c r="J603" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>78.085.401-4</t>
         </is>
       </c>
       <c r="K603" t="inlineStr">
@@ -39250,13 +39242,13 @@
         </is>
       </c>
       <c r="M603" s="2" t="n">
-        <v>817.5700000000001</v>
+        <v>1344.24</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="inlineStr">
         <is>
-          <t>3712-548-CM26</t>
+          <t>1574-158-CM26</t>
         </is>
       </c>
       <c r="B604" t="inlineStr">
@@ -39271,22 +39263,22 @@
       </c>
       <c r="D604" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="E604" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F604" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G604" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H604" t="inlineStr">
@@ -39296,17 +39288,17 @@
       </c>
       <c r="I604" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIALIZADORA CUARENTA Y UNO SPA</t>
         </is>
       </c>
       <c r="J604" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>78.085.401-4</t>
         </is>
       </c>
       <c r="K604" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L604" t="inlineStr">
@@ -39315,13 +39307,13 @@
         </is>
       </c>
       <c r="M604" s="2" t="n">
-        <v>1057.61</v>
+        <v>10317.27</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="inlineStr">
         <is>
-          <t>1057439-5257-CM26</t>
+          <t>1574-157-CM26</t>
         </is>
       </c>
       <c r="B605" t="inlineStr">
@@ -39336,7 +39328,7 @@
       </c>
       <c r="D605" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="E605" t="inlineStr">
@@ -39346,12 +39338,12 @@
       </c>
       <c r="F605" t="inlineStr">
         <is>
-          <t>61.606.402-9</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G605" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H605" t="inlineStr">
@@ -39361,28 +39353,32 @@
       </c>
       <c r="I605" t="inlineStr">
         <is>
-          <t>ROLAND VORWERK Y COMPANIA LIMITADA</t>
+          <t>COMERCIALIZADORA CUARENTA Y UNO SPA</t>
         </is>
       </c>
       <c r="J605" t="inlineStr">
         <is>
-          <t>78.178.530-k</t>
-        </is>
-      </c>
-      <c r="K605" t="inlineStr"/>
+          <t>78.085.401-4</t>
+        </is>
+      </c>
+      <c r="K605" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L605" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M605" s="2" t="n">
-        <v>2843.29</v>
+        <v>11365.81</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="inlineStr">
         <is>
-          <t>5416-837-CM26</t>
+          <t>1962-532-CM26</t>
         </is>
       </c>
       <c r="B606" t="inlineStr">
@@ -39397,7 +39393,7 @@
       </c>
       <c r="D606" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="E606" t="inlineStr">
@@ -39407,12 +39403,12 @@
       </c>
       <c r="F606" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>61.004.012-8</t>
         </is>
       </c>
       <c r="G606" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H606" t="inlineStr">
@@ -39422,17 +39418,17 @@
       </c>
       <c r="I606" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>COMERCIALIZADORA CUARENTA Y UNO SPA</t>
         </is>
       </c>
       <c r="J606" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>78.085.401-4</t>
         </is>
       </c>
       <c r="K606" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L606" t="inlineStr">
@@ -39441,13 +39437,13 @@
         </is>
       </c>
       <c r="M606" s="2" t="n">
-        <v>2047</v>
+        <v>876.1</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="inlineStr">
         <is>
-          <t>3712-549-CM26</t>
+          <t>3712-550-CM26</t>
         </is>
       </c>
       <c r="B607" t="inlineStr">
@@ -39462,7 +39458,7 @@
       </c>
       <c r="D607" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="E607" t="inlineStr">
@@ -39506,13 +39502,13 @@
         </is>
       </c>
       <c r="M607" s="2" t="n">
-        <v>841.66</v>
+        <v>817.5700000000001</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="inlineStr">
         <is>
-          <t>2711-217-CM26</t>
+          <t>3712-548-CM26</t>
         </is>
       </c>
       <c r="B608" t="inlineStr">
@@ -39527,22 +39523,22 @@
       </c>
       <c r="D608" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="E608" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F608" t="inlineStr">
         <is>
-          <t>69.040.700-0</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G608" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE OVALLE</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H608" t="inlineStr">
@@ -39571,13 +39567,13 @@
         </is>
       </c>
       <c r="M608" s="2" t="n">
-        <v>1144.17</v>
+        <v>1057.61</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="inlineStr">
         <is>
-          <t>2992-305-CM26</t>
+          <t>1057439-5257-CM26</t>
         </is>
       </c>
       <c r="B609" t="inlineStr">
@@ -39592,22 +39588,22 @@
       </c>
       <c r="D609" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="E609" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F609" t="inlineStr">
         <is>
-          <t>69.040.800-7</t>
+          <t>61.606.402-9</t>
         </is>
       </c>
       <c r="G609" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MONTEPATRIA</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
         </is>
       </c>
       <c r="H609" t="inlineStr">
@@ -39617,32 +39613,28 @@
       </c>
       <c r="I609" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>ROLAND VORWERK Y COMPANIA LIMITADA</t>
         </is>
       </c>
       <c r="J609" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
-        </is>
-      </c>
-      <c r="K609" t="inlineStr">
-        <is>
-          <t>Coquimbo</t>
-        </is>
-      </c>
+          <t>78.178.530-k</t>
+        </is>
+      </c>
+      <c r="K609" t="inlineStr"/>
       <c r="L609" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M609" s="2" t="n">
-        <v>1192.2</v>
+        <v>2843.29</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="inlineStr">
         <is>
-          <t>2450-854-CM26</t>
+          <t>5416-837-CM26</t>
         </is>
       </c>
       <c r="B610" t="inlineStr">
@@ -39657,22 +39649,22 @@
       </c>
       <c r="D610" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="E610" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F610" t="inlineStr">
         <is>
-          <t>69.040.100-2</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G610" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE LA SERENA</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H610" t="inlineStr">
@@ -39682,17 +39674,17 @@
       </c>
       <c r="I610" t="inlineStr">
         <is>
-          <t>BAILEY GROUP SPA</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J610" t="inlineStr">
         <is>
-          <t>77.638.992-7</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K610" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="L610" t="inlineStr">
@@ -39701,13 +39693,13 @@
         </is>
       </c>
       <c r="M610" s="2" t="n">
-        <v>11355.09</v>
+        <v>2047</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="inlineStr">
         <is>
-          <t>1962-556-CM26</t>
+          <t>3712-549-CM26</t>
         </is>
       </c>
       <c r="B611" t="inlineStr">
@@ -39722,22 +39714,22 @@
       </c>
       <c r="D611" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="E611" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F611" t="inlineStr">
         <is>
-          <t>61.004.012-8</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G611" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H611" t="inlineStr">
@@ -39766,13 +39758,13 @@
         </is>
       </c>
       <c r="M611" s="2" t="n">
-        <v>2715.35</v>
+        <v>841.66</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="inlineStr">
         <is>
-          <t>3712-561-CM26</t>
+          <t>2711-217-CM26</t>
         </is>
       </c>
       <c r="B612" t="inlineStr">
@@ -39787,7 +39779,7 @@
       </c>
       <c r="D612" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="E612" t="inlineStr">
@@ -39797,12 +39789,12 @@
       </c>
       <c r="F612" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>69.040.700-0</t>
         </is>
       </c>
       <c r="G612" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>MUNICIPALIDAD DE OVALLE</t>
         </is>
       </c>
       <c r="H612" t="inlineStr">
@@ -39812,17 +39804,17 @@
       </c>
       <c r="I612" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J612" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K612" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L612" t="inlineStr">
@@ -39831,13 +39823,13 @@
         </is>
       </c>
       <c r="M612" s="2" t="n">
-        <v>1447.99</v>
+        <v>1144.17</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="inlineStr">
         <is>
-          <t>4619-16-CM26</t>
+          <t>2992-305-CM26</t>
         </is>
       </c>
       <c r="B613" t="inlineStr">
@@ -39852,22 +39844,22 @@
       </c>
       <c r="D613" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="E613" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F613" t="inlineStr">
         <is>
-          <t>61.502.000-1</t>
+          <t>69.040.800-7</t>
         </is>
       </c>
       <c r="G613" t="inlineStr">
         <is>
-          <t>DIRECCION DEL TRABAJO</t>
+          <t>I MUNICIPALIDAD DE MONTEPATRIA</t>
         </is>
       </c>
       <c r="H613" t="inlineStr">
@@ -39877,17 +39869,17 @@
       </c>
       <c r="I613" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J613" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K613" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="L613" t="inlineStr">
@@ -39896,7 +39888,7 @@
         </is>
       </c>
       <c r="M613" s="2" t="n">
-        <v>3364.3</v>
+        <v>1192.2</v>
       </c>
     </row>
     <row r="614">
@@ -39922,7 +39914,7 @@
       </c>
       <c r="E614" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F614" t="inlineStr">
@@ -39967,7 +39959,7 @@
     <row r="615">
       <c r="A615" t="inlineStr">
         <is>
-          <t>3712-557-CM26</t>
+          <t>3712-561-CM26</t>
         </is>
       </c>
       <c r="B615" t="inlineStr">
@@ -39982,7 +39974,7 @@
       </c>
       <c r="D615" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="E615" t="inlineStr">
@@ -40026,13 +40018,13 @@
         </is>
       </c>
       <c r="M615" s="2" t="n">
-        <v>1638.09</v>
+        <v>1447.99</v>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="inlineStr">
         <is>
-          <t>3712-570-CM26</t>
+          <t>4619-16-CM26</t>
         </is>
       </c>
       <c r="B616" t="inlineStr">
@@ -40047,7 +40039,7 @@
       </c>
       <c r="D616" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="E616" t="inlineStr">
@@ -40057,12 +40049,12 @@
       </c>
       <c r="F616" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>61.502.000-1</t>
         </is>
       </c>
       <c r="G616" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>DIRECCION DEL TRABAJO</t>
         </is>
       </c>
       <c r="H616" t="inlineStr">
@@ -40091,13 +40083,13 @@
         </is>
       </c>
       <c r="M616" s="2" t="n">
-        <v>944</v>
+        <v>3364.3</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="inlineStr">
         <is>
-          <t>1242121-442-CM26</t>
+          <t>1962-556-CM26</t>
         </is>
       </c>
       <c r="B617" t="inlineStr">
@@ -40112,7 +40104,7 @@
       </c>
       <c r="D617" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="E617" t="inlineStr">
@@ -40122,12 +40114,12 @@
       </c>
       <c r="F617" t="inlineStr">
         <is>
-          <t>61.606.404-5</t>
+          <t>61.004.012-8</t>
         </is>
       </c>
       <c r="G617" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE O</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H617" t="inlineStr">
@@ -40137,17 +40129,17 @@
       </c>
       <c r="I617" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J617" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K617" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L617" t="inlineStr">
@@ -40156,13 +40148,13 @@
         </is>
       </c>
       <c r="M617" s="2" t="n">
-        <v>3925.54</v>
+        <v>2715.35</v>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="inlineStr">
         <is>
-          <t>2711-226-CM26</t>
+          <t>2450-854-CM26</t>
         </is>
       </c>
       <c r="B618" t="inlineStr">
@@ -40177,22 +40169,22 @@
       </c>
       <c r="D618" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="E618" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F618" t="inlineStr">
         <is>
-          <t>69.040.700-0</t>
+          <t>69.040.100-2</t>
         </is>
       </c>
       <c r="G618" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE OVALLE</t>
+          <t>ILUSTRE MUNICIPALIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H618" t="inlineStr">
@@ -40221,13 +40213,13 @@
         </is>
       </c>
       <c r="M618" s="2" t="n">
-        <v>878.9299999999999</v>
+        <v>11355.09</v>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="inlineStr">
         <is>
-          <t>2711-225-CM26</t>
+          <t>3712-557-CM26</t>
         </is>
       </c>
       <c r="B619" t="inlineStr">
@@ -40242,22 +40234,22 @@
       </c>
       <c r="D619" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="E619" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F619" t="inlineStr">
         <is>
-          <t>69.040.700-0</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G619" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE OVALLE</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H619" t="inlineStr">
@@ -40267,12 +40259,12 @@
       </c>
       <c r="I619" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J619" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K619" t="inlineStr">
@@ -40286,13 +40278,13 @@
         </is>
       </c>
       <c r="M619" s="2" t="n">
-        <v>2343.25</v>
+        <v>1638.09</v>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="inlineStr">
         <is>
-          <t>3511-297-CM26</t>
+          <t>3712-570-CM26</t>
         </is>
       </c>
       <c r="B620" t="inlineStr">
@@ -40307,22 +40299,22 @@
       </c>
       <c r="D620" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="E620" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F620" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G620" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H620" t="inlineStr">
@@ -40332,17 +40324,17 @@
       </c>
       <c r="I620" t="inlineStr">
         <is>
-          <t>CASTILLA Y ARAGON SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J620" t="inlineStr">
         <is>
-          <t>96.989.530-7</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K620" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L620" t="inlineStr">
@@ -40351,13 +40343,13 @@
         </is>
       </c>
       <c r="M620" s="2" t="n">
-        <v>1627.53</v>
+        <v>944</v>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="inlineStr">
         <is>
-          <t>1574-234-CM26</t>
+          <t>1242121-442-CM26</t>
         </is>
       </c>
       <c r="B621" t="inlineStr">
@@ -40372,7 +40364,7 @@
       </c>
       <c r="D621" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="E621" t="inlineStr">
@@ -40382,12 +40374,12 @@
       </c>
       <c r="F621" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>61.606.404-5</t>
         </is>
       </c>
       <c r="G621" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE O</t>
         </is>
       </c>
       <c r="H621" t="inlineStr">
@@ -40397,17 +40389,17 @@
       </c>
       <c r="I621" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA CUARENTA Y UNO SPA</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J621" t="inlineStr">
         <is>
-          <t>78.085.401-4</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K621" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="L621" t="inlineStr">
@@ -40416,13 +40408,13 @@
         </is>
       </c>
       <c r="M621" s="2" t="n">
-        <v>7170.29</v>
+        <v>3925.54</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="inlineStr">
         <is>
-          <t>1230663-155-CM26</t>
+          <t>2711-226-CM26</t>
         </is>
       </c>
       <c r="B622" t="inlineStr">
@@ -40437,22 +40429,22 @@
       </c>
       <c r="D622" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="E622" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F622" t="inlineStr">
         <is>
-          <t>65.100.165-k</t>
+          <t>69.040.700-0</t>
         </is>
       </c>
       <c r="G622" t="inlineStr">
         <is>
-          <t>CORPORACION CULTURAL MUNICIPAL DE VICUNA</t>
+          <t>MUNICIPALIDAD DE OVALLE</t>
         </is>
       </c>
       <c r="H622" t="inlineStr">
@@ -40462,17 +40454,17 @@
       </c>
       <c r="I622" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>BAILEY GROUP SPA</t>
         </is>
       </c>
       <c r="J622" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.638.992-7</t>
         </is>
       </c>
       <c r="K622" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L622" t="inlineStr">
@@ -40481,13 +40473,13 @@
         </is>
       </c>
       <c r="M622" s="2" t="n">
-        <v>804.72</v>
+        <v>878.9299999999999</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="inlineStr">
         <is>
-          <t>1962-582-CM26</t>
+          <t>2711-225-CM26</t>
         </is>
       </c>
       <c r="B623" t="inlineStr">
@@ -40502,7 +40494,7 @@
       </c>
       <c r="D623" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="E623" t="inlineStr">
@@ -40512,12 +40504,12 @@
       </c>
       <c r="F623" t="inlineStr">
         <is>
-          <t>61.004.012-8</t>
+          <t>69.040.700-0</t>
         </is>
       </c>
       <c r="G623" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>MUNICIPALIDAD DE OVALLE</t>
         </is>
       </c>
       <c r="H623" t="inlineStr">
@@ -40527,17 +40519,17 @@
       </c>
       <c r="I623" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J623" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K623" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L623" t="inlineStr">
@@ -40546,13 +40538,13 @@
         </is>
       </c>
       <c r="M623" s="2" t="n">
-        <v>1279.6</v>
+        <v>2343.25</v>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="inlineStr">
         <is>
-          <t>3712-583-CM26</t>
+          <t>3511-297-CM26</t>
         </is>
       </c>
       <c r="B624" t="inlineStr">
@@ -40567,22 +40559,22 @@
       </c>
       <c r="D624" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="E624" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F624" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G624" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H624" t="inlineStr">
@@ -40592,12 +40584,12 @@
       </c>
       <c r="I624" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>CASTILLA Y ARAGON SPA</t>
         </is>
       </c>
       <c r="J624" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.989.530-7</t>
         </is>
       </c>
       <c r="K624" t="inlineStr">
@@ -40611,13 +40603,13 @@
         </is>
       </c>
       <c r="M624" s="2" t="n">
-        <v>1270.68</v>
+        <v>1627.53</v>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="inlineStr">
         <is>
-          <t>707418-117-CM26</t>
+          <t>1574-234-CM26</t>
         </is>
       </c>
       <c r="B625" t="inlineStr">
@@ -40627,12 +40619,12 @@
       </c>
       <c r="C625" t="inlineStr">
         <is>
-          <t>sep-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D625" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="E625" t="inlineStr">
@@ -40642,12 +40634,12 @@
       </c>
       <c r="F625" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G625" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H625" t="inlineStr">
@@ -40657,17 +40649,17 @@
       </c>
       <c r="I625" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>COMERCIALIZADORA CUARENTA Y UNO SPA</t>
         </is>
       </c>
       <c r="J625" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>78.085.401-4</t>
         </is>
       </c>
       <c r="K625" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L625" t="inlineStr">
@@ -40676,13 +40668,13 @@
         </is>
       </c>
       <c r="M625" s="2" t="n">
-        <v>12092.39</v>
+        <v>7170.29</v>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="inlineStr">
         <is>
-          <t>1962-604-CM26</t>
+          <t>1230663-155-CM26</t>
         </is>
       </c>
       <c r="B626" t="inlineStr">
@@ -40692,12 +40684,12 @@
       </c>
       <c r="C626" t="inlineStr">
         <is>
-          <t>sep-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D626" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="E626" t="inlineStr">
@@ -40707,12 +40699,12 @@
       </c>
       <c r="F626" t="inlineStr">
         <is>
-          <t>61.004.012-8</t>
+          <t>65.100.165-k</t>
         </is>
       </c>
       <c r="G626" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>CORPORACION CULTURAL MUNICIPAL DE VICUNA</t>
         </is>
       </c>
       <c r="H626" t="inlineStr">
@@ -40722,17 +40714,17 @@
       </c>
       <c r="I626" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J626" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K626" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L626" t="inlineStr">
@@ -40741,13 +40733,13 @@
         </is>
       </c>
       <c r="M626" s="2" t="n">
-        <v>771.13</v>
+        <v>804.72</v>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="inlineStr">
         <is>
-          <t>1057439-5685-CM26</t>
+          <t>1962-582-CM26</t>
         </is>
       </c>
       <c r="B627" t="inlineStr">
@@ -40757,12 +40749,12 @@
       </c>
       <c r="C627" t="inlineStr">
         <is>
-          <t>sep-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D627" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="E627" t="inlineStr">
@@ -40772,12 +40764,12 @@
       </c>
       <c r="F627" t="inlineStr">
         <is>
-          <t>61.606.402-9</t>
+          <t>61.004.012-8</t>
         </is>
       </c>
       <c r="G627" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H627" t="inlineStr">
@@ -40787,28 +40779,32 @@
       </c>
       <c r="I627" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO VARGAS CASTILLO</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J627" t="inlineStr">
         <is>
-          <t>13.940.082-8</t>
-        </is>
-      </c>
-      <c r="K627" t="inlineStr"/>
+          <t>77.012.870-6</t>
+        </is>
+      </c>
+      <c r="K627" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L627" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M627" s="2" t="n">
-        <v>7381.49</v>
+        <v>1279.6</v>
       </c>
     </row>
     <row r="628">
       <c r="A628" t="inlineStr">
         <is>
-          <t>1057439-5722-CM26</t>
+          <t>3712-583-CM26</t>
         </is>
       </c>
       <c r="B628" t="inlineStr">
@@ -40818,12 +40814,12 @@
       </c>
       <c r="C628" t="inlineStr">
         <is>
-          <t>sep-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D628" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="E628" t="inlineStr">
@@ -40833,12 +40829,12 @@
       </c>
       <c r="F628" t="inlineStr">
         <is>
-          <t>61.606.402-9</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G628" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H628" t="inlineStr">
@@ -40848,28 +40844,32 @@
       </c>
       <c r="I628" t="inlineStr">
         <is>
-          <t>ROLAND VORWERK Y COMPANIA LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J628" t="inlineStr">
         <is>
-          <t>78.178.530-k</t>
-        </is>
-      </c>
-      <c r="K628" t="inlineStr"/>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K628" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L628" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M628" s="2" t="n">
-        <v>3243.97</v>
+        <v>1270.68</v>
       </c>
     </row>
     <row r="629">
       <c r="A629" t="inlineStr">
         <is>
-          <t>3712-565-CM26</t>
+          <t>707418-117-CM26</t>
         </is>
       </c>
       <c r="B629" t="inlineStr">
@@ -40884,7 +40884,7 @@
       </c>
       <c r="D629" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="E629" t="inlineStr">
@@ -40894,12 +40894,12 @@
       </c>
       <c r="F629" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G629" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H629" t="inlineStr">
@@ -40909,17 +40909,17 @@
       </c>
       <c r="I629" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J629" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K629" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="L629" t="inlineStr">
@@ -40928,13 +40928,13 @@
         </is>
       </c>
       <c r="M629" s="2" t="n">
-        <v>1880.11</v>
+        <v>12092.39</v>
       </c>
     </row>
     <row r="630">
       <c r="A630" t="inlineStr">
         <is>
-          <t>3511-316-CM26</t>
+          <t>1962-604-CM26</t>
         </is>
       </c>
       <c r="B630" t="inlineStr">
@@ -40949,22 +40949,22 @@
       </c>
       <c r="D630" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="E630" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F630" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>61.004.012-8</t>
         </is>
       </c>
       <c r="G630" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H630" t="inlineStr">
@@ -40974,17 +40974,17 @@
       </c>
       <c r="I630" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J630" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.346.435-9</t>
         </is>
       </c>
       <c r="K630" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L630" t="inlineStr">
@@ -40993,13 +40993,13 @@
         </is>
       </c>
       <c r="M630" s="2" t="n">
-        <v>1151.54</v>
+        <v>771.13</v>
       </c>
     </row>
     <row r="631">
       <c r="A631" t="inlineStr">
         <is>
-          <t>3714-234-CM26</t>
+          <t>1057439-5685-CM26</t>
         </is>
       </c>
       <c r="B631" t="inlineStr">
@@ -41014,7 +41014,7 @@
       </c>
       <c r="D631" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="E631" t="inlineStr">
@@ -41024,12 +41024,12 @@
       </c>
       <c r="F631" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>61.606.402-9</t>
         </is>
       </c>
       <c r="G631" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
         </is>
       </c>
       <c r="H631" t="inlineStr">
@@ -41039,32 +41039,28 @@
       </c>
       <c r="I631" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>CARLOS ALBERTO VARGAS CASTILLO</t>
         </is>
       </c>
       <c r="J631" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
-        </is>
-      </c>
-      <c r="K631" t="inlineStr">
-        <is>
-          <t>Antofagasta</t>
-        </is>
-      </c>
+          <t>13.940.082-8</t>
+        </is>
+      </c>
+      <c r="K631" t="inlineStr"/>
       <c r="L631" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M631" s="2" t="n">
-        <v>936.13</v>
+        <v>7381.49</v>
       </c>
     </row>
     <row r="632">
       <c r="A632" t="inlineStr">
         <is>
-          <t>2125-1800-CM26</t>
+          <t>1057439-5722-CM26</t>
         </is>
       </c>
       <c r="B632" t="inlineStr">
@@ -41079,7 +41075,7 @@
       </c>
       <c r="D632" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="E632" t="inlineStr">
@@ -41089,12 +41085,12 @@
       </c>
       <c r="F632" t="inlineStr">
         <is>
-          <t>61.606.407-k</t>
+          <t>61.606.402-9</t>
         </is>
       </c>
       <c r="G632" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DR. HUMBERTO ELORZA CORTES</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
         </is>
       </c>
       <c r="H632" t="inlineStr">
@@ -41104,32 +41100,28 @@
       </c>
       <c r="I632" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>ROLAND VORWERK Y COMPANIA LIMITADA</t>
         </is>
       </c>
       <c r="J632" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
-        </is>
-      </c>
-      <c r="K632" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>78.178.530-k</t>
+        </is>
+      </c>
+      <c r="K632" t="inlineStr"/>
       <c r="L632" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M632" s="2" t="n">
-        <v>1098.27</v>
+        <v>3243.97</v>
       </c>
     </row>
     <row r="633">
       <c r="A633" t="inlineStr">
         <is>
-          <t>1962-615-CM26</t>
+          <t>3712-565-CM26</t>
         </is>
       </c>
       <c r="B633" t="inlineStr">
@@ -41144,7 +41136,7 @@
       </c>
       <c r="D633" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="E633" t="inlineStr">
@@ -41154,12 +41146,12 @@
       </c>
       <c r="F633" t="inlineStr">
         <is>
-          <t>61.004.012-8</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G633" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H633" t="inlineStr">
@@ -41169,17 +41161,17 @@
       </c>
       <c r="I633" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J633" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>77.346.435-9</t>
         </is>
       </c>
       <c r="K633" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L633" t="inlineStr">
@@ -41188,13 +41180,13 @@
         </is>
       </c>
       <c r="M633" s="2" t="n">
-        <v>1299.72</v>
+        <v>1880.11</v>
       </c>
     </row>
     <row r="634">
       <c r="A634" t="inlineStr">
         <is>
-          <t>2997-108-CM26</t>
+          <t>3511-316-CM26</t>
         </is>
       </c>
       <c r="B634" t="inlineStr">
@@ -41209,7 +41201,7 @@
       </c>
       <c r="D634" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="E634" t="inlineStr">
@@ -41219,12 +41211,12 @@
       </c>
       <c r="F634" t="inlineStr">
         <is>
-          <t>69.040.800-7</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G634" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MONTEPATRIA</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H634" t="inlineStr">
@@ -41253,13 +41245,13 @@
         </is>
       </c>
       <c r="M634" s="2" t="n">
-        <v>1313.52</v>
+        <v>1151.54</v>
       </c>
     </row>
     <row r="635">
       <c r="A635" t="inlineStr">
         <is>
-          <t>1352-76-CM26</t>
+          <t>3714-234-CM26</t>
         </is>
       </c>
       <c r="B635" t="inlineStr">
@@ -41274,22 +41266,22 @@
       </c>
       <c r="D635" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="E635" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F635" t="inlineStr">
         <is>
-          <t>61.002.010-0</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G635" t="inlineStr">
         <is>
-          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H635" t="inlineStr">
@@ -41299,17 +41291,17 @@
       </c>
       <c r="I635" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J635" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K635" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L635" t="inlineStr">
@@ -41318,13 +41310,13 @@
         </is>
       </c>
       <c r="M635" s="2" t="n">
-        <v>2760.88</v>
+        <v>936.13</v>
       </c>
     </row>
     <row r="636">
       <c r="A636" t="inlineStr">
         <is>
-          <t>1352-75-CM26</t>
+          <t>2125-1800-CM26</t>
         </is>
       </c>
       <c r="B636" t="inlineStr">
@@ -41339,22 +41331,22 @@
       </c>
       <c r="D636" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="E636" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F636" t="inlineStr">
         <is>
-          <t>61.002.010-0</t>
+          <t>61.606.407-k</t>
         </is>
       </c>
       <c r="G636" t="inlineStr">
         <is>
-          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DR. HUMBERTO ELORZA CORTES</t>
         </is>
       </c>
       <c r="H636" t="inlineStr">
@@ -41364,17 +41356,17 @@
       </c>
       <c r="I636" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J636" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K636" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L636" t="inlineStr">
@@ -41383,13 +41375,13 @@
         </is>
       </c>
       <c r="M636" s="2" t="n">
-        <v>2435.28</v>
+        <v>1098.27</v>
       </c>
     </row>
     <row r="637">
       <c r="A637" t="inlineStr">
         <is>
-          <t>3593-349-CM26</t>
+          <t>1962-615-CM26</t>
         </is>
       </c>
       <c r="B637" t="inlineStr">
@@ -41404,22 +41396,22 @@
       </c>
       <c r="D637" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="E637" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F637" t="inlineStr">
         <is>
-          <t>69.041.100-8</t>
+          <t>61.004.012-8</t>
         </is>
       </c>
       <c r="G637" t="inlineStr">
         <is>
-          <t>ILUSTRE MINICIPALIDAD DE COMBARBALA</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H637" t="inlineStr">
@@ -41448,13 +41440,13 @@
         </is>
       </c>
       <c r="M637" s="2" t="n">
-        <v>1288.26</v>
+        <v>1299.72</v>
       </c>
     </row>
     <row r="638">
       <c r="A638" t="inlineStr">
         <is>
-          <t>3712-636-CM26</t>
+          <t>2997-108-CM26</t>
         </is>
       </c>
       <c r="B638" t="inlineStr">
@@ -41469,22 +41461,22 @@
       </c>
       <c r="D638" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E638" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F638" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>69.040.800-7</t>
         </is>
       </c>
       <c r="G638" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>I MUNICIPALIDAD DE MONTEPATRIA</t>
         </is>
       </c>
       <c r="H638" t="inlineStr">
@@ -41494,17 +41486,17 @@
       </c>
       <c r="I638" t="inlineStr">
         <is>
-          <t>BAILEY GROUP SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J638" t="inlineStr">
         <is>
-          <t>77.638.992-7</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K638" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L638" t="inlineStr">
@@ -41513,13 +41505,13 @@
         </is>
       </c>
       <c r="M638" s="2" t="n">
-        <v>1465.42</v>
+        <v>1313.52</v>
       </c>
     </row>
     <row r="639">
       <c r="A639" t="inlineStr">
         <is>
-          <t>3511-300-CM26</t>
+          <t>1352-76-CM26</t>
         </is>
       </c>
       <c r="B639" t="inlineStr">
@@ -41534,7 +41526,7 @@
       </c>
       <c r="D639" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E639" t="inlineStr">
@@ -41544,12 +41536,12 @@
       </c>
       <c r="F639" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>61.002.010-0</t>
         </is>
       </c>
       <c r="G639" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
         </is>
       </c>
       <c r="H639" t="inlineStr">
@@ -41559,17 +41551,17 @@
       </c>
       <c r="I639" t="inlineStr">
         <is>
-          <t>COMERCIAL VALLE SPA</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J639" t="inlineStr">
         <is>
-          <t>77.988.165-2</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K639" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="L639" t="inlineStr">
@@ -41578,13 +41570,13 @@
         </is>
       </c>
       <c r="M639" s="2" t="n">
-        <v>836.36</v>
+        <v>2760.88</v>
       </c>
     </row>
     <row r="640">
       <c r="A640" t="inlineStr">
         <is>
-          <t>2708-513-CM26</t>
+          <t>1352-75-CM26</t>
         </is>
       </c>
       <c r="B640" t="inlineStr">
@@ -41599,7 +41591,7 @@
       </c>
       <c r="D640" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E640" t="inlineStr">
@@ -41609,12 +41601,12 @@
       </c>
       <c r="F640" t="inlineStr">
         <is>
-          <t>69.040.700-0</t>
+          <t>61.002.010-0</t>
         </is>
       </c>
       <c r="G640" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE OVALLE</t>
+          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
         </is>
       </c>
       <c r="H640" t="inlineStr">
@@ -41624,17 +41616,17 @@
       </c>
       <c r="I640" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J640" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K640" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="L640" t="inlineStr">
@@ -41643,13 +41635,13 @@
         </is>
       </c>
       <c r="M640" s="2" t="n">
-        <v>1541.16</v>
+        <v>2435.28</v>
       </c>
     </row>
     <row r="641">
       <c r="A641" t="inlineStr">
         <is>
-          <t>3511-365-CM26</t>
+          <t>3593-349-CM26</t>
         </is>
       </c>
       <c r="B641" t="inlineStr">
@@ -41664,7 +41656,7 @@
       </c>
       <c r="D641" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E641" t="inlineStr">
@@ -41674,12 +41666,12 @@
       </c>
       <c r="F641" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>69.041.100-8</t>
         </is>
       </c>
       <c r="G641" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>ILUSTRE MINICIPALIDAD DE COMBARBALA</t>
         </is>
       </c>
       <c r="H641" t="inlineStr">
@@ -41689,17 +41681,17 @@
       </c>
       <c r="I641" t="inlineStr">
         <is>
-          <t>CASTILLA Y ARAGON SPA</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J641" t="inlineStr">
         <is>
-          <t>96.989.530-7</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K641" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="L641" t="inlineStr">
@@ -41708,13 +41700,13 @@
         </is>
       </c>
       <c r="M641" s="2" t="n">
-        <v>3820.84</v>
+        <v>1288.26</v>
       </c>
     </row>
     <row r="642">
       <c r="A642" t="inlineStr">
         <is>
-          <t>624-217-CM26</t>
+          <t>3712-636-CM26</t>
         </is>
       </c>
       <c r="B642" t="inlineStr">
@@ -41729,7 +41721,7 @@
       </c>
       <c r="D642" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E642" t="inlineStr">
@@ -41739,12 +41731,12 @@
       </c>
       <c r="F642" t="inlineStr">
         <is>
-          <t>72.225.700-6</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G642" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL IV REGION COQUIMBO</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H642" t="inlineStr">
@@ -41754,17 +41746,17 @@
       </c>
       <c r="I642" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>BAILEY GROUP SPA</t>
         </is>
       </c>
       <c r="J642" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.638.992-7</t>
         </is>
       </c>
       <c r="K642" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L642" t="inlineStr">
@@ -41773,13 +41765,13 @@
         </is>
       </c>
       <c r="M642" s="2" t="n">
-        <v>4516.79</v>
+        <v>1465.42</v>
       </c>
     </row>
     <row r="643">
       <c r="A643" t="inlineStr">
         <is>
-          <t>1057438-265-CM26</t>
+          <t>3511-300-CM26</t>
         </is>
       </c>
       <c r="B643" t="inlineStr">
@@ -41794,22 +41786,22 @@
       </c>
       <c r="D643" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E643" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F643" t="inlineStr">
         <is>
-          <t>61.606.401-0</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G643" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL VICUNA</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H643" t="inlineStr">
@@ -41819,12 +41811,12 @@
       </c>
       <c r="I643" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>COMERCIAL VALLE SPA</t>
         </is>
       </c>
       <c r="J643" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>77.988.165-2</t>
         </is>
       </c>
       <c r="K643" t="inlineStr">
@@ -41838,13 +41830,13 @@
         </is>
       </c>
       <c r="M643" s="2" t="n">
-        <v>747.9299999999999</v>
+        <v>836.36</v>
       </c>
     </row>
     <row r="644">
       <c r="A644" t="inlineStr">
         <is>
-          <t>1673-223-CM26</t>
+          <t>2708-513-CM26</t>
         </is>
       </c>
       <c r="B644" t="inlineStr">
@@ -41864,17 +41856,17 @@
       </c>
       <c r="E644" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F644" t="inlineStr">
         <is>
-          <t>61.606.401-0</t>
+          <t>69.040.700-0</t>
         </is>
       </c>
       <c r="G644" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL VICUNA</t>
+          <t>MUNICIPALIDAD DE OVALLE</t>
         </is>
       </c>
       <c r="H644" t="inlineStr">
@@ -41884,17 +41876,17 @@
       </c>
       <c r="I644" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J644" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K644" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L644" t="inlineStr">
@@ -41903,13 +41895,13 @@
         </is>
       </c>
       <c r="M644" s="2" t="n">
-        <v>748.35</v>
+        <v>1541.16</v>
       </c>
     </row>
     <row r="645">
       <c r="A645" t="inlineStr">
         <is>
-          <t>2446-1140-CM26</t>
+          <t>3511-365-CM26</t>
         </is>
       </c>
       <c r="B645" t="inlineStr">
@@ -41924,22 +41916,22 @@
       </c>
       <c r="D645" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E645" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F645" t="inlineStr">
         <is>
-          <t>69.040.300-5</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G645" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COQUIMBO</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H645" t="inlineStr">
@@ -41949,12 +41941,12 @@
       </c>
       <c r="I645" t="inlineStr">
         <is>
-          <t>BAILEY GROUP SPA</t>
+          <t>CASTILLA Y ARAGON SPA</t>
         </is>
       </c>
       <c r="J645" t="inlineStr">
         <is>
-          <t>77.638.992-7</t>
+          <t>96.989.530-7</t>
         </is>
       </c>
       <c r="K645" t="inlineStr">
@@ -41968,13 +41960,13 @@
         </is>
       </c>
       <c r="M645" s="2" t="n">
-        <v>2859.18</v>
+        <v>3820.84</v>
       </c>
     </row>
     <row r="646">
       <c r="A646" t="inlineStr">
         <is>
-          <t>1289649-74-CM26</t>
+          <t>624-217-CM26</t>
         </is>
       </c>
       <c r="B646" t="inlineStr">
@@ -41989,7 +41981,7 @@
       </c>
       <c r="D646" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E646" t="inlineStr">
@@ -41999,12 +41991,12 @@
       </c>
       <c r="F646" t="inlineStr">
         <is>
-          <t>60.905.000-4</t>
+          <t>72.225.700-6</t>
         </is>
       </c>
       <c r="G646" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
+          <t>GOBIERNO REGIONAL IV REGION COQUIMBO</t>
         </is>
       </c>
       <c r="H646" t="inlineStr">
@@ -42014,17 +42006,17 @@
       </c>
       <c r="I646" t="inlineStr">
         <is>
-          <t>RUSTIC PINK SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J646" t="inlineStr">
         <is>
-          <t>77.649.678-2</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K646" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L646" t="inlineStr">
@@ -42033,13 +42025,13 @@
         </is>
       </c>
       <c r="M646" s="2" t="n">
-        <v>850.6799999999999</v>
+        <v>4516.79</v>
       </c>
     </row>
     <row r="647">
       <c r="A647" t="inlineStr">
         <is>
-          <t>1962-650-CM26</t>
+          <t>1057438-265-CM26</t>
         </is>
       </c>
       <c r="B647" t="inlineStr">
@@ -42054,7 +42046,7 @@
       </c>
       <c r="D647" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E647" t="inlineStr">
@@ -42064,12 +42056,12 @@
       </c>
       <c r="F647" t="inlineStr">
         <is>
-          <t>61.004.012-8</t>
+          <t>61.606.401-0</t>
         </is>
       </c>
       <c r="G647" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL VICUNA</t>
         </is>
       </c>
       <c r="H647" t="inlineStr">
@@ -42079,17 +42071,17 @@
       </c>
       <c r="I647" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J647" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K647" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L647" t="inlineStr">
@@ -42098,13 +42090,13 @@
         </is>
       </c>
       <c r="M647" s="2" t="n">
-        <v>744.27</v>
+        <v>747.9299999999999</v>
       </c>
     </row>
     <row r="648">
       <c r="A648" t="inlineStr">
         <is>
-          <t>5416-1017-CM26</t>
+          <t>1673-223-CM26</t>
         </is>
       </c>
       <c r="B648" t="inlineStr">
@@ -42119,7 +42111,7 @@
       </c>
       <c r="D648" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E648" t="inlineStr">
@@ -42129,12 +42121,12 @@
       </c>
       <c r="F648" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>61.606.401-0</t>
         </is>
       </c>
       <c r="G648" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL VICUNA</t>
         </is>
       </c>
       <c r="H648" t="inlineStr">
@@ -42144,17 +42136,17 @@
       </c>
       <c r="I648" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J648" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K648" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L648" t="inlineStr">
@@ -42163,13 +42155,13 @@
         </is>
       </c>
       <c r="M648" s="2" t="n">
-        <v>1396.42</v>
+        <v>748.35</v>
       </c>
     </row>
     <row r="649">
       <c r="A649" t="inlineStr">
         <is>
-          <t>3713-86-CM26</t>
+          <t>2446-1140-CM26</t>
         </is>
       </c>
       <c r="B649" t="inlineStr">
@@ -42179,27 +42171,27 @@
       </c>
       <c r="C649" t="inlineStr">
         <is>
-          <t>oct-2026</t>
+          <t>sep-2026</t>
         </is>
       </c>
       <c r="D649" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E649" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F649" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>69.040.300-5</t>
         </is>
       </c>
       <c r="G649" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>I MUNICIPALIDAD DE COQUIMBO</t>
         </is>
       </c>
       <c r="H649" t="inlineStr">
@@ -42209,12 +42201,12 @@
       </c>
       <c r="I649" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>BAILEY GROUP SPA</t>
         </is>
       </c>
       <c r="J649" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.638.992-7</t>
         </is>
       </c>
       <c r="K649" t="inlineStr">
@@ -42228,13 +42220,13 @@
         </is>
       </c>
       <c r="M649" s="2" t="n">
-        <v>2647.39</v>
+        <v>2859.18</v>
       </c>
     </row>
     <row r="650">
       <c r="A650" t="inlineStr">
         <is>
-          <t>3593-364-CM26</t>
+          <t>1289649-74-CM26</t>
         </is>
       </c>
       <c r="B650" t="inlineStr">
@@ -42244,27 +42236,27 @@
       </c>
       <c r="C650" t="inlineStr">
         <is>
-          <t>oct-2026</t>
+          <t>sep-2026</t>
         </is>
       </c>
       <c r="D650" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E650" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F650" t="inlineStr">
         <is>
-          <t>69.041.100-8</t>
+          <t>60.905.000-4</t>
         </is>
       </c>
       <c r="G650" t="inlineStr">
         <is>
-          <t>ILUSTRE MINICIPALIDAD DE COMBARBALA</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H650" t="inlineStr">
@@ -42274,17 +42266,17 @@
       </c>
       <c r="I650" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>RUSTIC PINK SPA</t>
         </is>
       </c>
       <c r="J650" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>77.649.678-2</t>
         </is>
       </c>
       <c r="K650" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L650" t="inlineStr">
@@ -42293,13 +42285,13 @@
         </is>
       </c>
       <c r="M650" s="2" t="n">
-        <v>776.59</v>
+        <v>850.6799999999999</v>
       </c>
     </row>
     <row r="651">
       <c r="A651" t="inlineStr">
         <is>
-          <t>2288-840-CM26</t>
+          <t>1962-650-CM26</t>
         </is>
       </c>
       <c r="B651" t="inlineStr">
@@ -42309,12 +42301,12 @@
       </c>
       <c r="C651" t="inlineStr">
         <is>
-          <t>oct-2026</t>
+          <t>sep-2026</t>
         </is>
       </c>
       <c r="D651" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E651" t="inlineStr">
@@ -42324,12 +42316,12 @@
       </c>
       <c r="F651" t="inlineStr">
         <is>
-          <t>69.041.300-0</t>
+          <t>61.004.012-8</t>
         </is>
       </c>
       <c r="G651" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CANELA</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H651" t="inlineStr">
@@ -42339,17 +42331,17 @@
       </c>
       <c r="I651" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J651" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K651" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L651" t="inlineStr">
@@ -42358,13 +42350,13 @@
         </is>
       </c>
       <c r="M651" s="2" t="n">
-        <v>1916.47</v>
+        <v>744.27</v>
       </c>
     </row>
     <row r="652">
       <c r="A652" t="inlineStr">
         <is>
-          <t>3511-387-CM26</t>
+          <t>5416-1017-CM26</t>
         </is>
       </c>
       <c r="B652" t="inlineStr">
@@ -42374,27 +42366,27 @@
       </c>
       <c r="C652" t="inlineStr">
         <is>
-          <t>oct-2026</t>
+          <t>sep-2026</t>
         </is>
       </c>
       <c r="D652" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E652" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F652" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G652" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H652" t="inlineStr">
@@ -42404,12 +42396,12 @@
       </c>
       <c r="I652" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA PAPELES INDUSTRIALES SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J652" t="inlineStr">
         <is>
-          <t>93.558.000-5</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K652" t="inlineStr">
@@ -42423,13 +42415,13 @@
         </is>
       </c>
       <c r="M652" s="2" t="n">
-        <v>833.98</v>
+        <v>1396.42</v>
       </c>
     </row>
     <row r="653">
       <c r="A653" t="inlineStr">
         <is>
-          <t>1002588-252-CM26</t>
+          <t>3713-86-CM26</t>
         </is>
       </c>
       <c r="B653" t="inlineStr">
@@ -42444,7 +42436,7 @@
       </c>
       <c r="D653" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E653" t="inlineStr">
@@ -42454,12 +42446,12 @@
       </c>
       <c r="F653" t="inlineStr">
         <is>
-          <t>61.999.320-9</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G653" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE PUERTO CORDILLERA</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H653" t="inlineStr">
@@ -42469,17 +42461,17 @@
       </c>
       <c r="I653" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J653" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K653" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L653" t="inlineStr">
@@ -42488,13 +42480,13 @@
         </is>
       </c>
       <c r="M653" s="2" t="n">
-        <v>1589.88</v>
+        <v>2647.39</v>
       </c>
     </row>
     <row r="654">
       <c r="A654" t="inlineStr">
         <is>
-          <t>1002588-253-CM26</t>
+          <t>3593-364-CM26</t>
         </is>
       </c>
       <c r="B654" t="inlineStr">
@@ -42509,7 +42501,7 @@
       </c>
       <c r="D654" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E654" t="inlineStr">
@@ -42519,12 +42511,12 @@
       </c>
       <c r="F654" t="inlineStr">
         <is>
-          <t>61.999.320-9</t>
+          <t>69.041.100-8</t>
         </is>
       </c>
       <c r="G654" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE PUERTO CORDILLERA</t>
+          <t>ILUSTRE MINICIPALIDAD DE COMBARBALA</t>
         </is>
       </c>
       <c r="H654" t="inlineStr">
@@ -42553,13 +42545,13 @@
         </is>
       </c>
       <c r="M654" s="2" t="n">
-        <v>14334.41</v>
+        <v>776.59</v>
       </c>
     </row>
     <row r="655">
       <c r="A655" t="inlineStr">
         <is>
-          <t>2450-1024-CM26</t>
+          <t>2288-840-CM26</t>
         </is>
       </c>
       <c r="B655" t="inlineStr">
@@ -42574,22 +42566,22 @@
       </c>
       <c r="D655" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E655" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F655" t="inlineStr">
         <is>
-          <t>69.040.100-2</t>
+          <t>69.041.300-0</t>
         </is>
       </c>
       <c r="G655" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE LA SERENA</t>
+          <t>I MUNICIPALIDAD DE CANELA</t>
         </is>
       </c>
       <c r="H655" t="inlineStr">
@@ -42599,12 +42591,12 @@
       </c>
       <c r="I655" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J655" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K655" t="inlineStr">
@@ -42618,13 +42610,13 @@
         </is>
       </c>
       <c r="M655" s="2" t="n">
-        <v>1990.69</v>
+        <v>1916.47</v>
       </c>
     </row>
     <row r="656">
       <c r="A656" t="inlineStr">
         <is>
-          <t>2450-1026-CM26</t>
+          <t>3511-387-CM26</t>
         </is>
       </c>
       <c r="B656" t="inlineStr">
@@ -42639,7 +42631,7 @@
       </c>
       <c r="D656" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E656" t="inlineStr">
@@ -42649,12 +42641,12 @@
       </c>
       <c r="F656" t="inlineStr">
         <is>
-          <t>69.040.100-2</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G656" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE LA SERENA</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H656" t="inlineStr">
@@ -42664,28 +42656,32 @@
       </c>
       <c r="I656" t="inlineStr">
         <is>
-          <t>IMPORTADORA  Y DISTRIBUIDORA BLANMAR SPA</t>
+          <t>DISTRIBUIDORA PAPELES INDUSTRIALES SPA</t>
         </is>
       </c>
       <c r="J656" t="inlineStr">
         <is>
-          <t>76.993.355-7</t>
-        </is>
-      </c>
-      <c r="K656" t="inlineStr"/>
+          <t>93.558.000-5</t>
+        </is>
+      </c>
+      <c r="K656" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L656" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M656" s="2" t="n">
-        <v>1777.95</v>
+        <v>833.98</v>
       </c>
     </row>
     <row r="657">
       <c r="A657" t="inlineStr">
         <is>
-          <t>646-102-CM26</t>
+          <t>1002588-252-CM26</t>
         </is>
       </c>
       <c r="B657" t="inlineStr">
@@ -42700,22 +42696,22 @@
       </c>
       <c r="D657" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E657" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F657" t="inlineStr">
         <is>
-          <t>61.816.000-9</t>
+          <t>61.999.320-9</t>
         </is>
       </c>
       <c r="G657" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION IV REGION</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE PUERTO CORDILLERA</t>
         </is>
       </c>
       <c r="H657" t="inlineStr">
@@ -42725,17 +42721,17 @@
       </c>
       <c r="I657" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J657" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K657" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="L657" t="inlineStr">
@@ -42744,13 +42740,13 @@
         </is>
       </c>
       <c r="M657" s="2" t="n">
-        <v>2709.69</v>
+        <v>1589.88</v>
       </c>
     </row>
     <row r="658">
       <c r="A658" t="inlineStr">
         <is>
-          <t>3509-425-CM26</t>
+          <t>1002588-253-CM26</t>
         </is>
       </c>
       <c r="B658" t="inlineStr">
@@ -42765,7 +42761,7 @@
       </c>
       <c r="D658" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E658" t="inlineStr">
@@ -42775,12 +42771,12 @@
       </c>
       <c r="F658" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>61.999.320-9</t>
         </is>
       </c>
       <c r="G658" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE PUERTO CORDILLERA</t>
         </is>
       </c>
       <c r="H658" t="inlineStr">
@@ -42809,13 +42805,13 @@
         </is>
       </c>
       <c r="M658" s="2" t="n">
-        <v>758.85</v>
+        <v>14334.41</v>
       </c>
     </row>
     <row r="659">
       <c r="A659" t="inlineStr">
         <is>
-          <t>1242121-526-CM26</t>
+          <t>2450-1024-CM26</t>
         </is>
       </c>
       <c r="B659" t="inlineStr">
@@ -42830,22 +42826,22 @@
       </c>
       <c r="D659" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E659" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F659" t="inlineStr">
         <is>
-          <t>61.606.404-5</t>
+          <t>69.040.100-2</t>
         </is>
       </c>
       <c r="G659" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE O</t>
+          <t>ILUSTRE MUNICIPALIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H659" t="inlineStr">
@@ -42855,12 +42851,12 @@
       </c>
       <c r="I659" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J659" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K659" t="inlineStr">
@@ -42874,13 +42870,13 @@
         </is>
       </c>
       <c r="M659" s="2" t="n">
-        <v>2547.63</v>
+        <v>1990.69</v>
       </c>
     </row>
     <row r="660">
       <c r="A660" t="inlineStr">
         <is>
-          <t>548854-39-CM26</t>
+          <t>2450-1026-CM26</t>
         </is>
       </c>
       <c r="B660" t="inlineStr">
@@ -42895,7 +42891,7 @@
       </c>
       <c r="D660" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E660" t="inlineStr">
@@ -42905,12 +42901,12 @@
       </c>
       <c r="F660" t="inlineStr">
         <is>
-          <t>61.979.440-0</t>
+          <t>69.040.100-2</t>
         </is>
       </c>
       <c r="G660" t="inlineStr">
         <is>
-          <t>INSTITUTO DE PREVISION SOCIAL</t>
+          <t>ILUSTRE MUNICIPALIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H660" t="inlineStr">
@@ -42920,32 +42916,28 @@
       </c>
       <c r="I660" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>IMPORTADORA  Y DISTRIBUIDORA BLANMAR SPA</t>
         </is>
       </c>
       <c r="J660" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
-        </is>
-      </c>
-      <c r="K660" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.993.355-7</t>
+        </is>
+      </c>
+      <c r="K660" t="inlineStr"/>
       <c r="L660" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M660" s="2" t="n">
-        <v>934.55</v>
+        <v>1777.95</v>
       </c>
     </row>
     <row r="661">
       <c r="A661" t="inlineStr">
         <is>
-          <t>2125-2010-CM26</t>
+          <t>646-102-CM26</t>
         </is>
       </c>
       <c r="B661" t="inlineStr">
@@ -42960,22 +42952,22 @@
       </c>
       <c r="D661" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E661" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F661" t="inlineStr">
         <is>
-          <t>61.606.407-k</t>
+          <t>61.816.000-9</t>
         </is>
       </c>
       <c r="G661" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DR. HUMBERTO ELORZA CORTES</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION IV REGION</t>
         </is>
       </c>
       <c r="H661" t="inlineStr">
@@ -42985,12 +42977,12 @@
       </c>
       <c r="I661" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J661" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K661" t="inlineStr">
@@ -43004,13 +42996,13 @@
         </is>
       </c>
       <c r="M661" s="2" t="n">
-        <v>874.61</v>
+        <v>2709.69</v>
       </c>
     </row>
     <row r="662">
       <c r="A662" t="inlineStr">
         <is>
-          <t>3265-589-CM26</t>
+          <t>3509-425-CM26</t>
         </is>
       </c>
       <c r="B662" t="inlineStr">
@@ -43025,7 +43017,7 @@
       </c>
       <c r="D662" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="E662" t="inlineStr">
@@ -43035,12 +43027,12 @@
       </c>
       <c r="F662" t="inlineStr">
         <is>
-          <t>69.041.000-1</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G662" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RIO HURTADO</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H662" t="inlineStr">
@@ -43050,17 +43042,17 @@
       </c>
       <c r="I662" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J662" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K662" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="L662" t="inlineStr">
@@ -43069,67 +43061,327 @@
         </is>
       </c>
       <c r="M662" s="2" t="n">
-        <v>2465.83</v>
+        <v>758.85</v>
       </c>
     </row>
     <row r="663">
       <c r="A663" t="inlineStr">
         <is>
+          <t>1242121-526-CM26</t>
+        </is>
+      </c>
+      <c r="B663" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C663" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D663" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="E663" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F663" t="inlineStr">
+        <is>
+          <t>61.606.404-5</t>
+        </is>
+      </c>
+      <c r="G663" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE O</t>
+        </is>
+      </c>
+      <c r="H663" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I663" t="inlineStr">
+        <is>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+        </is>
+      </c>
+      <c r="J663" t="inlineStr">
+        <is>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K663" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L663" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M663" s="2" t="n">
+        <v>2547.63</v>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" t="inlineStr">
+        <is>
+          <t>548854-39-CM26</t>
+        </is>
+      </c>
+      <c r="B664" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C664" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D664" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="E664" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F664" t="inlineStr">
+        <is>
+          <t>61.979.440-0</t>
+        </is>
+      </c>
+      <c r="G664" t="inlineStr">
+        <is>
+          <t>INSTITUTO DE PREVISION SOCIAL</t>
+        </is>
+      </c>
+      <c r="H664" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I664" t="inlineStr">
+        <is>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+        </is>
+      </c>
+      <c r="J664" t="inlineStr">
+        <is>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K664" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L664" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M664" s="2" t="n">
+        <v>934.55</v>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" t="inlineStr">
+        <is>
+          <t>2125-2010-CM26</t>
+        </is>
+      </c>
+      <c r="B665" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C665" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D665" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="E665" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F665" t="inlineStr">
+        <is>
+          <t>61.606.407-k</t>
+        </is>
+      </c>
+      <c r="G665" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DR. HUMBERTO ELORZA CORTES</t>
+        </is>
+      </c>
+      <c r="H665" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I665" t="inlineStr">
+        <is>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+        </is>
+      </c>
+      <c r="J665" t="inlineStr">
+        <is>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K665" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L665" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M665" s="2" t="n">
+        <v>874.61</v>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" t="inlineStr">
+        <is>
+          <t>3265-589-CM26</t>
+        </is>
+      </c>
+      <c r="B666" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C666" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D666" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="E666" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F666" t="inlineStr">
+        <is>
+          <t>69.041.000-1</t>
+        </is>
+      </c>
+      <c r="G666" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE RIO HURTADO</t>
+        </is>
+      </c>
+      <c r="H666" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I666" t="inlineStr">
+        <is>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+        </is>
+      </c>
+      <c r="J666" t="inlineStr">
+        <is>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K666" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L666" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M666" s="2" t="n">
+        <v>2465.83</v>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" t="inlineStr">
+        <is>
           <t>1057439-6481-CM26</t>
         </is>
       </c>
-      <c r="B663" t="inlineStr">
-        <is>
-          <t>2239-16-LR24</t>
-        </is>
-      </c>
-      <c r="C663" t="inlineStr">
+      <c r="B667" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C667" t="inlineStr">
         <is>
           <t>oct-2026</t>
         </is>
       </c>
-      <c r="D663" t="inlineStr">
+      <c r="D667" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="E663" t="inlineStr">
+      <c r="E667" t="inlineStr">
         <is>
           <t>Aceptada</t>
         </is>
       </c>
-      <c r="F663" t="inlineStr">
+      <c r="F667" t="inlineStr">
         <is>
           <t>61.606.402-9</t>
         </is>
       </c>
-      <c r="G663" t="inlineStr">
+      <c r="G667" t="inlineStr">
         <is>
           <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
         </is>
       </c>
-      <c r="H663" t="inlineStr">
-        <is>
-          <t>Coquimbo</t>
-        </is>
-      </c>
-      <c r="I663" t="inlineStr">
+      <c r="H667" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I667" t="inlineStr">
         <is>
           <t>CARLOS ALBERTO VARGAS CASTILLO</t>
         </is>
       </c>
-      <c r="J663" t="inlineStr">
+      <c r="J667" t="inlineStr">
         <is>
           <t>13.940.082-8</t>
         </is>
       </c>
-      <c r="K663" t="inlineStr"/>
-      <c r="L663" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M663" s="2" t="n">
+      <c r="K667" t="inlineStr"/>
+      <c r="L667" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M667" s="2" t="n">
         <v>7053.91</v>
       </c>
     </row>

--- a/docs/oc-regiones/articulos-de-escritorio-y-papeleria/coquimbo.xlsx
+++ b/docs/oc-regiones/articulos-de-escritorio-y-papeleria/coquimbo.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M667"/>
+  <dimension ref="A1:M672"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2505,7 +2505,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2711-44-CM25</t>
+          <t>2711-46-CM25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2545,12 +2545,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>CASTILLA Y ARAGON SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>96.989.530-7</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2564,13 +2564,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>1040.47</v>
+        <v>719.26</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1574-30-CM25</t>
+          <t>2711-44-CM25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2590,17 +2590,17 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>69.040.700-0</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>MUNICIPALIDAD DE OVALLE</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2610,12 +2610,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>CASTILLA Y ARAGON SPA</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.989.530-7</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2629,13 +2629,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>2221.66</v>
+        <v>1040.47</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2711-46-CM25</t>
+          <t>1574-30-CM25</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2655,17 +2655,17 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>69.040.700-0</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE OVALLE</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2694,7 +2694,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>719.26</v>
+        <v>2221.66</v>
       </c>
     </row>
     <row r="36">
@@ -3923,7 +3923,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>5416-127-CM25</t>
+          <t>4619-7-CM25</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>61.502.000-1</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>DIRECCION DEL TRABAJO</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3963,17 +3963,17 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -3982,13 +3982,13 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>969.41</v>
+        <v>760.8200000000001</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>4619-7-CM25</t>
+          <t>5416-127-CM25</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4013,12 +4013,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>61.502.000-1</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>DIRECCION DEL TRABAJO</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -4028,17 +4028,17 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -4047,7 +4047,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>760.8200000000001</v>
+        <v>969.41</v>
       </c>
     </row>
     <row r="57">
@@ -4183,7 +4183,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>627786-32-CM25</t>
+          <t>2711-80-CM25</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4203,17 +4203,17 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>60.505.206-1</t>
+          <t>69.040.700-0</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>MUNICIPALIDAD DE OVALLE</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4223,32 +4223,28 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>AMINORTE S A</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>Coquimbo</t>
-        </is>
-      </c>
+          <t>99.533.780-0</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>737.52</v>
+        <v>1360.31</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2711-80-CM25</t>
+          <t>627786-32-CM25</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4268,17 +4264,17 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>69.040.700-0</t>
+          <t>60.505.206-1</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE OVALLE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4288,22 +4284,26 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>AMINORTE S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>99.533.780-0</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr"/>
+          <t>77.012.870-6</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>1360.31</v>
+        <v>737.52</v>
       </c>
     </row>
     <row r="61">
@@ -4374,7 +4374,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>1346282-100-CM25</t>
+          <t>2992-163-CM25</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4399,12 +4399,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>69.040.800-7</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>I MUNICIPALIDAD DE MONTEPATRIA</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4433,13 +4433,13 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>2633.14</v>
+        <v>3383.6</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2992-163-CM25</t>
+          <t>1346282-100-CM25</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4464,12 +4464,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>69.040.800-7</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MONTEPATRIA</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4498,7 +4498,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>3383.6</v>
+        <v>2633.14</v>
       </c>
     </row>
     <row r="64">
@@ -4569,7 +4569,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>4619-10-CM25</t>
+          <t>2145-250-CM25</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4594,12 +4594,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>61.502.000-1</t>
+          <t>61.606.409-6</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>DIRECCION DEL TRABAJO</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE LOS VILOS</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4609,17 +4609,17 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -4628,13 +4628,13 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>832.23</v>
+        <v>2023.33</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2145-250-CM25</t>
+          <t>4619-10-CM25</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4659,12 +4659,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>61.606.409-6</t>
+          <t>61.502.000-1</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE LOS VILOS</t>
+          <t>DIRECCION DEL TRABAJO</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4674,17 +4674,17 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>2023.33</v>
+        <v>832.23</v>
       </c>
     </row>
     <row r="67">
@@ -5215,7 +5215,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>5416-245-CM25</t>
+          <t>5416-240-CM25</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -5274,13 +5274,13 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>4082.97</v>
+        <v>2440.86</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>5416-240-CM25</t>
+          <t>5416-245-CM25</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5339,7 +5339,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>2440.86</v>
+        <v>4082.97</v>
       </c>
     </row>
     <row r="77">
@@ -6300,7 +6300,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>3597-226-CM25</t>
+          <t>2554-16-CM25</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6320,17 +6320,17 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>69.040.500-8</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VICUNA</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -6340,17 +6340,17 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -6359,13 +6359,13 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>7404.75</v>
+        <v>933.54</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2554-16-CM25</t>
+          <t>3597-226-CM25</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6385,17 +6385,17 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>69.040.500-8</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>I MUNICIPALIDAD DE VICUNA</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -6405,17 +6405,17 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -6424,7 +6424,7 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>933.54</v>
+        <v>7404.75</v>
       </c>
     </row>
     <row r="94">
@@ -6881,7 +6881,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>3712-329-CM25</t>
+          <t>2711-167-CM25</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6901,17 +6901,17 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>69.040.700-0</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>MUNICIPALIDAD DE OVALLE</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -6921,28 +6921,32 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>SURTI VENTAS S.A.</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>76.462.500-5</t>
-        </is>
-      </c>
-      <c r="K101" t="inlineStr"/>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L101" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>905.45</v>
+        <v>16727.54</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2711-167-CM25</t>
+          <t>1352-53-CM25</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -6962,17 +6966,17 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>69.040.700-0</t>
+          <t>61.002.010-0</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE OVALLE</t>
+          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -6982,17 +6986,17 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -7001,13 +7005,13 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>16727.54</v>
+        <v>6321.69</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>1352-53-CM25</t>
+          <t>3712-329-CM25</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -7032,12 +7036,12 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>61.002.010-0</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -7047,26 +7051,22 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>SURTI VENTAS S.A.</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
-        </is>
-      </c>
-      <c r="K103" t="inlineStr">
-        <is>
-          <t>Coquimbo</t>
-        </is>
-      </c>
+          <t>76.462.500-5</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr"/>
       <c r="L103" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>6321.69</v>
+        <v>905.45</v>
       </c>
     </row>
     <row r="104">
@@ -7198,7 +7198,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>627786-58-CM25</t>
+          <t>707418-46-CM25</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -7223,12 +7223,12 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>60.505.206-1</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -7238,17 +7238,17 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>COMERCIALIZADORA SAN JERONIMO SPA</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>77.610.393-4</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -7257,13 +7257,13 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>5278.57</v>
+        <v>778.63</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>707418-46-CM25</t>
+          <t>2710-353-CM25</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -7288,12 +7288,12 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>69.040.700-0</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>MUNICIPALIDAD DE OVALLE</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -7303,32 +7303,28 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SAN JERONIMO SPA</t>
+          <t>ROLAND VORWERK Y COMPANIA LIMITADA</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>77.610.393-4</t>
-        </is>
-      </c>
-      <c r="K107" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>78.178.530-k</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr"/>
       <c r="L107" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>778.63</v>
+        <v>13700.49</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2710-353-CM25</t>
+          <t>1057439-13241-CM25</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -7353,12 +7349,12 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>69.040.700-0</t>
+          <t>61.606.402-9</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE OVALLE</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -7368,12 +7364,12 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>ROLAND VORWERK Y COMPANIA LIMITADA</t>
+          <t>CARLOS ALBERTO VARGAS CASTILLO</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>78.178.530-k</t>
+          <t>13.940.082-8</t>
         </is>
       </c>
       <c r="K108" t="inlineStr"/>
@@ -7383,13 +7379,13 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>13700.49</v>
+        <v>9048.790000000001</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>1057439-13241-CM25</t>
+          <t>3532-49-CM25</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -7414,12 +7410,12 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>61.606.402-9</t>
+          <t>81.925.500-8</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -7429,28 +7425,32 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO VARGAS CASTILLO</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>13.940.082-8</t>
-        </is>
-      </c>
-      <c r="K109" t="inlineStr"/>
+          <t>77.012.870-6</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L109" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>9048.790000000001</v>
+        <v>1486.13</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>3532-49-CM25</t>
+          <t>627786-58-CM25</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -7475,12 +7475,12 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>81.925.500-8</t>
+          <t>60.505.206-1</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -7509,7 +7509,7 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>1486.13</v>
+        <v>5278.57</v>
       </c>
     </row>
     <row r="111">
@@ -7905,7 +7905,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>1698-135-CM25</t>
+          <t>1218463-21-CM25</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -7925,17 +7925,17 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>70.892.100-9</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>CORP.MUNICIPAL GABRIEL GONZALEZ VIDELA DE LA SERENA</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -7945,12 +7945,12 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
@@ -7964,7 +7964,7 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>4832.32</v>
+        <v>15839.69</v>
       </c>
     </row>
     <row r="118">
@@ -8161,7 +8161,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>1218463-21-CM25</t>
+          <t>1698-135-CM25</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -8181,17 +8181,17 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>70.892.100-9</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>CORP.MUNICIPAL GABRIEL GONZALEZ VIDELA DE LA SERENA</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -8201,12 +8201,12 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
@@ -8220,7 +8220,7 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>15839.69</v>
+        <v>4832.32</v>
       </c>
     </row>
     <row r="122">
@@ -8681,7 +8681,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>1430710-1630-CM25</t>
+          <t>1079505-486-CM25</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -8706,12 +8706,12 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>61.606.403-7</t>
+          <t>60.505.206-1</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE COQUIMBO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -8721,32 +8721,28 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>MALMO S.A.</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
-        </is>
-      </c>
-      <c r="K129" t="inlineStr">
-        <is>
-          <t>Antofagasta</t>
-        </is>
-      </c>
+          <t>76.195.558-6</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr"/>
       <c r="L129" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>4510.75</v>
+        <v>3767.99</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>1079505-486-CM25</t>
+          <t>3754-163-CM25</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -8766,17 +8762,17 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>60.505.206-1</t>
+          <t>69.041.300-0</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD DE CANELA</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -8786,28 +8782,32 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>MALMO S.A.</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>76.195.558-6</t>
-        </is>
-      </c>
-      <c r="K130" t="inlineStr"/>
+          <t>77.012.870-6</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L130" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>3767.99</v>
+        <v>3576.9</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>3754-163-CM25</t>
+          <t>1430710-1630-CM25</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -8827,17 +8827,17 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>69.041.300-0</t>
+          <t>61.606.403-7</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CANELA</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE COQUIMBO</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -8847,17 +8847,17 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
@@ -8866,7 +8866,7 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>3576.9</v>
+        <v>4510.75</v>
       </c>
     </row>
     <row r="132">
@@ -10221,7 +10221,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2125-3414-CM25</t>
+          <t>4619-27-CM25</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -10246,12 +10246,12 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>61.606.407-k</t>
+          <t>61.502.000-1</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DR. HUMBERTO ELORZA CORTES</t>
+          <t>DIRECCION DEL TRABAJO</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -10261,17 +10261,17 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
@@ -10280,7 +10280,7 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>1393.85</v>
+        <v>1173.66</v>
       </c>
     </row>
     <row r="154">
@@ -10351,7 +10351,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>4619-27-CM25</t>
+          <t>2125-3414-CM25</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -10376,12 +10376,12 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>61.502.000-1</t>
+          <t>61.606.407-k</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>DIRECCION DEL TRABAJO</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DR. HUMBERTO ELORZA CORTES</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -10391,17 +10391,17 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
@@ -10410,7 +10410,7 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>1173.66</v>
+        <v>1393.85</v>
       </c>
     </row>
     <row r="156">
@@ -13955,7 +13955,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>3276-27-CM25</t>
+          <t>3511-389-CM25</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -13975,17 +13975,17 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>60.506.000-5</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -13995,28 +13995,32 @@
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>IMPORTADORA  Y DISTRIBUIDORA BLANMAR SPA</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J211" t="inlineStr">
         <is>
-          <t>76.993.355-7</t>
-        </is>
-      </c>
-      <c r="K211" t="inlineStr"/>
+          <t>77.012.870-6</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L211" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M211" s="2" t="n">
-        <v>1633.93</v>
+        <v>756.78</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>1574-315-CM25</t>
+          <t>3276-27-CM25</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -14041,12 +14045,12 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>60.506.000-5</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -14056,32 +14060,28 @@
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>IMPORTADORA  Y DISTRIBUIDORA BLANMAR SPA</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
-        </is>
-      </c>
-      <c r="K212" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.993.355-7</t>
+        </is>
+      </c>
+      <c r="K212" t="inlineStr"/>
       <c r="L212" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>2018.74</v>
+        <v>1633.93</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>3511-389-CM25</t>
+          <t>1574-315-CM25</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -14101,17 +14101,17 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -14121,17 +14121,17 @@
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J213" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K213" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L213" t="inlineStr">
@@ -14140,7 +14140,7 @@
         </is>
       </c>
       <c r="M213" s="2" t="n">
-        <v>756.78</v>
+        <v>2018.74</v>
       </c>
     </row>
     <row r="214">
@@ -14853,7 +14853,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>3714-288-CM25</t>
+          <t>646-112-CM25</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -14873,17 +14873,17 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>61.816.000-9</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION IV REGION</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -14893,17 +14893,17 @@
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J225" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K225" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="L225" t="inlineStr">
@@ -14912,13 +14912,13 @@
         </is>
       </c>
       <c r="M225" s="2" t="n">
-        <v>1952.13</v>
+        <v>5964.64</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>646-112-CM25</t>
+          <t>3714-288-CM25</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -14938,17 +14938,17 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>61.816.000-9</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION IV REGION</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -14958,17 +14958,17 @@
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K226" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L226" t="inlineStr">
@@ -14977,7 +14977,7 @@
         </is>
       </c>
       <c r="M226" s="2" t="n">
-        <v>5964.64</v>
+        <v>1952.13</v>
       </c>
     </row>
     <row r="227">
@@ -15422,7 +15422,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>1962-574-CM25</t>
+          <t>1242121-531-CM25</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -15447,12 +15447,12 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>61.004.012-8</t>
+          <t>61.606.404-5</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE O</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
@@ -15462,17 +15462,17 @@
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J234" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K234" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L234" t="inlineStr">
@@ -15481,13 +15481,13 @@
         </is>
       </c>
       <c r="M234" s="2" t="n">
-        <v>2102.98</v>
+        <v>3985</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>1242121-531-CM25</t>
+          <t>1962-574-CM25</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -15512,12 +15512,12 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>61.606.404-5</t>
+          <t>61.004.012-8</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE O</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
@@ -15527,17 +15527,17 @@
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J235" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K235" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="L235" t="inlineStr">
@@ -15546,7 +15546,7 @@
         </is>
       </c>
       <c r="M235" s="2" t="n">
-        <v>3985</v>
+        <v>2102.98</v>
       </c>
     </row>
     <row r="236">
@@ -15682,7 +15682,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>2446-1585-CM25</t>
+          <t>5416-1036-CM25</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -15707,12 +15707,12 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>69.040.300-5</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COQUIMBO</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
@@ -15741,13 +15741,13 @@
         </is>
       </c>
       <c r="M238" s="2" t="n">
-        <v>2050.61</v>
+        <v>1825.03</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>5416-1036-CM25</t>
+          <t>2446-1585-CM25</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -15772,12 +15772,12 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>69.040.300-5</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>I MUNICIPALIDAD DE COQUIMBO</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
@@ -15806,7 +15806,7 @@
         </is>
       </c>
       <c r="M239" s="2" t="n">
-        <v>1825.03</v>
+        <v>2050.61</v>
       </c>
     </row>
     <row r="240">
@@ -16584,7 +16584,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>1057439-19195-CM25</t>
+          <t>3511-582-CM25</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -16604,17 +16604,17 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>61.606.402-9</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
@@ -16624,12 +16624,12 @@
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO VARGAS CASTILLO</t>
+          <t>MALMO S.A.</t>
         </is>
       </c>
       <c r="J252" t="inlineStr">
         <is>
-          <t>13.940.082-8</t>
+          <t>76.195.558-6</t>
         </is>
       </c>
       <c r="K252" t="inlineStr"/>
@@ -16639,13 +16639,13 @@
         </is>
       </c>
       <c r="M252" s="2" t="n">
-        <v>3619.31</v>
+        <v>1400.28</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>3511-582-CM25</t>
+          <t>1057439-19195-CM25</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -16665,17 +16665,17 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>61.606.402-9</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
@@ -16685,12 +16685,12 @@
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t>MALMO S.A.</t>
+          <t>CARLOS ALBERTO VARGAS CASTILLO</t>
         </is>
       </c>
       <c r="J253" t="inlineStr">
         <is>
-          <t>76.195.558-6</t>
+          <t>13.940.082-8</t>
         </is>
       </c>
       <c r="K253" t="inlineStr"/>
@@ -16700,7 +16700,7 @@
         </is>
       </c>
       <c r="M253" s="2" t="n">
-        <v>1400.28</v>
+        <v>3619.31</v>
       </c>
     </row>
     <row r="254">
@@ -16836,7 +16836,7 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>707418-176-CM25</t>
+          <t>1057438-295-CM25</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -16861,12 +16861,12 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.606.401-0</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL VICUNA</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
@@ -16876,17 +16876,17 @@
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J256" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K256" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L256" t="inlineStr">
@@ -16895,13 +16895,13 @@
         </is>
       </c>
       <c r="M256" s="2" t="n">
-        <v>6454.19</v>
+        <v>1402.13</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>1057438-295-CM25</t>
+          <t>707418-174-CM25</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -16926,12 +16926,12 @@
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>61.606.401-0</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL VICUNA</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
@@ -16941,17 +16941,17 @@
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIALIZADORA SAN JERONIMO SPA</t>
         </is>
       </c>
       <c r="J257" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.610.393-4</t>
         </is>
       </c>
       <c r="K257" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L257" t="inlineStr">
@@ -16960,13 +16960,13 @@
         </is>
       </c>
       <c r="M257" s="2" t="n">
-        <v>1402.13</v>
+        <v>2262.26</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>707418-174-CM25</t>
+          <t>707418-176-CM25</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -17006,12 +17006,12 @@
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SAN JERONIMO SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J258" t="inlineStr">
         <is>
-          <t>77.610.393-4</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K258" t="inlineStr">
@@ -17025,7 +17025,7 @@
         </is>
       </c>
       <c r="M258" s="2" t="n">
-        <v>2262.26</v>
+        <v>6454.19</v>
       </c>
     </row>
     <row r="259">
@@ -17413,7 +17413,7 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>646-134-CM25</t>
+          <t>1461054-336-CM25</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -17438,12 +17438,12 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>61.816.000-9</t>
+          <t>61.981.040-6</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION IV REGION</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DEL ELQUI</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
@@ -17453,17 +17453,17 @@
       </c>
       <c r="I265" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J265" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K265" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="L265" t="inlineStr">
@@ -17472,13 +17472,13 @@
         </is>
       </c>
       <c r="M265" s="2" t="n">
-        <v>2340.96</v>
+        <v>14650.02</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>1461054-336-CM25</t>
+          <t>646-134-CM25</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -17503,12 +17503,12 @@
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>61.981.040-6</t>
+          <t>61.816.000-9</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DEL ELQUI</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION IV REGION</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
@@ -17518,17 +17518,17 @@
       </c>
       <c r="I266" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J266" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K266" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L266" t="inlineStr">
@@ -17537,7 +17537,7 @@
         </is>
       </c>
       <c r="M266" s="2" t="n">
-        <v>14650.02</v>
+        <v>2340.96</v>
       </c>
     </row>
     <row r="267">
@@ -18888,7 +18888,7 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>1232565-421-CM25</t>
+          <t>1461054-447-CM25</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -18913,12 +18913,12 @@
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>61.981.040-6</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DEL ELQUI</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
@@ -18928,17 +18928,17 @@
       </c>
       <c r="I288" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J288" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K288" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="L288" t="inlineStr">
@@ -18947,13 +18947,13 @@
         </is>
       </c>
       <c r="M288" s="2" t="n">
-        <v>958.62</v>
+        <v>3111.59</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>5416-1402-CM25</t>
+          <t>1232565-421-CM25</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -19012,13 +19012,13 @@
         </is>
       </c>
       <c r="M289" s="2" t="n">
-        <v>2178.64</v>
+        <v>958.62</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>1461054-447-CM25</t>
+          <t>5416-1402-CM25</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -19043,12 +19043,12 @@
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>61.981.040-6</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DEL ELQUI</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
@@ -19058,17 +19058,17 @@
       </c>
       <c r="I290" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J290" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K290" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L290" t="inlineStr">
@@ -19077,7 +19077,7 @@
         </is>
       </c>
       <c r="M290" s="2" t="n">
-        <v>3111.59</v>
+        <v>2178.64</v>
       </c>
     </row>
     <row r="291">
@@ -20375,7 +20375,7 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>1574-361-CM25</t>
+          <t>1574-357-CM25</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -20415,12 +20415,12 @@
       </c>
       <c r="I311" t="inlineStr">
         <is>
-          <t>IMPORTADORA Y COMERCIALIZADORA JMMB SPA</t>
+          <t>ALEMED SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J311" t="inlineStr">
         <is>
-          <t>77.461.733-7</t>
+          <t>77.727.285-3</t>
         </is>
       </c>
       <c r="K311" t="inlineStr">
@@ -20434,13 +20434,13 @@
         </is>
       </c>
       <c r="M311" s="2" t="n">
-        <v>18784.6</v>
+        <v>760.87</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>1574-357-CM25</t>
+          <t>1574-361-CM25</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -20480,12 +20480,12 @@
       </c>
       <c r="I312" t="inlineStr">
         <is>
-          <t>ALEMED SOLUCIONES INTEGRALES SPA</t>
+          <t>IMPORTADORA Y COMERCIALIZADORA JMMB SPA</t>
         </is>
       </c>
       <c r="J312" t="inlineStr">
         <is>
-          <t>77.727.285-3</t>
+          <t>77.461.733-7</t>
         </is>
       </c>
       <c r="K312" t="inlineStr">
@@ -20499,7 +20499,7 @@
         </is>
       </c>
       <c r="M312" s="2" t="n">
-        <v>760.87</v>
+        <v>18784.6</v>
       </c>
     </row>
     <row r="313">
@@ -24544,7 +24544,7 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>3750-17-CM26</t>
+          <t>3712-7-CM26</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
@@ -24564,17 +24564,17 @@
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F376" t="inlineStr">
         <is>
-          <t>69.040.200-9</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G376" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA HIGUERA</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H376" t="inlineStr">
@@ -24584,17 +24584,17 @@
       </c>
       <c r="I376" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J376" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K376" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L376" t="inlineStr">
@@ -24603,13 +24603,13 @@
         </is>
       </c>
       <c r="M376" s="2" t="n">
-        <v>815.24</v>
+        <v>2010.47</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>3712-7-CM26</t>
+          <t>3750-17-CM26</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
@@ -24629,17 +24629,17 @@
       </c>
       <c r="E377" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F377" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>69.040.200-9</t>
         </is>
       </c>
       <c r="G377" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>I MUNICIPALIDAD DE LA HIGUERA</t>
         </is>
       </c>
       <c r="H377" t="inlineStr">
@@ -24649,17 +24649,17 @@
       </c>
       <c r="I377" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J377" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K377" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="L377" t="inlineStr">
@@ -24668,7 +24668,7 @@
         </is>
       </c>
       <c r="M377" s="2" t="n">
-        <v>2010.47</v>
+        <v>815.24</v>
       </c>
     </row>
     <row r="378">
@@ -24869,7 +24869,7 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>2992-3-CM26</t>
+          <t>2996-7-CM26</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
@@ -24889,7 +24889,7 @@
       </c>
       <c r="E381" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F381" t="inlineStr">
@@ -24909,17 +24909,17 @@
       </c>
       <c r="I381" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J381" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K381" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L381" t="inlineStr">
@@ -24928,7 +24928,7 @@
         </is>
       </c>
       <c r="M381" s="2" t="n">
-        <v>3011.72</v>
+        <v>8246.370000000001</v>
       </c>
     </row>
     <row r="382">
@@ -24999,7 +24999,7 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>2996-7-CM26</t>
+          <t>2992-3-CM26</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
@@ -25019,7 +25019,7 @@
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F383" t="inlineStr">
@@ -25039,17 +25039,17 @@
       </c>
       <c r="I383" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J383" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K383" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="L383" t="inlineStr">
@@ -25058,13 +25058,13 @@
         </is>
       </c>
       <c r="M383" s="2" t="n">
-        <v>8246.370000000001</v>
+        <v>3011.72</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>3712-35-CM26</t>
+          <t>1430710-87-CM26</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
@@ -25089,12 +25089,12 @@
       </c>
       <c r="F384" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>61.606.403-7</t>
         </is>
       </c>
       <c r="G384" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE COQUIMBO</t>
         </is>
       </c>
       <c r="H384" t="inlineStr">
@@ -25104,12 +25104,12 @@
       </c>
       <c r="I384" t="inlineStr">
         <is>
-          <t>OPEN SANTIAGO SPA</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J384" t="inlineStr">
         <is>
-          <t>78.069.505-6</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K384" t="inlineStr">
@@ -25123,13 +25123,13 @@
         </is>
       </c>
       <c r="M384" s="2" t="n">
-        <v>1013.86</v>
+        <v>5144.81</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>1430710-87-CM26</t>
+          <t>3712-35-CM26</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
@@ -25154,12 +25154,12 @@
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>61.606.403-7</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G385" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE COQUIMBO</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H385" t="inlineStr">
@@ -25169,12 +25169,12 @@
       </c>
       <c r="I385" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>OPEN SANTIAGO SPA</t>
         </is>
       </c>
       <c r="J385" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>78.069.505-6</t>
         </is>
       </c>
       <c r="K385" t="inlineStr">
@@ -25188,13 +25188,13 @@
         </is>
       </c>
       <c r="M385" s="2" t="n">
-        <v>5144.81</v>
+        <v>1013.86</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>2992-13-CM26</t>
+          <t>2992-12-CM26</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
@@ -25253,13 +25253,13 @@
         </is>
       </c>
       <c r="M386" s="2" t="n">
-        <v>4202.75</v>
+        <v>9578.959999999999</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>2992-12-CM26</t>
+          <t>2992-13-CM26</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
@@ -25318,7 +25318,7 @@
         </is>
       </c>
       <c r="M387" s="2" t="n">
-        <v>9578.959999999999</v>
+        <v>4202.75</v>
       </c>
     </row>
     <row r="388">
@@ -25389,7 +25389,7 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>3615-5-CM26</t>
+          <t>3712-56-CM26</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
@@ -25414,12 +25414,12 @@
       </c>
       <c r="F389" t="inlineStr">
         <is>
-          <t>69.041.100-8</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G389" t="inlineStr">
         <is>
-          <t>ILUSTRE MINICIPALIDAD DE COMBARBALA</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H389" t="inlineStr">
@@ -25448,13 +25448,13 @@
         </is>
       </c>
       <c r="M389" s="2" t="n">
-        <v>5504.15</v>
+        <v>1130.94</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>2146-34-CM26</t>
+          <t>3615-5-CM26</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
@@ -25479,12 +25479,12 @@
       </c>
       <c r="F390" t="inlineStr">
         <is>
-          <t>61.606.405-3</t>
+          <t>69.041.100-8</t>
         </is>
       </c>
       <c r="G390" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE ANDACOLLO</t>
+          <t>ILUSTRE MINICIPALIDAD DE COMBARBALA</t>
         </is>
       </c>
       <c r="H390" t="inlineStr">
@@ -25513,13 +25513,13 @@
         </is>
       </c>
       <c r="M390" s="2" t="n">
-        <v>2810.21</v>
+        <v>5504.15</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>3712-56-CM26</t>
+          <t>2146-34-CM26</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
@@ -25544,12 +25544,12 @@
       </c>
       <c r="F391" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>61.606.405-3</t>
         </is>
       </c>
       <c r="G391" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE ANDACOLLO</t>
         </is>
       </c>
       <c r="H391" t="inlineStr">
@@ -25578,7 +25578,7 @@
         </is>
       </c>
       <c r="M391" s="2" t="n">
-        <v>1130.94</v>
+        <v>2810.21</v>
       </c>
     </row>
     <row r="392">
@@ -25909,7 +25909,7 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>3509-49-CM26</t>
+          <t>1698-20-CM26</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
@@ -25934,12 +25934,12 @@
       </c>
       <c r="F397" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G397" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H397" t="inlineStr">
@@ -25949,28 +25949,32 @@
       </c>
       <c r="I397" t="inlineStr">
         <is>
-          <t>MALMO S.A.</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J397" t="inlineStr">
         <is>
-          <t>76.195.558-6</t>
-        </is>
-      </c>
-      <c r="K397" t="inlineStr"/>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K397" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L397" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M397" s="2" t="n">
-        <v>3357.69</v>
+        <v>11069.98</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>1698-20-CM26</t>
+          <t>4036-91-CM26</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
@@ -25995,12 +25999,12 @@
       </c>
       <c r="F398" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>69.040.400-1</t>
         </is>
       </c>
       <c r="G398" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>I MUNICIPALIDAD DE ANDACOLLO</t>
         </is>
       </c>
       <c r="H398" t="inlineStr">
@@ -26010,17 +26014,17 @@
       </c>
       <c r="I398" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J398" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K398" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L398" t="inlineStr">
@@ -26029,13 +26033,13 @@
         </is>
       </c>
       <c r="M398" s="2" t="n">
-        <v>11069.98</v>
+        <v>3646.32</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>4036-91-CM26</t>
+          <t>4036-90-CM26</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
@@ -26075,12 +26079,12 @@
       </c>
       <c r="I399" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>ANTALIS CHILE LIMITADA</t>
         </is>
       </c>
       <c r="J399" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>77.305.910-1</t>
         </is>
       </c>
       <c r="K399" t="inlineStr">
@@ -26094,13 +26098,13 @@
         </is>
       </c>
       <c r="M399" s="2" t="n">
-        <v>3646.32</v>
+        <v>4191.29</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>4036-90-CM26</t>
+          <t>3509-49-CM26</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
@@ -26125,12 +26129,12 @@
       </c>
       <c r="F400" t="inlineStr">
         <is>
-          <t>69.040.400-1</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G400" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANDACOLLO</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H400" t="inlineStr">
@@ -26140,32 +26144,28 @@
       </c>
       <c r="I400" t="inlineStr">
         <is>
-          <t>ANTALIS CHILE LIMITADA</t>
+          <t>MALMO S.A.</t>
         </is>
       </c>
       <c r="J400" t="inlineStr">
         <is>
-          <t>77.305.910-1</t>
-        </is>
-      </c>
-      <c r="K400" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.195.558-6</t>
+        </is>
+      </c>
+      <c r="K400" t="inlineStr"/>
       <c r="L400" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M400" s="2" t="n">
-        <v>4191.29</v>
+        <v>3357.69</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>3614-12-CM26</t>
+          <t>3614-11-CM26</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
@@ -26205,17 +26205,17 @@
       </c>
       <c r="I401" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J401" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K401" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L401" t="inlineStr">
@@ -26224,13 +26224,13 @@
         </is>
       </c>
       <c r="M401" s="2" t="n">
-        <v>1494.83</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>3614-11-CM26</t>
+          <t>3614-12-CM26</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
@@ -26270,17 +26270,17 @@
       </c>
       <c r="I402" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J402" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K402" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L402" t="inlineStr">
@@ -26289,7 +26289,7 @@
         </is>
       </c>
       <c r="M402" s="2" t="n">
-        <v>1306</v>
+        <v>1494.83</v>
       </c>
     </row>
     <row r="403">
@@ -26490,7 +26490,7 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>1346282-49-CM26</t>
+          <t>2992-39-CM26</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
@@ -26515,12 +26515,12 @@
       </c>
       <c r="F406" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>69.040.800-7</t>
         </is>
       </c>
       <c r="G406" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>I MUNICIPALIDAD DE MONTEPATRIA</t>
         </is>
       </c>
       <c r="H406" t="inlineStr">
@@ -26530,17 +26530,17 @@
       </c>
       <c r="I406" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J406" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K406" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="L406" t="inlineStr">
@@ -26549,13 +26549,13 @@
         </is>
       </c>
       <c r="M406" s="2" t="n">
-        <v>844.66</v>
+        <v>24541.9</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>2992-39-CM26</t>
+          <t>1346282-49-CM26</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
@@ -26580,12 +26580,12 @@
       </c>
       <c r="F407" t="inlineStr">
         <is>
-          <t>69.040.800-7</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G407" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MONTEPATRIA</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H407" t="inlineStr">
@@ -26595,17 +26595,17 @@
       </c>
       <c r="I407" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J407" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K407" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L407" t="inlineStr">
@@ -26614,7 +26614,7 @@
         </is>
       </c>
       <c r="M407" s="2" t="n">
-        <v>24541.9</v>
+        <v>844.66</v>
       </c>
     </row>
     <row r="408">
@@ -26750,7 +26750,7 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>1057439-1118-CM26</t>
+          <t>1346282-67-CM26</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
@@ -26775,12 +26775,12 @@
       </c>
       <c r="F410" t="inlineStr">
         <is>
-          <t>61.606.402-9</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G410" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H410" t="inlineStr">
@@ -26790,28 +26790,32 @@
       </c>
       <c r="I410" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO VARGAS CASTILLO</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J410" t="inlineStr">
         <is>
-          <t>13.940.082-8</t>
-        </is>
-      </c>
-      <c r="K410" t="inlineStr"/>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K410" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L410" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M410" s="2" t="n">
-        <v>10755.7</v>
+        <v>1045.73</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>1346282-68-CM26</t>
+          <t>1057439-1118-CM26</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
@@ -26836,12 +26840,12 @@
       </c>
       <c r="F411" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>61.606.402-9</t>
         </is>
       </c>
       <c r="G411" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
         </is>
       </c>
       <c r="H411" t="inlineStr">
@@ -26851,32 +26855,28 @@
       </c>
       <c r="I411" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>CARLOS ALBERTO VARGAS CASTILLO</t>
         </is>
       </c>
       <c r="J411" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
-        </is>
-      </c>
-      <c r="K411" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>13.940.082-8</t>
+        </is>
+      </c>
+      <c r="K411" t="inlineStr"/>
       <c r="L411" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M411" s="2" t="n">
-        <v>1935.97</v>
+        <v>10755.7</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>1346282-67-CM26</t>
+          <t>1346282-68-CM26</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
@@ -26935,13 +26935,13 @@
         </is>
       </c>
       <c r="M412" s="2" t="n">
-        <v>1045.73</v>
+        <v>1935.97</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>3712-67-CM26</t>
+          <t>1962-77-CM26</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
@@ -26966,12 +26966,12 @@
       </c>
       <c r="F413" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>61.004.012-8</t>
         </is>
       </c>
       <c r="G413" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H413" t="inlineStr">
@@ -26981,12 +26981,12 @@
       </c>
       <c r="I413" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J413" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K413" t="inlineStr">
@@ -27000,13 +27000,13 @@
         </is>
       </c>
       <c r="M413" s="2" t="n">
-        <v>1036.31</v>
+        <v>1977.71</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>1057439-1206-CM26</t>
+          <t>3712-67-CM26</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
@@ -27031,12 +27031,12 @@
       </c>
       <c r="F414" t="inlineStr">
         <is>
-          <t>61.606.402-9</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G414" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H414" t="inlineStr">
@@ -27046,28 +27046,32 @@
       </c>
       <c r="I414" t="inlineStr">
         <is>
-          <t>ROLAND VORWERK Y COMPANIA LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J414" t="inlineStr">
         <is>
-          <t>78.178.530-k</t>
-        </is>
-      </c>
-      <c r="K414" t="inlineStr"/>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K414" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L414" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M414" s="2" t="n">
-        <v>3396.27</v>
+        <v>1036.31</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>1962-77-CM26</t>
+          <t>1057439-1206-CM26</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
@@ -27092,12 +27096,12 @@
       </c>
       <c r="F415" t="inlineStr">
         <is>
-          <t>61.004.012-8</t>
+          <t>61.606.402-9</t>
         </is>
       </c>
       <c r="G415" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
         </is>
       </c>
       <c r="H415" t="inlineStr">
@@ -27107,26 +27111,22 @@
       </c>
       <c r="I415" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>ROLAND VORWERK Y COMPANIA LIMITADA</t>
         </is>
       </c>
       <c r="J415" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
-        </is>
-      </c>
-      <c r="K415" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>78.178.530-k</t>
+        </is>
+      </c>
+      <c r="K415" t="inlineStr"/>
       <c r="L415" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M415" s="2" t="n">
-        <v>1977.71</v>
+        <v>3396.27</v>
       </c>
     </row>
     <row r="416">
@@ -27327,7 +27327,7 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>2992-66-CM26</t>
+          <t>2992-64-CM26</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
@@ -27386,13 +27386,13 @@
         </is>
       </c>
       <c r="M419" s="2" t="n">
-        <v>2116.12</v>
+        <v>7998.11</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>2992-64-CM26</t>
+          <t>2992-66-CM26</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
@@ -27451,7 +27451,7 @@
         </is>
       </c>
       <c r="M420" s="2" t="n">
-        <v>7998.11</v>
+        <v>2116.12</v>
       </c>
     </row>
     <row r="421">
@@ -28030,7 +28030,7 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>3712-165-CM26</t>
+          <t>3712-208-CM26</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
@@ -28089,13 +28089,13 @@
         </is>
       </c>
       <c r="M430" s="2" t="n">
-        <v>1200.51</v>
+        <v>1020.8</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>3712-208-CM26</t>
+          <t>3712-165-CM26</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
@@ -28154,7 +28154,7 @@
         </is>
       </c>
       <c r="M431" s="2" t="n">
-        <v>1020.8</v>
+        <v>1200.51</v>
       </c>
     </row>
     <row r="432">
@@ -28607,7 +28607,7 @@
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>1057439-1890-CM26</t>
+          <t>1430710-195-CM26</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
@@ -28632,12 +28632,12 @@
       </c>
       <c r="F439" t="inlineStr">
         <is>
-          <t>61.606.402-9</t>
+          <t>61.606.403-7</t>
         </is>
       </c>
       <c r="G439" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE COQUIMBO</t>
         </is>
       </c>
       <c r="H439" t="inlineStr">
@@ -28647,22 +28647,26 @@
       </c>
       <c r="I439" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO VARGAS CASTILLO</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J439" t="inlineStr">
         <is>
-          <t>13.940.082-8</t>
-        </is>
-      </c>
-      <c r="K439" t="inlineStr"/>
+          <t>76.540.457-6</t>
+        </is>
+      </c>
+      <c r="K439" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L439" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M439" s="2" t="n">
-        <v>9472.610000000001</v>
+        <v>3275.93</v>
       </c>
     </row>
     <row r="440">
@@ -28733,7 +28737,7 @@
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>1430710-195-CM26</t>
+          <t>1057439-1890-CM26</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
@@ -28758,12 +28762,12 @@
       </c>
       <c r="F441" t="inlineStr">
         <is>
-          <t>61.606.403-7</t>
+          <t>61.606.402-9</t>
         </is>
       </c>
       <c r="G441" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE COQUIMBO</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
         </is>
       </c>
       <c r="H441" t="inlineStr">
@@ -28773,26 +28777,22 @@
       </c>
       <c r="I441" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>CARLOS ALBERTO VARGAS CASTILLO</t>
         </is>
       </c>
       <c r="J441" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
-        </is>
-      </c>
-      <c r="K441" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>13.940.082-8</t>
+        </is>
+      </c>
+      <c r="K441" t="inlineStr"/>
       <c r="L441" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M441" s="2" t="n">
-        <v>3275.93</v>
+        <v>9472.610000000001</v>
       </c>
     </row>
     <row r="442">
@@ -28928,7 +28928,7 @@
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>3712-159-CM26</t>
+          <t>1232565-48-CM26</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
@@ -28953,12 +28953,12 @@
       </c>
       <c r="F444" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G444" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H444" t="inlineStr">
@@ -28968,12 +28968,12 @@
       </c>
       <c r="I444" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>BAILEY GROUP SPA</t>
         </is>
       </c>
       <c r="J444" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.638.992-7</t>
         </is>
       </c>
       <c r="K444" t="inlineStr">
@@ -28987,13 +28987,13 @@
         </is>
       </c>
       <c r="M444" s="2" t="n">
-        <v>1197.89</v>
+        <v>967.4</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>1232565-48-CM26</t>
+          <t>3712-159-CM26</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
@@ -29018,12 +29018,12 @@
       </c>
       <c r="F445" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G445" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H445" t="inlineStr">
@@ -29033,12 +29033,12 @@
       </c>
       <c r="I445" t="inlineStr">
         <is>
-          <t>BAILEY GROUP SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J445" t="inlineStr">
         <is>
-          <t>77.638.992-7</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K445" t="inlineStr">
@@ -29052,7 +29052,7 @@
         </is>
       </c>
       <c r="M445" s="2" t="n">
-        <v>967.4</v>
+        <v>1197.89</v>
       </c>
     </row>
     <row r="446">
@@ -29188,7 +29188,7 @@
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>3616-30-CM26</t>
+          <t>2146-123-CM26</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
@@ -29208,17 +29208,17 @@
       </c>
       <c r="E448" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F448" t="inlineStr">
         <is>
-          <t>69.041.100-8</t>
+          <t>61.606.405-3</t>
         </is>
       </c>
       <c r="G448" t="inlineStr">
         <is>
-          <t>ILUSTRE MINICIPALIDAD DE COMBARBALA</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE ANDACOLLO</t>
         </is>
       </c>
       <c r="H448" t="inlineStr">
@@ -29247,13 +29247,13 @@
         </is>
       </c>
       <c r="M448" s="2" t="n">
-        <v>5483.22</v>
+        <v>1400.18</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>5416-197-CM26</t>
+          <t>3616-30-CM26</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
@@ -29273,17 +29273,17 @@
       </c>
       <c r="E449" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F449" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>69.041.100-8</t>
         </is>
       </c>
       <c r="G449" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>ILUSTRE MINICIPALIDAD DE COMBARBALA</t>
         </is>
       </c>
       <c r="H449" t="inlineStr">
@@ -29293,17 +29293,17 @@
       </c>
       <c r="I449" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J449" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K449" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L449" t="inlineStr">
@@ -29312,13 +29312,13 @@
         </is>
       </c>
       <c r="M449" s="2" t="n">
-        <v>3368.41</v>
+        <v>5483.22</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>2146-123-CM26</t>
+          <t>5416-197-CM26</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
@@ -29343,12 +29343,12 @@
       </c>
       <c r="F450" t="inlineStr">
         <is>
-          <t>61.606.405-3</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G450" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE ANDACOLLO</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H450" t="inlineStr">
@@ -29358,17 +29358,17 @@
       </c>
       <c r="I450" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J450" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K450" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="L450" t="inlineStr">
@@ -29377,7 +29377,7 @@
         </is>
       </c>
       <c r="M450" s="2" t="n">
-        <v>1400.18</v>
+        <v>3368.41</v>
       </c>
     </row>
     <row r="451">
@@ -29448,7 +29448,7 @@
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>3713-35-CM26</t>
+          <t>3713-36-CM26</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
@@ -29468,7 +29468,7 @@
       </c>
       <c r="E452" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F452" t="inlineStr">
@@ -29488,17 +29488,17 @@
       </c>
       <c r="I452" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J452" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K452" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L452" t="inlineStr">
@@ -29507,13 +29507,13 @@
         </is>
       </c>
       <c r="M452" s="2" t="n">
-        <v>1199.06</v>
+        <v>1441.63</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>3713-36-CM26</t>
+          <t>3713-35-CM26</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
@@ -29533,7 +29533,7 @@
       </c>
       <c r="E453" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F453" t="inlineStr">
@@ -29553,17 +29553,17 @@
       </c>
       <c r="I453" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J453" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K453" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L453" t="inlineStr">
@@ -29572,7 +29572,7 @@
         </is>
       </c>
       <c r="M453" s="2" t="n">
-        <v>1441.63</v>
+        <v>1199.06</v>
       </c>
     </row>
     <row r="454">
@@ -29704,7 +29704,7 @@
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>2992-85-CM26</t>
+          <t>3511-95-CM26</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
@@ -29724,17 +29724,17 @@
       </c>
       <c r="E456" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F456" t="inlineStr">
         <is>
-          <t>69.040.800-7</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G456" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MONTEPATRIA</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H456" t="inlineStr">
@@ -29744,17 +29744,17 @@
       </c>
       <c r="I456" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J456" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K456" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L456" t="inlineStr">
@@ -29763,13 +29763,13 @@
         </is>
       </c>
       <c r="M456" s="2" t="n">
-        <v>1055.81</v>
+        <v>753.8099999999999</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>3511-95-CM26</t>
+          <t>3511-96-CM26</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
@@ -29828,13 +29828,13 @@
         </is>
       </c>
       <c r="M457" s="2" t="n">
-        <v>753.8099999999999</v>
+        <v>1410.7</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>3511-96-CM26</t>
+          <t>3511-97-CM26</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
@@ -29874,32 +29874,28 @@
       </c>
       <c r="I458" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>AMINORTE S A</t>
         </is>
       </c>
       <c r="J458" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
-        </is>
-      </c>
-      <c r="K458" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>99.533.780-0</t>
+        </is>
+      </c>
+      <c r="K458" t="inlineStr"/>
       <c r="L458" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M458" s="2" t="n">
-        <v>1410.7</v>
+        <v>769.84</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>3511-97-CM26</t>
+          <t>2992-85-CM26</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
@@ -29919,17 +29915,17 @@
       </c>
       <c r="E459" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F459" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>69.040.800-7</t>
         </is>
       </c>
       <c r="G459" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>I MUNICIPALIDAD DE MONTEPATRIA</t>
         </is>
       </c>
       <c r="H459" t="inlineStr">
@@ -29939,28 +29935,32 @@
       </c>
       <c r="I459" t="inlineStr">
         <is>
-          <t>AMINORTE S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J459" t="inlineStr">
         <is>
-          <t>99.533.780-0</t>
-        </is>
-      </c>
-      <c r="K459" t="inlineStr"/>
+          <t>77.012.870-6</t>
+        </is>
+      </c>
+      <c r="K459" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L459" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M459" s="2" t="n">
-        <v>769.84</v>
+        <v>1055.81</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>3511-98-CM26</t>
+          <t>1660-226-CM26</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
@@ -29980,17 +29980,17 @@
       </c>
       <c r="E460" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F460" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>61.606.408-8</t>
         </is>
       </c>
       <c r="G460" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>SERVICIO SALUD COQUIMBO HOSP DE SALAMANC</t>
         </is>
       </c>
       <c r="H460" t="inlineStr">
@@ -30000,17 +30000,17 @@
       </c>
       <c r="I460" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J460" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K460" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L460" t="inlineStr">
@@ -30019,13 +30019,13 @@
         </is>
       </c>
       <c r="M460" s="2" t="n">
-        <v>886.38</v>
+        <v>763.74</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>1660-226-CM26</t>
+          <t>3511-98-CM26</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
@@ -30045,17 +30045,17 @@
       </c>
       <c r="E461" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F461" t="inlineStr">
         <is>
-          <t>61.606.408-8</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G461" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD COQUIMBO HOSP DE SALAMANC</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H461" t="inlineStr">
@@ -30065,17 +30065,17 @@
       </c>
       <c r="I461" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J461" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K461" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L461" t="inlineStr">
@@ -30084,7 +30084,7 @@
         </is>
       </c>
       <c r="M461" s="2" t="n">
-        <v>763.74</v>
+        <v>886.38</v>
       </c>
     </row>
     <row r="462">
@@ -30155,7 +30155,7 @@
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>2125-759-CM26</t>
+          <t>548854-16-CM26</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
@@ -30180,12 +30180,12 @@
       </c>
       <c r="F463" t="inlineStr">
         <is>
-          <t>61.606.407-k</t>
+          <t>61.979.440-0</t>
         </is>
       </c>
       <c r="G463" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DR. HUMBERTO ELORZA CORTES</t>
+          <t>INSTITUTO DE PREVISION SOCIAL</t>
         </is>
       </c>
       <c r="H463" t="inlineStr">
@@ -30214,13 +30214,13 @@
         </is>
       </c>
       <c r="M463" s="2" t="n">
-        <v>880.6900000000001</v>
+        <v>6860.64</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>2708-193-CM26</t>
+          <t>2125-759-CM26</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
@@ -30240,17 +30240,17 @@
       </c>
       <c r="E464" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F464" t="inlineStr">
         <is>
-          <t>69.040.700-0</t>
+          <t>61.606.407-k</t>
         </is>
       </c>
       <c r="G464" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE OVALLE</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DR. HUMBERTO ELORZA CORTES</t>
         </is>
       </c>
       <c r="H464" t="inlineStr">
@@ -30279,13 +30279,13 @@
         </is>
       </c>
       <c r="M464" s="2" t="n">
-        <v>929.33</v>
+        <v>880.6900000000001</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>548854-16-CM26</t>
+          <t>2708-193-CM26</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
@@ -30305,17 +30305,17 @@
       </c>
       <c r="E465" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F465" t="inlineStr">
         <is>
-          <t>61.979.440-0</t>
+          <t>69.040.700-0</t>
         </is>
       </c>
       <c r="G465" t="inlineStr">
         <is>
-          <t>INSTITUTO DE PREVISION SOCIAL</t>
+          <t>MUNICIPALIDAD DE OVALLE</t>
         </is>
       </c>
       <c r="H465" t="inlineStr">
@@ -30344,7 +30344,7 @@
         </is>
       </c>
       <c r="M465" s="2" t="n">
-        <v>6860.64</v>
+        <v>929.33</v>
       </c>
     </row>
     <row r="466">
@@ -30415,7 +30415,7 @@
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>1242121-177-CM26</t>
+          <t>1346282-145-CM26</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
@@ -30440,12 +30440,12 @@
       </c>
       <c r="F467" t="inlineStr">
         <is>
-          <t>61.606.404-5</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G467" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE O</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H467" t="inlineStr">
@@ -30474,7 +30474,7 @@
         </is>
       </c>
       <c r="M467" s="2" t="n">
-        <v>4623.35</v>
+        <v>784.3099999999999</v>
       </c>
     </row>
     <row r="468">
@@ -30545,7 +30545,7 @@
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>1346282-145-CM26</t>
+          <t>1242121-177-CM26</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
@@ -30570,12 +30570,12 @@
       </c>
       <c r="F469" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>61.606.404-5</t>
         </is>
       </c>
       <c r="G469" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE O</t>
         </is>
       </c>
       <c r="H469" t="inlineStr">
@@ -30604,13 +30604,13 @@
         </is>
       </c>
       <c r="M469" s="2" t="n">
-        <v>784.3099999999999</v>
+        <v>4623.35</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>1289649-11-CM26</t>
+          <t>1057439-2381-CM26</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
@@ -30635,12 +30635,12 @@
       </c>
       <c r="F470" t="inlineStr">
         <is>
-          <t>60.905.000-4</t>
+          <t>61.606.402-9</t>
         </is>
       </c>
       <c r="G470" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
         </is>
       </c>
       <c r="H470" t="inlineStr">
@@ -30650,12 +30650,12 @@
       </c>
       <c r="I470" t="inlineStr">
         <is>
-          <t>Comercial IBL SpA</t>
+          <t>CARLOS ALBERTO VARGAS CASTILLO</t>
         </is>
       </c>
       <c r="J470" t="inlineStr">
         <is>
-          <t>76.452.485-3</t>
+          <t>13.940.082-8</t>
         </is>
       </c>
       <c r="K470" t="inlineStr"/>
@@ -30665,13 +30665,13 @@
         </is>
       </c>
       <c r="M470" s="2" t="n">
-        <v>1697.98</v>
+        <v>9554.030000000001</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>3511-108-CM26</t>
+          <t>1461054-116-CM26</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
@@ -30691,17 +30691,17 @@
       </c>
       <c r="E471" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F471" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>61.981.040-6</t>
         </is>
       </c>
       <c r="G471" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DEL ELQUI</t>
         </is>
       </c>
       <c r="H471" t="inlineStr">
@@ -30730,7 +30730,7 @@
         </is>
       </c>
       <c r="M471" s="2" t="n">
-        <v>1556.65</v>
+        <v>44593.84</v>
       </c>
     </row>
     <row r="472">
@@ -30801,7 +30801,7 @@
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>1057439-2381-CM26</t>
+          <t>1289649-11-CM26</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
@@ -30826,12 +30826,12 @@
       </c>
       <c r="F473" t="inlineStr">
         <is>
-          <t>61.606.402-9</t>
+          <t>60.905.000-4</t>
         </is>
       </c>
       <c r="G473" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H473" t="inlineStr">
@@ -30841,12 +30841,12 @@
       </c>
       <c r="I473" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO VARGAS CASTILLO</t>
+          <t>Comercial IBL SpA</t>
         </is>
       </c>
       <c r="J473" t="inlineStr">
         <is>
-          <t>13.940.082-8</t>
+          <t>76.452.485-3</t>
         </is>
       </c>
       <c r="K473" t="inlineStr"/>
@@ -30856,13 +30856,13 @@
         </is>
       </c>
       <c r="M473" s="2" t="n">
-        <v>9554.030000000001</v>
+        <v>1697.98</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>1461054-116-CM26</t>
+          <t>3511-108-CM26</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
@@ -30882,17 +30882,17 @@
       </c>
       <c r="E474" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F474" t="inlineStr">
         <is>
-          <t>61.981.040-6</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G474" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DEL ELQUI</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H474" t="inlineStr">
@@ -30921,7 +30921,7 @@
         </is>
       </c>
       <c r="M474" s="2" t="n">
-        <v>44593.84</v>
+        <v>1556.65</v>
       </c>
     </row>
     <row r="475">
@@ -30992,7 +30992,7 @@
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>2708-229-CM26</t>
+          <t>3614-44-CM26</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
@@ -31012,17 +31012,17 @@
       </c>
       <c r="E476" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F476" t="inlineStr">
         <is>
-          <t>69.040.700-0</t>
+          <t>69.040.500-8</t>
         </is>
       </c>
       <c r="G476" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE OVALLE</t>
+          <t>I MUNICIPALIDAD DE VICUNA</t>
         </is>
       </c>
       <c r="H476" t="inlineStr">
@@ -31051,13 +31051,13 @@
         </is>
       </c>
       <c r="M476" s="2" t="n">
-        <v>1023.35</v>
+        <v>810.02</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>3614-44-CM26</t>
+          <t>2708-229-CM26</t>
         </is>
       </c>
       <c r="B477" t="inlineStr">
@@ -31077,17 +31077,17 @@
       </c>
       <c r="E477" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F477" t="inlineStr">
         <is>
-          <t>69.040.500-8</t>
+          <t>69.040.700-0</t>
         </is>
       </c>
       <c r="G477" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VICUNA</t>
+          <t>MUNICIPALIDAD DE OVALLE</t>
         </is>
       </c>
       <c r="H477" t="inlineStr">
@@ -31116,7 +31116,7 @@
         </is>
       </c>
       <c r="M477" s="2" t="n">
-        <v>810.02</v>
+        <v>1023.35</v>
       </c>
     </row>
     <row r="478">
@@ -31638,7 +31638,7 @@
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>5416-345-CM26</t>
+          <t>1232820-55-CM26</t>
         </is>
       </c>
       <c r="B486" t="inlineStr">
@@ -31658,17 +31658,17 @@
       </c>
       <c r="E486" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F486" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>65.080.284-5</t>
         </is>
       </c>
       <c r="G486" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>CORPORACION MUNICIPAL DE TURISMO VICUNA</t>
         </is>
       </c>
       <c r="H486" t="inlineStr">
@@ -31678,17 +31678,17 @@
       </c>
       <c r="I486" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J486" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K486" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L486" t="inlineStr">
@@ -31697,13 +31697,13 @@
         </is>
       </c>
       <c r="M486" s="2" t="n">
-        <v>951.66</v>
+        <v>795.16</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>3712-301-CM26</t>
+          <t>5416-345-CM26</t>
         </is>
       </c>
       <c r="B487" t="inlineStr">
@@ -31728,12 +31728,12 @@
       </c>
       <c r="F487" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G487" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H487" t="inlineStr">
@@ -31743,17 +31743,17 @@
       </c>
       <c r="I487" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J487" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K487" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="L487" t="inlineStr">
@@ -31762,13 +31762,13 @@
         </is>
       </c>
       <c r="M487" s="2" t="n">
-        <v>1455.94</v>
+        <v>951.66</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>1232820-55-CM26</t>
+          <t>3712-301-CM26</t>
         </is>
       </c>
       <c r="B488" t="inlineStr">
@@ -31788,17 +31788,17 @@
       </c>
       <c r="E488" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F488" t="inlineStr">
         <is>
-          <t>65.080.284-5</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G488" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE TURISMO VICUNA</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H488" t="inlineStr">
@@ -31827,7 +31827,7 @@
         </is>
       </c>
       <c r="M488" s="2" t="n">
-        <v>795.16</v>
+        <v>1455.94</v>
       </c>
     </row>
     <row r="489">
@@ -32410,7 +32410,7 @@
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>2710-204-CM26</t>
+          <t>2710-201-CM26</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
@@ -32430,7 +32430,7 @@
       </c>
       <c r="E498" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F498" t="inlineStr">
@@ -32450,17 +32450,17 @@
       </c>
       <c r="I498" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J498" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K498" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L498" t="inlineStr">
@@ -32469,7 +32469,7 @@
         </is>
       </c>
       <c r="M498" s="2" t="n">
-        <v>13054.6</v>
+        <v>27569.02</v>
       </c>
     </row>
     <row r="499">
@@ -32540,7 +32540,7 @@
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>2710-201-CM26</t>
+          <t>2710-204-CM26</t>
         </is>
       </c>
       <c r="B500" t="inlineStr">
@@ -32560,7 +32560,7 @@
       </c>
       <c r="E500" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F500" t="inlineStr">
@@ -32580,17 +32580,17 @@
       </c>
       <c r="I500" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J500" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>77.474.803-2</t>
         </is>
       </c>
       <c r="K500" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="L500" t="inlineStr">
@@ -32599,7 +32599,7 @@
         </is>
       </c>
       <c r="M500" s="2" t="n">
-        <v>27569.02</v>
+        <v>13054.6</v>
       </c>
     </row>
     <row r="501">
@@ -32792,7 +32792,7 @@
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>1004823-47-CM26</t>
+          <t>2125-1018-CM26</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
@@ -32812,17 +32812,17 @@
       </c>
       <c r="E504" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F504" t="inlineStr">
         <is>
-          <t>61.999.280-6</t>
+          <t>61.606.407-k</t>
         </is>
       </c>
       <c r="G504" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACION TECNICA DE LA REGION DE COQUIMBO</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DR. HUMBERTO ELORZA CORTES</t>
         </is>
       </c>
       <c r="H504" t="inlineStr">
@@ -32832,17 +32832,17 @@
       </c>
       <c r="I504" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J504" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K504" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L504" t="inlineStr">
@@ -32851,13 +32851,13 @@
         </is>
       </c>
       <c r="M504" s="2" t="n">
-        <v>3866.2</v>
+        <v>872.66</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>2125-1018-CM26</t>
+          <t>1004823-47-CM26</t>
         </is>
       </c>
       <c r="B505" t="inlineStr">
@@ -32877,17 +32877,17 @@
       </c>
       <c r="E505" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F505" t="inlineStr">
         <is>
-          <t>61.606.407-k</t>
+          <t>61.999.280-6</t>
         </is>
       </c>
       <c r="G505" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DR. HUMBERTO ELORZA CORTES</t>
+          <t>CENTRO DE FORMACION TECNICA DE LA REGION DE COQUIMBO</t>
         </is>
       </c>
       <c r="H505" t="inlineStr">
@@ -32897,17 +32897,17 @@
       </c>
       <c r="I505" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J505" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K505" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="L505" t="inlineStr">
@@ -32916,13 +32916,13 @@
         </is>
       </c>
       <c r="M505" s="2" t="n">
-        <v>872.66</v>
+        <v>3866.2</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>4295-54-CM26</t>
+          <t>4295-53-CM26</t>
         </is>
       </c>
       <c r="B506" t="inlineStr">
@@ -32962,28 +32962,32 @@
       </c>
       <c r="I506" t="inlineStr">
         <is>
-          <t>BARDANE SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J506" t="inlineStr">
         <is>
-          <t>77.205.722-9</t>
-        </is>
-      </c>
-      <c r="K506" t="inlineStr"/>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K506" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L506" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M506" s="2" t="n">
-        <v>9664.629999999999</v>
+        <v>35758.86</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>4295-53-CM26</t>
+          <t>4295-54-CM26</t>
         </is>
       </c>
       <c r="B507" t="inlineStr">
@@ -33023,32 +33027,28 @@
       </c>
       <c r="I507" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>BARDANE SPA</t>
         </is>
       </c>
       <c r="J507" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
-        </is>
-      </c>
-      <c r="K507" t="inlineStr">
-        <is>
-          <t>Antofagasta</t>
-        </is>
-      </c>
+          <t>77.205.722-9</t>
+        </is>
+      </c>
+      <c r="K507" t="inlineStr"/>
       <c r="L507" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M507" s="2" t="n">
-        <v>35758.86</v>
+        <v>9664.629999999999</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>5416-435-CM26</t>
+          <t>3511-160-CM26</t>
         </is>
       </c>
       <c r="B508" t="inlineStr">
@@ -33068,17 +33068,17 @@
       </c>
       <c r="E508" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F508" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G508" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H508" t="inlineStr">
@@ -33088,17 +33088,17 @@
       </c>
       <c r="I508" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>CASTILLA Y ARAGON SPA</t>
         </is>
       </c>
       <c r="J508" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.989.530-7</t>
         </is>
       </c>
       <c r="K508" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L508" t="inlineStr">
@@ -33107,7 +33107,7 @@
         </is>
       </c>
       <c r="M508" s="2" t="n">
-        <v>1702.06</v>
+        <v>2070.66</v>
       </c>
     </row>
     <row r="509">
@@ -33178,7 +33178,7 @@
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>3511-160-CM26</t>
+          <t>5416-435-CM26</t>
         </is>
       </c>
       <c r="B510" t="inlineStr">
@@ -33198,17 +33198,17 @@
       </c>
       <c r="E510" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F510" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G510" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H510" t="inlineStr">
@@ -33218,17 +33218,17 @@
       </c>
       <c r="I510" t="inlineStr">
         <is>
-          <t>CASTILLA Y ARAGON SPA</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J510" t="inlineStr">
         <is>
-          <t>96.989.530-7</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K510" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="L510" t="inlineStr">
@@ -33237,7 +33237,7 @@
         </is>
       </c>
       <c r="M510" s="2" t="n">
-        <v>2070.66</v>
+        <v>1702.06</v>
       </c>
     </row>
     <row r="511">
@@ -33373,7 +33373,7 @@
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>1430710-357-CM26</t>
+          <t>1461054-178-CM26</t>
         </is>
       </c>
       <c r="B513" t="inlineStr">
@@ -33398,12 +33398,12 @@
       </c>
       <c r="F513" t="inlineStr">
         <is>
-          <t>61.606.403-7</t>
+          <t>61.981.040-6</t>
         </is>
       </c>
       <c r="G513" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE COQUIMBO</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DEL ELQUI</t>
         </is>
       </c>
       <c r="H513" t="inlineStr">
@@ -33413,12 +33413,12 @@
       </c>
       <c r="I513" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J513" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K513" t="inlineStr">
@@ -33432,13 +33432,13 @@
         </is>
       </c>
       <c r="M513" s="2" t="n">
-        <v>5739.47</v>
+        <v>2205.7</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>1461054-178-CM26</t>
+          <t>1430710-357-CM26</t>
         </is>
       </c>
       <c r="B514" t="inlineStr">
@@ -33463,12 +33463,12 @@
       </c>
       <c r="F514" t="inlineStr">
         <is>
-          <t>61.981.040-6</t>
+          <t>61.606.403-7</t>
         </is>
       </c>
       <c r="G514" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DEL ELQUI</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE COQUIMBO</t>
         </is>
       </c>
       <c r="H514" t="inlineStr">
@@ -33478,12 +33478,12 @@
       </c>
       <c r="I514" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J514" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K514" t="inlineStr">
@@ -33497,13 +33497,13 @@
         </is>
       </c>
       <c r="M514" s="2" t="n">
-        <v>2205.7</v>
+        <v>5739.47</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>3714-110-CM26</t>
+          <t>3509-197-CM26</t>
         </is>
       </c>
       <c r="B515" t="inlineStr">
@@ -33523,17 +33523,17 @@
       </c>
       <c r="E515" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F515" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G515" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H515" t="inlineStr">
@@ -33543,28 +33543,32 @@
       </c>
       <c r="I515" t="inlineStr">
         <is>
-          <t>SURTI VENTAS S.A.</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J515" t="inlineStr">
         <is>
-          <t>76.462.500-5</t>
-        </is>
-      </c>
-      <c r="K515" t="inlineStr"/>
+          <t>77.012.870-6</t>
+        </is>
+      </c>
+      <c r="K515" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L515" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M515" s="2" t="n">
-        <v>3748.11</v>
+        <v>786.61</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>3509-197-CM26</t>
+          <t>3714-109-CM26</t>
         </is>
       </c>
       <c r="B516" t="inlineStr">
@@ -33584,17 +33588,17 @@
       </c>
       <c r="E516" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F516" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G516" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H516" t="inlineStr">
@@ -33604,32 +33608,28 @@
       </c>
       <c r="I516" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>SURTI VENTAS S.A.</t>
         </is>
       </c>
       <c r="J516" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
-        </is>
-      </c>
-      <c r="K516" t="inlineStr">
-        <is>
-          <t>Coquimbo</t>
-        </is>
-      </c>
+          <t>76.462.500-5</t>
+        </is>
+      </c>
+      <c r="K516" t="inlineStr"/>
       <c r="L516" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M516" s="2" t="n">
-        <v>786.61</v>
+        <v>871.65</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>3714-109-CM26</t>
+          <t>3714-110-CM26</t>
         </is>
       </c>
       <c r="B517" t="inlineStr">
@@ -33684,7 +33684,7 @@
         </is>
       </c>
       <c r="M517" s="2" t="n">
-        <v>871.65</v>
+        <v>3748.11</v>
       </c>
     </row>
     <row r="518">
@@ -33885,7 +33885,7 @@
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>3512-520-CM26</t>
+          <t>1232565-123-CM26</t>
         </is>
       </c>
       <c r="B521" t="inlineStr">
@@ -33905,17 +33905,17 @@
       </c>
       <c r="E521" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F521" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G521" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H521" t="inlineStr">
@@ -33925,28 +33925,32 @@
       </c>
       <c r="I521" t="inlineStr">
         <is>
-          <t>AMINORTE S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J521" t="inlineStr">
         <is>
-          <t>99.533.780-0</t>
-        </is>
-      </c>
-      <c r="K521" t="inlineStr"/>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K521" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L521" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M521" s="2" t="n">
-        <v>2180.91</v>
+        <v>2793.88</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>1232565-123-CM26</t>
+          <t>3512-520-CM26</t>
         </is>
       </c>
       <c r="B522" t="inlineStr">
@@ -33966,17 +33970,17 @@
       </c>
       <c r="E522" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F522" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G522" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H522" t="inlineStr">
@@ -33986,26 +33990,22 @@
       </c>
       <c r="I522" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>AMINORTE S A</t>
         </is>
       </c>
       <c r="J522" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
-        </is>
-      </c>
-      <c r="K522" t="inlineStr">
-        <is>
-          <t>Antofagasta</t>
-        </is>
-      </c>
+          <t>99.533.780-0</t>
+        </is>
+      </c>
+      <c r="K522" t="inlineStr"/>
       <c r="L522" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M522" s="2" t="n">
-        <v>2793.88</v>
+        <v>2180.91</v>
       </c>
     </row>
     <row r="523">
@@ -34336,7 +34336,7 @@
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>3509-220-CM26</t>
+          <t>1574-77-CM26</t>
         </is>
       </c>
       <c r="B528" t="inlineStr">
@@ -34356,17 +34356,17 @@
       </c>
       <c r="E528" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F528" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G528" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H528" t="inlineStr">
@@ -34376,17 +34376,17 @@
       </c>
       <c r="I528" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J528" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K528" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L528" t="inlineStr">
@@ -34395,13 +34395,13 @@
         </is>
       </c>
       <c r="M528" s="2" t="n">
-        <v>1805.68</v>
+        <v>4851.02</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>1574-77-CM26</t>
+          <t>1574-78-CM26</t>
         </is>
       </c>
       <c r="B529" t="inlineStr">
@@ -34421,7 +34421,7 @@
       </c>
       <c r="E529" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F529" t="inlineStr">
@@ -34460,13 +34460,13 @@
         </is>
       </c>
       <c r="M529" s="2" t="n">
-        <v>4851.02</v>
+        <v>2148.75</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>1574-78-CM26</t>
+          <t>3509-220-CM26</t>
         </is>
       </c>
       <c r="B530" t="inlineStr">
@@ -34491,12 +34491,12 @@
       </c>
       <c r="F530" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G530" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H530" t="inlineStr">
@@ -34506,17 +34506,17 @@
       </c>
       <c r="I530" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J530" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K530" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="L530" t="inlineStr">
@@ -34525,7 +34525,7 @@
         </is>
       </c>
       <c r="M530" s="2" t="n">
-        <v>2148.75</v>
+        <v>1805.68</v>
       </c>
     </row>
     <row r="531">
@@ -34787,7 +34787,7 @@
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>2708-318-CM26</t>
+          <t>1159-141-CM26</t>
         </is>
       </c>
       <c r="B535" t="inlineStr">
@@ -34807,17 +34807,17 @@
       </c>
       <c r="E535" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F535" t="inlineStr">
         <is>
-          <t>69.040.700-0</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G535" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE OVALLE</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H535" t="inlineStr">
@@ -34827,17 +34827,17 @@
       </c>
       <c r="I535" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>IMPORTADORA Y COMERCIALIZADORA JMMB SPA</t>
         </is>
       </c>
       <c r="J535" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.461.733-7</t>
         </is>
       </c>
       <c r="K535" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L535" t="inlineStr">
@@ -34846,13 +34846,13 @@
         </is>
       </c>
       <c r="M535" s="2" t="n">
-        <v>6281.81</v>
+        <v>4063.8</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>1159-141-CM26</t>
+          <t>2708-318-CM26</t>
         </is>
       </c>
       <c r="B536" t="inlineStr">
@@ -34872,17 +34872,17 @@
       </c>
       <c r="E536" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F536" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>69.040.700-0</t>
         </is>
       </c>
       <c r="G536" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>MUNICIPALIDAD DE OVALLE</t>
         </is>
       </c>
       <c r="H536" t="inlineStr">
@@ -34892,17 +34892,17 @@
       </c>
       <c r="I536" t="inlineStr">
         <is>
-          <t>IMPORTADORA Y COMERCIALIZADORA JMMB SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J536" t="inlineStr">
         <is>
-          <t>77.461.733-7</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K536" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L536" t="inlineStr">
@@ -34911,13 +34911,13 @@
         </is>
       </c>
       <c r="M536" s="2" t="n">
-        <v>4063.8</v>
+        <v>6281.81</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>697055-32-CM26</t>
+          <t>3884-263-CM26</t>
         </is>
       </c>
       <c r="B537" t="inlineStr">
@@ -34942,12 +34942,12 @@
       </c>
       <c r="F537" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>69.040.600-4</t>
         </is>
       </c>
       <c r="G537" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>I MUNICIPALIDAD PAIHUANO</t>
         </is>
       </c>
       <c r="H537" t="inlineStr">
@@ -34957,17 +34957,17 @@
       </c>
       <c r="I537" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J537" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K537" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L537" t="inlineStr">
@@ -34976,13 +34976,13 @@
         </is>
       </c>
       <c r="M537" s="2" t="n">
-        <v>4898.03</v>
+        <v>2502.48</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>2711-150-CM26</t>
+          <t>1057439-3953-CM26</t>
         </is>
       </c>
       <c r="B538" t="inlineStr">
@@ -35002,17 +35002,17 @@
       </c>
       <c r="E538" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F538" t="inlineStr">
         <is>
-          <t>69.040.700-0</t>
+          <t>61.606.402-9</t>
         </is>
       </c>
       <c r="G538" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE OVALLE</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
         </is>
       </c>
       <c r="H538" t="inlineStr">
@@ -35022,32 +35022,28 @@
       </c>
       <c r="I538" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>ROLAND VORWERK Y COMPANIA LIMITADA</t>
         </is>
       </c>
       <c r="J538" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
-        </is>
-      </c>
-      <c r="K538" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>78.178.530-k</t>
+        </is>
+      </c>
+      <c r="K538" t="inlineStr"/>
       <c r="L538" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M538" s="2" t="n">
-        <v>6348.66</v>
+        <v>1586.78</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>1057439-3953-CM26</t>
+          <t>697055-32-CM26</t>
         </is>
       </c>
       <c r="B539" t="inlineStr">
@@ -35072,12 +35068,12 @@
       </c>
       <c r="F539" t="inlineStr">
         <is>
-          <t>61.606.402-9</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G539" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H539" t="inlineStr">
@@ -35087,28 +35083,32 @@
       </c>
       <c r="I539" t="inlineStr">
         <is>
-          <t>ROLAND VORWERK Y COMPANIA LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J539" t="inlineStr">
         <is>
-          <t>78.178.530-k</t>
-        </is>
-      </c>
-      <c r="K539" t="inlineStr"/>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K539" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L539" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M539" s="2" t="n">
-        <v>1586.78</v>
+        <v>4898.03</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>3884-263-CM26</t>
+          <t>2711-150-CM26</t>
         </is>
       </c>
       <c r="B540" t="inlineStr">
@@ -35128,17 +35128,17 @@
       </c>
       <c r="E540" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F540" t="inlineStr">
         <is>
-          <t>69.040.600-4</t>
+          <t>69.040.700-0</t>
         </is>
       </c>
       <c r="G540" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD PAIHUANO</t>
+          <t>MUNICIPALIDAD DE OVALLE</t>
         </is>
       </c>
       <c r="H540" t="inlineStr">
@@ -35148,17 +35148,17 @@
       </c>
       <c r="I540" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J540" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K540" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L540" t="inlineStr">
@@ -35167,7 +35167,7 @@
         </is>
       </c>
       <c r="M540" s="2" t="n">
-        <v>2502.48</v>
+        <v>6348.66</v>
       </c>
     </row>
     <row r="541">
@@ -35303,7 +35303,7 @@
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>2992-193-CM26</t>
+          <t>3712-412-CM26</t>
         </is>
       </c>
       <c r="B543" t="inlineStr">
@@ -35328,12 +35328,12 @@
       </c>
       <c r="F543" t="inlineStr">
         <is>
-          <t>69.040.800-7</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G543" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MONTEPATRIA</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H543" t="inlineStr">
@@ -35343,17 +35343,17 @@
       </c>
       <c r="I543" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J543" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>77.346.435-9</t>
         </is>
       </c>
       <c r="K543" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L543" t="inlineStr">
@@ -35362,13 +35362,13 @@
         </is>
       </c>
       <c r="M543" s="2" t="n">
-        <v>1972.16</v>
+        <v>1131.91</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>3712-412-CM26</t>
+          <t>3712-413-CM26</t>
         </is>
       </c>
       <c r="B544" t="inlineStr">
@@ -35427,13 +35427,13 @@
         </is>
       </c>
       <c r="M544" s="2" t="n">
-        <v>1131.91</v>
+        <v>1308.28</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>3712-413-CM26</t>
+          <t>2992-193-CM26</t>
         </is>
       </c>
       <c r="B545" t="inlineStr">
@@ -35458,12 +35458,12 @@
       </c>
       <c r="F545" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>69.040.800-7</t>
         </is>
       </c>
       <c r="G545" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>I MUNICIPALIDAD DE MONTEPATRIA</t>
         </is>
       </c>
       <c r="H545" t="inlineStr">
@@ -35473,17 +35473,17 @@
       </c>
       <c r="I545" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J545" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K545" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="L545" t="inlineStr">
@@ -35492,13 +35492,13 @@
         </is>
       </c>
       <c r="M545" s="2" t="n">
-        <v>1308.28</v>
+        <v>1972.16</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>2992-211-CM26</t>
+          <t>2125-1292-CM26</t>
         </is>
       </c>
       <c r="B546" t="inlineStr">
@@ -35523,12 +35523,12 @@
       </c>
       <c r="F546" t="inlineStr">
         <is>
-          <t>69.040.800-7</t>
+          <t>61.606.407-k</t>
         </is>
       </c>
       <c r="G546" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MONTEPATRIA</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DR. HUMBERTO ELORZA CORTES</t>
         </is>
       </c>
       <c r="H546" t="inlineStr">
@@ -35538,17 +35538,17 @@
       </c>
       <c r="I546" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J546" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K546" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L546" t="inlineStr">
@@ -35557,13 +35557,13 @@
         </is>
       </c>
       <c r="M546" s="2" t="n">
-        <v>5014.22</v>
+        <v>1352.97</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>2125-1292-CM26</t>
+          <t>2992-211-CM26</t>
         </is>
       </c>
       <c r="B547" t="inlineStr">
@@ -35588,12 +35588,12 @@
       </c>
       <c r="F547" t="inlineStr">
         <is>
-          <t>61.606.407-k</t>
+          <t>69.040.800-7</t>
         </is>
       </c>
       <c r="G547" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DR. HUMBERTO ELORZA CORTES</t>
+          <t>I MUNICIPALIDAD DE MONTEPATRIA</t>
         </is>
       </c>
       <c r="H547" t="inlineStr">
@@ -35603,17 +35603,17 @@
       </c>
       <c r="I547" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J547" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K547" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="L547" t="inlineStr">
@@ -35622,13 +35622,13 @@
         </is>
       </c>
       <c r="M547" s="2" t="n">
-        <v>1352.97</v>
+        <v>5014.22</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>1079505-335-CM26</t>
+          <t>2711-156-CM26</t>
         </is>
       </c>
       <c r="B548" t="inlineStr">
@@ -35648,17 +35648,17 @@
       </c>
       <c r="E548" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F548" t="inlineStr">
         <is>
-          <t>60.505.206-1</t>
+          <t>69.040.700-0</t>
         </is>
       </c>
       <c r="G548" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>MUNICIPALIDAD DE OVALLE</t>
         </is>
       </c>
       <c r="H548" t="inlineStr">
@@ -35668,17 +35668,17 @@
       </c>
       <c r="I548" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J548" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K548" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L548" t="inlineStr">
@@ -35687,13 +35687,13 @@
         </is>
       </c>
       <c r="M548" s="2" t="n">
-        <v>1113.87</v>
+        <v>865.65</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>2711-156-CM26</t>
+          <t>1079505-335-CM26</t>
         </is>
       </c>
       <c r="B549" t="inlineStr">
@@ -35713,17 +35713,17 @@
       </c>
       <c r="E549" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F549" t="inlineStr">
         <is>
-          <t>69.040.700-0</t>
+          <t>60.505.206-1</t>
         </is>
       </c>
       <c r="G549" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE OVALLE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H549" t="inlineStr">
@@ -35733,17 +35733,17 @@
       </c>
       <c r="I549" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J549" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K549" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L549" t="inlineStr">
@@ -35752,7 +35752,7 @@
         </is>
       </c>
       <c r="M549" s="2" t="n">
-        <v>865.65</v>
+        <v>1113.87</v>
       </c>
     </row>
     <row r="550">
@@ -35823,7 +35823,7 @@
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>3276-9446-CM26</t>
+          <t>1079505-341-CM26</t>
         </is>
       </c>
       <c r="B551" t="inlineStr">
@@ -35848,12 +35848,12 @@
       </c>
       <c r="F551" t="inlineStr">
         <is>
-          <t>60.506.000-5</t>
+          <t>60.505.206-1</t>
         </is>
       </c>
       <c r="G551" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H551" t="inlineStr">
@@ -35863,17 +35863,17 @@
       </c>
       <c r="I551" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J551" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K551" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L551" t="inlineStr">
@@ -35882,13 +35882,13 @@
         </is>
       </c>
       <c r="M551" s="2" t="n">
-        <v>2310.93</v>
+        <v>4061.88</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>1079505-341-CM26</t>
+          <t>3276-9446-CM26</t>
         </is>
       </c>
       <c r="B552" t="inlineStr">
@@ -35913,12 +35913,12 @@
       </c>
       <c r="F552" t="inlineStr">
         <is>
-          <t>60.505.206-1</t>
+          <t>60.506.000-5</t>
         </is>
       </c>
       <c r="G552" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H552" t="inlineStr">
@@ -35928,17 +35928,17 @@
       </c>
       <c r="I552" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J552" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K552" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L552" t="inlineStr">
@@ -35947,7 +35947,7 @@
         </is>
       </c>
       <c r="M552" s="2" t="n">
-        <v>4061.88</v>
+        <v>2310.93</v>
       </c>
     </row>
     <row r="553">
@@ -36148,7 +36148,7 @@
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>1962-370-CM26</t>
+          <t>1574-102-CM26</t>
         </is>
       </c>
       <c r="B556" t="inlineStr">
@@ -36173,12 +36173,12 @@
       </c>
       <c r="F556" t="inlineStr">
         <is>
-          <t>61.004.012-8</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G556" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H556" t="inlineStr">
@@ -36188,17 +36188,17 @@
       </c>
       <c r="I556" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>IMPORTADORA Y COMERCIALIZADORA JMMB SPA</t>
         </is>
       </c>
       <c r="J556" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>77.461.733-7</t>
         </is>
       </c>
       <c r="K556" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L556" t="inlineStr">
@@ -36207,13 +36207,13 @@
         </is>
       </c>
       <c r="M556" s="2" t="n">
-        <v>1801.34</v>
+        <v>3120.97</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>1574-102-CM26</t>
+          <t>1574-103-CM26</t>
         </is>
       </c>
       <c r="B557" t="inlineStr">
@@ -36272,13 +36272,13 @@
         </is>
       </c>
       <c r="M557" s="2" t="n">
-        <v>3120.97</v>
+        <v>1584.15</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>1574-103-CM26</t>
+          <t>1352-56-CM26</t>
         </is>
       </c>
       <c r="B558" t="inlineStr">
@@ -36298,17 +36298,17 @@
       </c>
       <c r="E558" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F558" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>61.002.010-0</t>
         </is>
       </c>
       <c r="G558" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
         </is>
       </c>
       <c r="H558" t="inlineStr">
@@ -36318,17 +36318,17 @@
       </c>
       <c r="I558" t="inlineStr">
         <is>
-          <t>IMPORTADORA Y COMERCIALIZADORA JMMB SPA</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J558" t="inlineStr">
         <is>
-          <t>77.461.733-7</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K558" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="L558" t="inlineStr">
@@ -36337,13 +36337,13 @@
         </is>
       </c>
       <c r="M558" s="2" t="n">
-        <v>1584.15</v>
+        <v>1115.85</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>1352-56-CM26</t>
+          <t>1962-370-CM26</t>
         </is>
       </c>
       <c r="B559" t="inlineStr">
@@ -36363,17 +36363,17 @@
       </c>
       <c r="E559" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F559" t="inlineStr">
         <is>
-          <t>61.002.010-0</t>
+          <t>61.004.012-8</t>
         </is>
       </c>
       <c r="G559" t="inlineStr">
         <is>
-          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H559" t="inlineStr">
@@ -36402,13 +36402,13 @@
         </is>
       </c>
       <c r="M559" s="2" t="n">
-        <v>1115.85</v>
+        <v>1801.34</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>2992-230-CM26</t>
+          <t>1159-175-CM26</t>
         </is>
       </c>
       <c r="B560" t="inlineStr">
@@ -36433,12 +36433,12 @@
       </c>
       <c r="F560" t="inlineStr">
         <is>
-          <t>69.040.800-7</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G560" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MONTEPATRIA</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H560" t="inlineStr">
@@ -36448,17 +36448,17 @@
       </c>
       <c r="I560" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J560" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K560" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L560" t="inlineStr">
@@ -36467,7 +36467,7 @@
         </is>
       </c>
       <c r="M560" s="2" t="n">
-        <v>4947.34</v>
+        <v>1720.66</v>
       </c>
     </row>
     <row r="561">
@@ -36538,7 +36538,7 @@
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>2288-580-CM26</t>
+          <t>2992-233-CM26</t>
         </is>
       </c>
       <c r="B562" t="inlineStr">
@@ -36563,12 +36563,12 @@
       </c>
       <c r="F562" t="inlineStr">
         <is>
-          <t>69.041.300-0</t>
+          <t>69.040.800-7</t>
         </is>
       </c>
       <c r="G562" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CANELA</t>
+          <t>I MUNICIPALIDAD DE MONTEPATRIA</t>
         </is>
       </c>
       <c r="H562" t="inlineStr">
@@ -36578,17 +36578,17 @@
       </c>
       <c r="I562" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J562" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K562" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="L562" t="inlineStr">
@@ -36597,13 +36597,13 @@
         </is>
       </c>
       <c r="M562" s="2" t="n">
-        <v>2165.13</v>
+        <v>2950.02</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>1159-175-CM26</t>
+          <t>2288-580-CM26</t>
         </is>
       </c>
       <c r="B563" t="inlineStr">
@@ -36628,12 +36628,12 @@
       </c>
       <c r="F563" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>69.041.300-0</t>
         </is>
       </c>
       <c r="G563" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>I MUNICIPALIDAD DE CANELA</t>
         </is>
       </c>
       <c r="H563" t="inlineStr">
@@ -36662,13 +36662,13 @@
         </is>
       </c>
       <c r="M563" s="2" t="n">
-        <v>1720.66</v>
+        <v>2165.13</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>2992-233-CM26</t>
+          <t>2992-230-CM26</t>
         </is>
       </c>
       <c r="B564" t="inlineStr">
@@ -36727,7 +36727,7 @@
         </is>
       </c>
       <c r="M564" s="2" t="n">
-        <v>2950.02</v>
+        <v>4947.34</v>
       </c>
     </row>
     <row r="565">
@@ -36928,7 +36928,7 @@
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>5416-661-CM26</t>
+          <t>2992-232-CM26</t>
         </is>
       </c>
       <c r="B568" t="inlineStr">
@@ -36953,12 +36953,12 @@
       </c>
       <c r="F568" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>69.040.800-7</t>
         </is>
       </c>
       <c r="G568" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>I MUNICIPALIDAD DE MONTEPATRIA</t>
         </is>
       </c>
       <c r="H568" t="inlineStr">
@@ -36987,13 +36987,13 @@
         </is>
       </c>
       <c r="M568" s="2" t="n">
-        <v>1406.77</v>
+        <v>5094.85</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>2992-232-CM26</t>
+          <t>5416-661-CM26</t>
         </is>
       </c>
       <c r="B569" t="inlineStr">
@@ -37018,12 +37018,12 @@
       </c>
       <c r="F569" t="inlineStr">
         <is>
-          <t>69.040.800-7</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G569" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MONTEPATRIA</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H569" t="inlineStr">
@@ -37052,7 +37052,7 @@
         </is>
       </c>
       <c r="M569" s="2" t="n">
-        <v>5094.85</v>
+        <v>1406.77</v>
       </c>
     </row>
     <row r="570">
@@ -37253,7 +37253,7 @@
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>3712-449-CM26</t>
+          <t>1660-591-CM26</t>
         </is>
       </c>
       <c r="B573" t="inlineStr">
@@ -37278,12 +37278,12 @@
       </c>
       <c r="F573" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>61.606.408-8</t>
         </is>
       </c>
       <c r="G573" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>SERVICIO SALUD COQUIMBO HOSP DE SALAMANC</t>
         </is>
       </c>
       <c r="H573" t="inlineStr">
@@ -37293,12 +37293,12 @@
       </c>
       <c r="I573" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J573" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K573" t="inlineStr">
@@ -37312,13 +37312,13 @@
         </is>
       </c>
       <c r="M573" s="2" t="n">
-        <v>921.77</v>
+        <v>2877.65</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>1660-591-CM26</t>
+          <t>3712-449-CM26</t>
         </is>
       </c>
       <c r="B574" t="inlineStr">
@@ -37343,12 +37343,12 @@
       </c>
       <c r="F574" t="inlineStr">
         <is>
-          <t>61.606.408-8</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G574" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD COQUIMBO HOSP DE SALAMANC</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H574" t="inlineStr">
@@ -37358,12 +37358,12 @@
       </c>
       <c r="I574" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J574" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.346.435-9</t>
         </is>
       </c>
       <c r="K574" t="inlineStr">
@@ -37377,7 +37377,7 @@
         </is>
       </c>
       <c r="M574" s="2" t="n">
-        <v>2877.65</v>
+        <v>921.77</v>
       </c>
     </row>
     <row r="575">
@@ -37769,7 +37769,7 @@
     <row r="581">
       <c r="A581" t="inlineStr">
         <is>
-          <t>1057439-4523-CM26</t>
+          <t>1057439-4554-CM26</t>
         </is>
       </c>
       <c r="B581" t="inlineStr">
@@ -37809,28 +37809,32 @@
       </c>
       <c r="I581" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO VARGAS CASTILLO</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J581" t="inlineStr">
         <is>
-          <t>13.940.082-8</t>
-        </is>
-      </c>
-      <c r="K581" t="inlineStr"/>
+          <t>77.012.870-6</t>
+        </is>
+      </c>
+      <c r="K581" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L581" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M581" s="2" t="n">
-        <v>8135.62</v>
+        <v>2780.09</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="inlineStr">
         <is>
-          <t>1057439-4554-CM26</t>
+          <t>1057439-4523-CM26</t>
         </is>
       </c>
       <c r="B582" t="inlineStr">
@@ -37870,26 +37874,22 @@
       </c>
       <c r="I582" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>CARLOS ALBERTO VARGAS CASTILLO</t>
         </is>
       </c>
       <c r="J582" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
-        </is>
-      </c>
-      <c r="K582" t="inlineStr">
-        <is>
-          <t>Coquimbo</t>
-        </is>
-      </c>
+          <t>13.940.082-8</t>
+        </is>
+      </c>
+      <c r="K582" t="inlineStr"/>
       <c r="L582" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M582" s="2" t="n">
-        <v>2780.09</v>
+        <v>8135.62</v>
       </c>
     </row>
     <row r="583">
@@ -38342,7 +38342,7 @@
     <row r="590">
       <c r="A590" t="inlineStr">
         <is>
-          <t>1962-510-CM26</t>
+          <t>2711-204-CM26</t>
         </is>
       </c>
       <c r="B590" t="inlineStr">
@@ -38362,17 +38362,17 @@
       </c>
       <c r="E590" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F590" t="inlineStr">
         <is>
-          <t>61.004.012-8</t>
+          <t>69.040.700-0</t>
         </is>
       </c>
       <c r="G590" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>MUNICIPALIDAD DE OVALLE</t>
         </is>
       </c>
       <c r="H590" t="inlineStr">
@@ -38382,17 +38382,17 @@
       </c>
       <c r="I590" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>CASTILLA Y ARAGON SPA</t>
         </is>
       </c>
       <c r="J590" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.989.530-7</t>
         </is>
       </c>
       <c r="K590" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L590" t="inlineStr">
@@ -38401,13 +38401,13 @@
         </is>
       </c>
       <c r="M590" s="2" t="n">
-        <v>979.21</v>
+        <v>2345.64</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="inlineStr">
         <is>
-          <t>2711-204-CM26</t>
+          <t>1962-510-CM26</t>
         </is>
       </c>
       <c r="B591" t="inlineStr">
@@ -38427,17 +38427,17 @@
       </c>
       <c r="E591" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F591" t="inlineStr">
         <is>
-          <t>69.040.700-0</t>
+          <t>61.004.012-8</t>
         </is>
       </c>
       <c r="G591" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE OVALLE</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H591" t="inlineStr">
@@ -38447,17 +38447,17 @@
       </c>
       <c r="I591" t="inlineStr">
         <is>
-          <t>CASTILLA Y ARAGON SPA</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J591" t="inlineStr">
         <is>
-          <t>96.989.530-7</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K591" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="L591" t="inlineStr">
@@ -38466,7 +38466,7 @@
         </is>
       </c>
       <c r="M591" s="2" t="n">
-        <v>2345.64</v>
+        <v>979.21</v>
       </c>
     </row>
     <row r="592">
@@ -38598,7 +38598,7 @@
     <row r="594">
       <c r="A594" t="inlineStr">
         <is>
-          <t>2125-1600-CM26</t>
+          <t>1346282-339-CM26</t>
         </is>
       </c>
       <c r="B594" t="inlineStr">
@@ -38623,12 +38623,12 @@
       </c>
       <c r="F594" t="inlineStr">
         <is>
-          <t>61.606.407-k</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G594" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DR. HUMBERTO ELORZA CORTES</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H594" t="inlineStr">
@@ -38657,13 +38657,13 @@
         </is>
       </c>
       <c r="M594" s="2" t="n">
-        <v>920.37</v>
+        <v>1058.58</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="inlineStr">
         <is>
-          <t>1346282-339-CM26</t>
+          <t>2125-1600-CM26</t>
         </is>
       </c>
       <c r="B595" t="inlineStr">
@@ -38688,12 +38688,12 @@
       </c>
       <c r="F595" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>61.606.407-k</t>
         </is>
       </c>
       <c r="G595" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DR. HUMBERTO ELORZA CORTES</t>
         </is>
       </c>
       <c r="H595" t="inlineStr">
@@ -38722,13 +38722,13 @@
         </is>
       </c>
       <c r="M595" s="2" t="n">
-        <v>1058.58</v>
+        <v>920.37</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="inlineStr">
         <is>
-          <t>3509-326-CM26</t>
+          <t>3712-535-CM26</t>
         </is>
       </c>
       <c r="B596" t="inlineStr">
@@ -38753,12 +38753,12 @@
       </c>
       <c r="F596" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G596" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H596" t="inlineStr">
@@ -38768,12 +38768,12 @@
       </c>
       <c r="I596" t="inlineStr">
         <is>
-          <t>BAILEY GROUP SPA</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J596" t="inlineStr">
         <is>
-          <t>77.638.992-7</t>
+          <t>77.346.435-9</t>
         </is>
       </c>
       <c r="K596" t="inlineStr">
@@ -38787,13 +38787,13 @@
         </is>
       </c>
       <c r="M596" s="2" t="n">
-        <v>2123.74</v>
+        <v>1190.13</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="inlineStr">
         <is>
-          <t>3712-535-CM26</t>
+          <t>3509-326-CM26</t>
         </is>
       </c>
       <c r="B597" t="inlineStr">
@@ -38818,12 +38818,12 @@
       </c>
       <c r="F597" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G597" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H597" t="inlineStr">
@@ -38833,12 +38833,12 @@
       </c>
       <c r="I597" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>BAILEY GROUP SPA</t>
         </is>
       </c>
       <c r="J597" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
+          <t>77.638.992-7</t>
         </is>
       </c>
       <c r="K597" t="inlineStr">
@@ -38852,13 +38852,13 @@
         </is>
       </c>
       <c r="M597" s="2" t="n">
-        <v>1190.13</v>
+        <v>2123.74</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="inlineStr">
         <is>
-          <t>1574-159-CM26</t>
+          <t>1574-153-CM26</t>
         </is>
       </c>
       <c r="B598" t="inlineStr">
@@ -38898,12 +38898,12 @@
       </c>
       <c r="I598" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>IMPORTADORA Y COMERCIALIZADORA JMMB SPA</t>
         </is>
       </c>
       <c r="J598" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.461.733-7</t>
         </is>
       </c>
       <c r="K598" t="inlineStr">
@@ -38917,13 +38917,13 @@
         </is>
       </c>
       <c r="M598" s="2" t="n">
-        <v>1317.61</v>
+        <v>3053.61</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="inlineStr">
         <is>
-          <t>1574-156-CM26</t>
+          <t>1574-154-CM26</t>
         </is>
       </c>
       <c r="B599" t="inlineStr">
@@ -38963,12 +38963,12 @@
       </c>
       <c r="I599" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>IMPORTADORA Y COMERCIALIZADORA JMMB SPA</t>
         </is>
       </c>
       <c r="J599" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>77.461.733-7</t>
         </is>
       </c>
       <c r="K599" t="inlineStr">
@@ -38982,13 +38982,13 @@
         </is>
       </c>
       <c r="M599" s="2" t="n">
-        <v>1147.86</v>
+        <v>1701.69</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="inlineStr">
         <is>
-          <t>1574-155-CM26</t>
+          <t>1574-156-CM26</t>
         </is>
       </c>
       <c r="B600" t="inlineStr">
@@ -39047,13 +39047,13 @@
         </is>
       </c>
       <c r="M600" s="2" t="n">
-        <v>2142.43</v>
+        <v>1147.86</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="inlineStr">
         <is>
-          <t>1574-154-CM26</t>
+          <t>1574-157-CM26</t>
         </is>
       </c>
       <c r="B601" t="inlineStr">
@@ -39093,12 +39093,12 @@
       </c>
       <c r="I601" t="inlineStr">
         <is>
-          <t>IMPORTADORA Y COMERCIALIZADORA JMMB SPA</t>
+          <t>COMERCIALIZADORA CUARENTA Y UNO SPA</t>
         </is>
       </c>
       <c r="J601" t="inlineStr">
         <is>
-          <t>77.461.733-7</t>
+          <t>78.085.401-4</t>
         </is>
       </c>
       <c r="K601" t="inlineStr">
@@ -39112,13 +39112,13 @@
         </is>
       </c>
       <c r="M601" s="2" t="n">
-        <v>1701.69</v>
+        <v>11365.81</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="inlineStr">
         <is>
-          <t>1574-153-CM26</t>
+          <t>1574-158-CM26</t>
         </is>
       </c>
       <c r="B602" t="inlineStr">
@@ -39158,12 +39158,12 @@
       </c>
       <c r="I602" t="inlineStr">
         <is>
-          <t>IMPORTADORA Y COMERCIALIZADORA JMMB SPA</t>
+          <t>COMERCIALIZADORA CUARENTA Y UNO SPA</t>
         </is>
       </c>
       <c r="J602" t="inlineStr">
         <is>
-          <t>77.461.733-7</t>
+          <t>78.085.401-4</t>
         </is>
       </c>
       <c r="K602" t="inlineStr">
@@ -39177,13 +39177,13 @@
         </is>
       </c>
       <c r="M602" s="2" t="n">
-        <v>3053.61</v>
+        <v>10317.27</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="inlineStr">
         <is>
-          <t>3265-417-CM26</t>
+          <t>1574-159-CM26</t>
         </is>
       </c>
       <c r="B603" t="inlineStr">
@@ -39203,17 +39203,17 @@
       </c>
       <c r="E603" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F603" t="inlineStr">
         <is>
-          <t>69.041.000-1</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G603" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RIO HURTADO</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H603" t="inlineStr">
@@ -39223,12 +39223,12 @@
       </c>
       <c r="I603" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA CUARENTA Y UNO SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J603" t="inlineStr">
         <is>
-          <t>78.085.401-4</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K603" t="inlineStr">
@@ -39242,13 +39242,13 @@
         </is>
       </c>
       <c r="M603" s="2" t="n">
-        <v>1344.24</v>
+        <v>1317.61</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="inlineStr">
         <is>
-          <t>1574-158-CM26</t>
+          <t>3265-417-CM26</t>
         </is>
       </c>
       <c r="B604" t="inlineStr">
@@ -39268,17 +39268,17 @@
       </c>
       <c r="E604" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F604" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>69.041.000-1</t>
         </is>
       </c>
       <c r="G604" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>I MUNICIPALIDAD DE RIO HURTADO</t>
         </is>
       </c>
       <c r="H604" t="inlineStr">
@@ -39307,13 +39307,13 @@
         </is>
       </c>
       <c r="M604" s="2" t="n">
-        <v>10317.27</v>
+        <v>1344.24</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="inlineStr">
         <is>
-          <t>1574-157-CM26</t>
+          <t>1574-155-CM26</t>
         </is>
       </c>
       <c r="B605" t="inlineStr">
@@ -39353,12 +39353,12 @@
       </c>
       <c r="I605" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA CUARENTA Y UNO SPA</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J605" t="inlineStr">
         <is>
-          <t>78.085.401-4</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K605" t="inlineStr">
@@ -39372,7 +39372,7 @@
         </is>
       </c>
       <c r="M605" s="2" t="n">
-        <v>11365.81</v>
+        <v>2142.43</v>
       </c>
     </row>
     <row r="606">
@@ -39959,7 +39959,7 @@
     <row r="615">
       <c r="A615" t="inlineStr">
         <is>
-          <t>3712-561-CM26</t>
+          <t>2450-854-CM26</t>
         </is>
       </c>
       <c r="B615" t="inlineStr">
@@ -39984,12 +39984,12 @@
       </c>
       <c r="F615" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>69.040.100-2</t>
         </is>
       </c>
       <c r="G615" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>ILUSTRE MUNICIPALIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H615" t="inlineStr">
@@ -39999,12 +39999,12 @@
       </c>
       <c r="I615" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>BAILEY GROUP SPA</t>
         </is>
       </c>
       <c r="J615" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.638.992-7</t>
         </is>
       </c>
       <c r="K615" t="inlineStr">
@@ -40018,13 +40018,13 @@
         </is>
       </c>
       <c r="M615" s="2" t="n">
-        <v>1447.99</v>
+        <v>11355.09</v>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="inlineStr">
         <is>
-          <t>4619-16-CM26</t>
+          <t>3712-561-CM26</t>
         </is>
       </c>
       <c r="B616" t="inlineStr">
@@ -40049,12 +40049,12 @@
       </c>
       <c r="F616" t="inlineStr">
         <is>
-          <t>61.502.000-1</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G616" t="inlineStr">
         <is>
-          <t>DIRECCION DEL TRABAJO</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H616" t="inlineStr">
@@ -40064,17 +40064,17 @@
       </c>
       <c r="I616" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J616" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K616" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L616" t="inlineStr">
@@ -40083,13 +40083,13 @@
         </is>
       </c>
       <c r="M616" s="2" t="n">
-        <v>3364.3</v>
+        <v>1447.99</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="inlineStr">
         <is>
-          <t>1962-556-CM26</t>
+          <t>4619-16-CM26</t>
         </is>
       </c>
       <c r="B617" t="inlineStr">
@@ -40114,12 +40114,12 @@
       </c>
       <c r="F617" t="inlineStr">
         <is>
-          <t>61.004.012-8</t>
+          <t>61.502.000-1</t>
         </is>
       </c>
       <c r="G617" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>DIRECCION DEL TRABAJO</t>
         </is>
       </c>
       <c r="H617" t="inlineStr">
@@ -40129,17 +40129,17 @@
       </c>
       <c r="I617" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J617" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K617" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L617" t="inlineStr">
@@ -40148,13 +40148,13 @@
         </is>
       </c>
       <c r="M617" s="2" t="n">
-        <v>2715.35</v>
+        <v>3364.3</v>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="inlineStr">
         <is>
-          <t>2450-854-CM26</t>
+          <t>1962-556-CM26</t>
         </is>
       </c>
       <c r="B618" t="inlineStr">
@@ -40179,12 +40179,12 @@
       </c>
       <c r="F618" t="inlineStr">
         <is>
-          <t>69.040.100-2</t>
+          <t>61.004.012-8</t>
         </is>
       </c>
       <c r="G618" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE LA SERENA</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H618" t="inlineStr">
@@ -40194,12 +40194,12 @@
       </c>
       <c r="I618" t="inlineStr">
         <is>
-          <t>BAILEY GROUP SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J618" t="inlineStr">
         <is>
-          <t>77.638.992-7</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K618" t="inlineStr">
@@ -40213,7 +40213,7 @@
         </is>
       </c>
       <c r="M618" s="2" t="n">
-        <v>11355.09</v>
+        <v>2715.35</v>
       </c>
     </row>
     <row r="619">
@@ -40414,7 +40414,7 @@
     <row r="622">
       <c r="A622" t="inlineStr">
         <is>
-          <t>2711-226-CM26</t>
+          <t>3511-297-CM26</t>
         </is>
       </c>
       <c r="B622" t="inlineStr">
@@ -40439,12 +40439,12 @@
       </c>
       <c r="F622" t="inlineStr">
         <is>
-          <t>69.040.700-0</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G622" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE OVALLE</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H622" t="inlineStr">
@@ -40454,12 +40454,12 @@
       </c>
       <c r="I622" t="inlineStr">
         <is>
-          <t>BAILEY GROUP SPA</t>
+          <t>CASTILLA Y ARAGON SPA</t>
         </is>
       </c>
       <c r="J622" t="inlineStr">
         <is>
-          <t>77.638.992-7</t>
+          <t>96.989.530-7</t>
         </is>
       </c>
       <c r="K622" t="inlineStr">
@@ -40473,7 +40473,7 @@
         </is>
       </c>
       <c r="M622" s="2" t="n">
-        <v>878.9299999999999</v>
+        <v>1627.53</v>
       </c>
     </row>
     <row r="623">
@@ -40544,7 +40544,7 @@
     <row r="624">
       <c r="A624" t="inlineStr">
         <is>
-          <t>3511-297-CM26</t>
+          <t>2711-226-CM26</t>
         </is>
       </c>
       <c r="B624" t="inlineStr">
@@ -40569,12 +40569,12 @@
       </c>
       <c r="F624" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>69.040.700-0</t>
         </is>
       </c>
       <c r="G624" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>MUNICIPALIDAD DE OVALLE</t>
         </is>
       </c>
       <c r="H624" t="inlineStr">
@@ -40584,12 +40584,12 @@
       </c>
       <c r="I624" t="inlineStr">
         <is>
-          <t>CASTILLA Y ARAGON SPA</t>
+          <t>BAILEY GROUP SPA</t>
         </is>
       </c>
       <c r="J624" t="inlineStr">
         <is>
-          <t>96.989.530-7</t>
+          <t>77.638.992-7</t>
         </is>
       </c>
       <c r="K624" t="inlineStr">
@@ -40603,13 +40603,13 @@
         </is>
       </c>
       <c r="M624" s="2" t="n">
-        <v>1627.53</v>
+        <v>878.9299999999999</v>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="inlineStr">
         <is>
-          <t>1574-234-CM26</t>
+          <t>1230663-155-CM26</t>
         </is>
       </c>
       <c r="B625" t="inlineStr">
@@ -40634,12 +40634,12 @@
       </c>
       <c r="F625" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>65.100.165-k</t>
         </is>
       </c>
       <c r="G625" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>CORPORACION CULTURAL MUNICIPAL DE VICUNA</t>
         </is>
       </c>
       <c r="H625" t="inlineStr">
@@ -40649,17 +40649,17 @@
       </c>
       <c r="I625" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA CUARENTA Y UNO SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J625" t="inlineStr">
         <is>
-          <t>78.085.401-4</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K625" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L625" t="inlineStr">
@@ -40668,13 +40668,13 @@
         </is>
       </c>
       <c r="M625" s="2" t="n">
-        <v>7170.29</v>
+        <v>804.72</v>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="inlineStr">
         <is>
-          <t>1230663-155-CM26</t>
+          <t>1574-234-CM26</t>
         </is>
       </c>
       <c r="B626" t="inlineStr">
@@ -40699,12 +40699,12 @@
       </c>
       <c r="F626" t="inlineStr">
         <is>
-          <t>65.100.165-k</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G626" t="inlineStr">
         <is>
-          <t>CORPORACION CULTURAL MUNICIPAL DE VICUNA</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H626" t="inlineStr">
@@ -40714,17 +40714,17 @@
       </c>
       <c r="I626" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIALIZADORA CUARENTA Y UNO SPA</t>
         </is>
       </c>
       <c r="J626" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>78.085.401-4</t>
         </is>
       </c>
       <c r="K626" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L626" t="inlineStr">
@@ -40733,7 +40733,7 @@
         </is>
       </c>
       <c r="M626" s="2" t="n">
-        <v>804.72</v>
+        <v>7170.29</v>
       </c>
     </row>
     <row r="627">
@@ -40934,7 +40934,7 @@
     <row r="630">
       <c r="A630" t="inlineStr">
         <is>
-          <t>1962-604-CM26</t>
+          <t>1057439-5685-CM26</t>
         </is>
       </c>
       <c r="B630" t="inlineStr">
@@ -40959,12 +40959,12 @@
       </c>
       <c r="F630" t="inlineStr">
         <is>
-          <t>61.004.012-8</t>
+          <t>61.606.402-9</t>
         </is>
       </c>
       <c r="G630" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
         </is>
       </c>
       <c r="H630" t="inlineStr">
@@ -40974,32 +40974,28 @@
       </c>
       <c r="I630" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>CARLOS ALBERTO VARGAS CASTILLO</t>
         </is>
       </c>
       <c r="J630" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
-        </is>
-      </c>
-      <c r="K630" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>13.940.082-8</t>
+        </is>
+      </c>
+      <c r="K630" t="inlineStr"/>
       <c r="L630" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M630" s="2" t="n">
-        <v>771.13</v>
+        <v>7381.49</v>
       </c>
     </row>
     <row r="631">
       <c r="A631" t="inlineStr">
         <is>
-          <t>1057439-5685-CM26</t>
+          <t>1962-604-CM26</t>
         </is>
       </c>
       <c r="B631" t="inlineStr">
@@ -41024,12 +41020,12 @@
       </c>
       <c r="F631" t="inlineStr">
         <is>
-          <t>61.606.402-9</t>
+          <t>61.004.012-8</t>
         </is>
       </c>
       <c r="G631" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H631" t="inlineStr">
@@ -41039,22 +41035,26 @@
       </c>
       <c r="I631" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO VARGAS CASTILLO</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J631" t="inlineStr">
         <is>
-          <t>13.940.082-8</t>
-        </is>
-      </c>
-      <c r="K631" t="inlineStr"/>
+          <t>77.346.435-9</t>
+        </is>
+      </c>
+      <c r="K631" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L631" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M631" s="2" t="n">
-        <v>7381.49</v>
+        <v>771.13</v>
       </c>
     </row>
     <row r="632">
@@ -41121,7 +41121,7 @@
     <row r="633">
       <c r="A633" t="inlineStr">
         <is>
-          <t>3712-565-CM26</t>
+          <t>3511-316-CM26</t>
         </is>
       </c>
       <c r="B633" t="inlineStr">
@@ -41141,17 +41141,17 @@
       </c>
       <c r="E633" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F633" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G633" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H633" t="inlineStr">
@@ -41161,17 +41161,17 @@
       </c>
       <c r="I633" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J633" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K633" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L633" t="inlineStr">
@@ -41180,13 +41180,13 @@
         </is>
       </c>
       <c r="M633" s="2" t="n">
-        <v>1880.11</v>
+        <v>1151.54</v>
       </c>
     </row>
     <row r="634">
       <c r="A634" t="inlineStr">
         <is>
-          <t>3511-316-CM26</t>
+          <t>3712-565-CM26</t>
         </is>
       </c>
       <c r="B634" t="inlineStr">
@@ -41206,17 +41206,17 @@
       </c>
       <c r="E634" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F634" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G634" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H634" t="inlineStr">
@@ -41226,17 +41226,17 @@
       </c>
       <c r="I634" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J634" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.346.435-9</t>
         </is>
       </c>
       <c r="K634" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L634" t="inlineStr">
@@ -41245,7 +41245,7 @@
         </is>
       </c>
       <c r="M634" s="2" t="n">
-        <v>1151.54</v>
+        <v>1880.11</v>
       </c>
     </row>
     <row r="635">
@@ -41511,7 +41511,7 @@
     <row r="639">
       <c r="A639" t="inlineStr">
         <is>
-          <t>1352-76-CM26</t>
+          <t>1352-75-CM26</t>
         </is>
       </c>
       <c r="B639" t="inlineStr">
@@ -41570,13 +41570,13 @@
         </is>
       </c>
       <c r="M639" s="2" t="n">
-        <v>2760.88</v>
+        <v>2435.28</v>
       </c>
     </row>
     <row r="640">
       <c r="A640" t="inlineStr">
         <is>
-          <t>1352-75-CM26</t>
+          <t>1352-76-CM26</t>
         </is>
       </c>
       <c r="B640" t="inlineStr">
@@ -41635,7 +41635,7 @@
         </is>
       </c>
       <c r="M640" s="2" t="n">
-        <v>2435.28</v>
+        <v>2760.88</v>
       </c>
     </row>
     <row r="641">
@@ -41706,7 +41706,7 @@
     <row r="642">
       <c r="A642" t="inlineStr">
         <is>
-          <t>3712-636-CM26</t>
+          <t>3511-300-CM26</t>
         </is>
       </c>
       <c r="B642" t="inlineStr">
@@ -41726,17 +41726,17 @@
       </c>
       <c r="E642" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F642" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G642" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H642" t="inlineStr">
@@ -41746,12 +41746,12 @@
       </c>
       <c r="I642" t="inlineStr">
         <is>
-          <t>BAILEY GROUP SPA</t>
+          <t>COMERCIAL VALLE SPA</t>
         </is>
       </c>
       <c r="J642" t="inlineStr">
         <is>
-          <t>77.638.992-7</t>
+          <t>77.988.165-2</t>
         </is>
       </c>
       <c r="K642" t="inlineStr">
@@ -41765,13 +41765,13 @@
         </is>
       </c>
       <c r="M642" s="2" t="n">
-        <v>1465.42</v>
+        <v>836.36</v>
       </c>
     </row>
     <row r="643">
       <c r="A643" t="inlineStr">
         <is>
-          <t>3511-300-CM26</t>
+          <t>3712-636-CM26</t>
         </is>
       </c>
       <c r="B643" t="inlineStr">
@@ -41791,17 +41791,17 @@
       </c>
       <c r="E643" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F643" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G643" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H643" t="inlineStr">
@@ -41811,12 +41811,12 @@
       </c>
       <c r="I643" t="inlineStr">
         <is>
-          <t>COMERCIAL VALLE SPA</t>
+          <t>BAILEY GROUP SPA</t>
         </is>
       </c>
       <c r="J643" t="inlineStr">
         <is>
-          <t>77.988.165-2</t>
+          <t>77.638.992-7</t>
         </is>
       </c>
       <c r="K643" t="inlineStr">
@@ -41830,13 +41830,13 @@
         </is>
       </c>
       <c r="M643" s="2" t="n">
-        <v>836.36</v>
+        <v>1465.42</v>
       </c>
     </row>
     <row r="644">
       <c r="A644" t="inlineStr">
         <is>
-          <t>2708-513-CM26</t>
+          <t>1673-223-CM26</t>
         </is>
       </c>
       <c r="B644" t="inlineStr">
@@ -41856,17 +41856,17 @@
       </c>
       <c r="E644" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F644" t="inlineStr">
         <is>
-          <t>69.040.700-0</t>
+          <t>61.606.401-0</t>
         </is>
       </c>
       <c r="G644" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE OVALLE</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL VICUNA</t>
         </is>
       </c>
       <c r="H644" t="inlineStr">
@@ -41876,17 +41876,17 @@
       </c>
       <c r="I644" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J644" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K644" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L644" t="inlineStr">
@@ -41895,13 +41895,13 @@
         </is>
       </c>
       <c r="M644" s="2" t="n">
-        <v>1541.16</v>
+        <v>748.35</v>
       </c>
     </row>
     <row r="645">
       <c r="A645" t="inlineStr">
         <is>
-          <t>3511-365-CM26</t>
+          <t>1057438-265-CM26</t>
         </is>
       </c>
       <c r="B645" t="inlineStr">
@@ -41921,17 +41921,17 @@
       </c>
       <c r="E645" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F645" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>61.606.401-0</t>
         </is>
       </c>
       <c r="G645" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL VICUNA</t>
         </is>
       </c>
       <c r="H645" t="inlineStr">
@@ -41941,12 +41941,12 @@
       </c>
       <c r="I645" t="inlineStr">
         <is>
-          <t>CASTILLA Y ARAGON SPA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J645" t="inlineStr">
         <is>
-          <t>96.989.530-7</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K645" t="inlineStr">
@@ -41960,7 +41960,7 @@
         </is>
       </c>
       <c r="M645" s="2" t="n">
-        <v>3820.84</v>
+        <v>747.9299999999999</v>
       </c>
     </row>
     <row r="646">
@@ -42031,7 +42031,7 @@
     <row r="647">
       <c r="A647" t="inlineStr">
         <is>
-          <t>1057438-265-CM26</t>
+          <t>3511-365-CM26</t>
         </is>
       </c>
       <c r="B647" t="inlineStr">
@@ -42051,17 +42051,17 @@
       </c>
       <c r="E647" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F647" t="inlineStr">
         <is>
-          <t>61.606.401-0</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G647" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL VICUNA</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H647" t="inlineStr">
@@ -42071,12 +42071,12 @@
       </c>
       <c r="I647" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>CASTILLA Y ARAGON SPA</t>
         </is>
       </c>
       <c r="J647" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>96.989.530-7</t>
         </is>
       </c>
       <c r="K647" t="inlineStr">
@@ -42090,13 +42090,13 @@
         </is>
       </c>
       <c r="M647" s="2" t="n">
-        <v>747.9299999999999</v>
+        <v>3820.84</v>
       </c>
     </row>
     <row r="648">
       <c r="A648" t="inlineStr">
         <is>
-          <t>1673-223-CM26</t>
+          <t>2708-513-CM26</t>
         </is>
       </c>
       <c r="B648" t="inlineStr">
@@ -42116,17 +42116,17 @@
       </c>
       <c r="E648" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F648" t="inlineStr">
         <is>
-          <t>61.606.401-0</t>
+          <t>69.040.700-0</t>
         </is>
       </c>
       <c r="G648" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL VICUNA</t>
+          <t>MUNICIPALIDAD DE OVALLE</t>
         </is>
       </c>
       <c r="H648" t="inlineStr">
@@ -42136,17 +42136,17 @@
       </c>
       <c r="I648" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J648" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K648" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L648" t="inlineStr">
@@ -42155,7 +42155,7 @@
         </is>
       </c>
       <c r="M648" s="2" t="n">
-        <v>748.35</v>
+        <v>1541.16</v>
       </c>
     </row>
     <row r="649">
@@ -43217,7 +43217,7 @@
       </c>
       <c r="E665" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F665" t="inlineStr">
@@ -43383,6 +43383,331 @@
       </c>
       <c r="M667" s="2" t="n">
         <v>7053.91</v>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" t="inlineStr">
+        <is>
+          <t>1159-283-CM26</t>
+        </is>
+      </c>
+      <c r="B668" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C668" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D668" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="E668" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F668" t="inlineStr">
+        <is>
+          <t>61.308.000-7</t>
+        </is>
+      </c>
+      <c r="G668" t="inlineStr">
+        <is>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
+        </is>
+      </c>
+      <c r="H668" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I668" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+        </is>
+      </c>
+      <c r="J668" t="inlineStr">
+        <is>
+          <t>77.346.435-9</t>
+        </is>
+      </c>
+      <c r="K668" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L668" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M668" s="2" t="n">
+        <v>807.97</v>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" t="inlineStr">
+        <is>
+          <t>2711-283-CM26</t>
+        </is>
+      </c>
+      <c r="B669" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C669" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D669" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="E669" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F669" t="inlineStr">
+        <is>
+          <t>69.040.700-0</t>
+        </is>
+      </c>
+      <c r="G669" t="inlineStr">
+        <is>
+          <t>MUNICIPALIDAD DE OVALLE</t>
+        </is>
+      </c>
+      <c r="H669" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I669" t="inlineStr">
+        <is>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+        </is>
+      </c>
+      <c r="J669" t="inlineStr">
+        <is>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K669" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L669" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M669" s="2" t="n">
+        <v>32044.76</v>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" t="inlineStr">
+        <is>
+          <t>5416-1161-CM26</t>
+        </is>
+      </c>
+      <c r="B670" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C670" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D670" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E670" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F670" t="inlineStr">
+        <is>
+          <t>70.783.100-6</t>
+        </is>
+      </c>
+      <c r="G670" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE LA SERENA</t>
+        </is>
+      </c>
+      <c r="H670" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I670" t="inlineStr">
+        <is>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+        </is>
+      </c>
+      <c r="J670" t="inlineStr">
+        <is>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K670" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L670" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M670" s="2" t="n">
+        <v>1844.44</v>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" t="inlineStr">
+        <is>
+          <t>707418-152-CM26</t>
+        </is>
+      </c>
+      <c r="B671" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C671" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D671" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="E671" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F671" t="inlineStr">
+        <is>
+          <t>70.574.900-0</t>
+        </is>
+      </c>
+      <c r="G671" t="inlineStr">
+        <is>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+        </is>
+      </c>
+      <c r="H671" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I671" t="inlineStr">
+        <is>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+        </is>
+      </c>
+      <c r="J671" t="inlineStr">
+        <is>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K671" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L671" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M671" s="2" t="n">
+        <v>2943.28</v>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" t="inlineStr">
+        <is>
+          <t>2711-287-CM26</t>
+        </is>
+      </c>
+      <c r="B672" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C672" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D672" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="E672" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F672" t="inlineStr">
+        <is>
+          <t>69.040.700-0</t>
+        </is>
+      </c>
+      <c r="G672" t="inlineStr">
+        <is>
+          <t>MUNICIPALIDAD DE OVALLE</t>
+        </is>
+      </c>
+      <c r="H672" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I672" t="inlineStr">
+        <is>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+        </is>
+      </c>
+      <c r="J672" t="inlineStr">
+        <is>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K672" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L672" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M672" s="2" t="n">
+        <v>21877.47</v>
       </c>
     </row>
   </sheetData>
